--- a/exhibition/contacts.xlsx
+++ b/exhibition/contacts.xlsx
@@ -12,7 +12,7 @@
     <sheet name="По странам" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Контакты!$A$1:$T$2</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Контакты!$A$1:$U$3</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="54">
   <si>
     <t xml:space="preserve">№</t>
   </si>
@@ -38,6 +38,9 @@
     <t xml:space="preserve">Компания</t>
   </si>
   <si>
+    <t xml:space="preserve">Выставка / стенд</t>
+  </si>
+  <si>
     <t xml:space="preserve">Сайт</t>
   </si>
   <si>
@@ -138,6 +141,42 @@
   </si>
   <si>
     <t xml:space="preserve">photos/001_kava.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Франция</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Авиньон</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Effervescence Lab</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cosmetic 360, стенд FB12 (Innovation Route — Formulation)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">effervescence-lab.com (по домену email, не проверен)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Независимая R&amp;D-лаборатория: разработка формул косметики «под ключ» — создание формулы, тесты, регуляторное досье. Формулы на заказ (sur mesure) и эксклюзивные. Категории: уход за кожей, солнцезащита, уход за волосами, пенящиеся средства, тональные (teint), стики, бальзамы, стерильные формулы. Конвенциональная и органическая (bio) косметика. Акцент на сенсорику и инновационные текстуры</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Авиньон, Франция</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ни с кем не познакомились — только фото стенда</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Основатель и директор — Muriel Hibon (физикохимия формулирования, 20+ лет в R&amp;D косметики). Коллекции готовых основ: Sublime, Hybride, Essentia (2025). Собственное производство в открытых источниках не подтверждено — уточнить, делают ли выпуск партий или только разработку.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.industries-cosmetiques.fr/en/effervescence-lab-formulation-et-sensorialite ; https://www.luxepackmonaco.com/en/speakers/67bdab0816a05b57ffb96610 ; https://www.cosmed.fr/app/uploads/2026/03/technicienne-de-formulation.pdf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Найти контакт (написать через сайт / LinkedIn Muriel Hibon), запросить условия разработки формулы и есть ли производство</t>
+  </si>
+  <si>
+    <t xml:space="preserve">photos/002_effervescence_lab.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">Компаний</t>
@@ -588,26 +627,27 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:T2"/>
+  <dimension ref="A1:U3"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="7" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="50"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="18" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="8" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="19" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="18"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -671,23 +711,24 @@
       <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E2" s="2" t="s">
         <v>23</v>
       </c>
+      <c r="E2" s="2"/>
       <c r="F2" s="2" t="s">
         <v>24</v>
       </c>
@@ -703,10 +744,10 @@
       <c r="J2" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>29</v>
       </c>
+      <c r="L2" s="2"/>
       <c r="M2" s="2" t="s">
         <v>30</v>
       </c>
@@ -731,9 +772,63 @@
       <c r="T2" s="2" t="s">
         <v>37</v>
       </c>
+      <c r="U2" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="S3" s="2"/>
+      <c r="T3" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>50</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T2"/>
+  <autoFilter ref="A1:U3"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -750,7 +845,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
@@ -763,35 +858,48 @@
         <v>1</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>39</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B2" s="5" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$2,A2)</f>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$3,A2)</f>
         <v>1</v>
       </c>
       <c r="C2" s="5" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$2,A2,Контакты!$R$2:$R$2,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$3,A2,Контакты!$S$2:$S$3,"Высокий")</f>
         <v>1</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B3" s="6" t="n">
-        <f aca="false">SUM(B2:B2)</f>
+      <c r="A3" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="5" t="n">
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$3,A3)</f>
         <v>1</v>
       </c>
-      <c r="C3" s="6" t="n">
-        <f aca="false">SUM(C2:C2)</f>
+      <c r="C3" s="5" t="n">
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$3,A3,Контакты!$S$2:$S$3,"Высокий")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="6" t="n">
+        <f aca="false">SUM(B2:B3)</f>
+        <v>2</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <f aca="false">SUM(C2:C3)</f>
         <v>1</v>
       </c>
     </row>

--- a/exhibition/contacts.xlsx
+++ b/exhibition/contacts.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="57">
   <si>
     <t xml:space="preserve">№</t>
   </si>
@@ -155,13 +155,22 @@
     <t xml:space="preserve">Cosmetic 360, стенд FB12 (Innovation Route — Formulation)</t>
   </si>
   <si>
-    <t xml:space="preserve">effervescence-lab.com (по домену email, не проверен)</t>
+    <t xml:space="preserve">www.effervescence-lab.com</t>
   </si>
   <si>
     <t xml:space="preserve">Независимая R&amp;D-лаборатория: разработка формул косметики «под ключ» — создание формулы, тесты, регуляторное досье. Формулы на заказ (sur mesure) и эксклюзивные. Категории: уход за кожей, солнцезащита, уход за волосами, пенящиеся средства, тональные (teint), стики, бальзамы, стерильные формулы. Конвенциональная и органическая (bio) косметика. Акцент на сенсорику и инновационные текстуры</t>
   </si>
   <si>
-    <t xml:space="preserve">Авиньон, Франция</t>
+    <t xml:space="preserve">contact@effervescence-lab.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+33 4 86 40 84 88</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le Newton, 65 Rue Lawrence Durrell, BP 51 552, 84916 Avignon Cedex 09, Франция</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Буклет со стенда (контакты на обороте)</t>
   </si>
   <si>
     <t xml:space="preserve">Ни с кем не познакомились — только фото стенда</t>
@@ -173,10 +182,10 @@
     <t xml:space="preserve">https://www.industries-cosmetiques.fr/en/effervescence-lab-formulation-et-sensorialite ; https://www.luxepackmonaco.com/en/speakers/67bdab0816a05b57ffb96610 ; https://www.cosmed.fr/app/uploads/2026/03/technicienne-de-formulation.pdf</t>
   </si>
   <si>
-    <t xml:space="preserve">Найти контакт (написать через сайт / LinkedIn Muriel Hibon), запросить условия разработки формулы и есть ли производство</t>
-  </si>
-  <si>
-    <t xml:space="preserve">photos/002_effervescence_lab.jpg</t>
+    <t xml:space="preserve">Написать на contact@effervescence-lab.com: условия разработки формулы, сроки, есть ли собственное производство/выпуск партий</t>
+  </si>
+  <si>
+    <t xml:space="preserve">photos/002_effervescence_lab.jpg ; photos/002b_effervescence_lab_brochure.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">Компаний</t>
@@ -801,30 +810,36 @@
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
+      <c r="K3" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>46</v>
+      </c>
       <c r="M3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="N3" s="2"/>
+        <v>47</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>48</v>
+      </c>
       <c r="O3" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="R3" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="S3" s="2"/>
       <c r="T3" s="2" t="s">
         <v>37</v>
       </c>
       <c r="U3" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -858,10 +873,10 @@
         <v>1</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -892,7 +907,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B4" s="6" t="n">
         <f aca="false">SUM(B2:B3)</f>

--- a/exhibition/contacts.xlsx
+++ b/exhibition/contacts.xlsx
@@ -12,7 +12,7 @@
     <sheet name="По странам" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Контакты!$A$1:$U$3</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Контакты!$A$1:$V$4</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="72">
   <si>
     <t xml:space="preserve">№</t>
   </si>
@@ -44,6 +44,9 @@
     <t xml:space="preserve">Сайт</t>
   </si>
   <si>
+    <t xml:space="preserve">Каталог</t>
+  </si>
+  <si>
     <t xml:space="preserve">Что производят</t>
   </si>
   <si>
@@ -186,6 +189,48 @@
   </si>
   <si>
     <t xml:space="preserve">photos/002_effervescence_lab.jpg ; photos/002b_effervescence_lab_brochure.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Япония</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Европейский офис: Леваллуа-Перре (пригород Парижа), Франция. Головной офис: Токио</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iwase Cosfa Europe (группа Iwase Cosfa)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cosmetic 360</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://iwasecosfa.eu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://iwasecosfa-eu.covalo.com/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Дистрибьютор японского косметического сырья: активные ингредиенты, эмульгаторы, УФ-фильтры, пигменты, текстурирующие агенты. На стенде — Formulation Book «Horizons — Beauty without boundaries» (готовые рецептуры на их ингредиентах)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">92300 Levallois-Perret, Франция</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Буклет Formulation Book «Horizons», QR-код на каталог</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ни с кем не познакомились — взяли буклет</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Японская группа, основана в 1931 г., штаб-квартира в Токио; офисы во Франции и США, недавно вышли в Марокко. Материнская компания сертифицирована ISO 9001 и ISO 14001. Коммерческий директор Europe — Antoine Joubin.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.cosmetic-valley.com/en/annuaire-entreprises/iwase-cosfa-europe ; https://ledesk.ma/enoff/cosmetique-le-japonais-iwase-cosfa-choisit-le-maroc-pour-souvrir-au-marche-africain/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Посмотреть каталог по ссылке, выбрать интересные ингредиенты; связаться через сайт / Antoine Joubin</t>
+  </si>
+  <si>
+    <t xml:space="preserve">photos/003_iwase_cosfa.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">Компаний</t>
@@ -204,7 +249,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -244,6 +289,14 @@
     <font>
       <b val="true"/>
       <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <u val="single"/>
+      <sz val="10"/>
+      <color rgb="FF0563C1"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -318,7 +371,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -332,6 +385,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -356,7 +413,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="4">
+  <dxfs count="5">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -388,6 +445,14 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF0563C1"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <colors>
     <indexedColors>
@@ -413,7 +478,7 @@
       <rgbColor rgb="FFDDEBF7"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
+      <rgbColor rgb="FF0563C1"/>
       <rgbColor rgb="FFCCCCFF"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
@@ -636,7 +701,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:V4"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -645,18 +710,19 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="24"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="8" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="50"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="19" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="20" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="18"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -723,27 +789,28 @@
       <c r="U1" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E2" s="2"/>
-      <c r="F2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="G2" s="2" t="s">
+      <c r="F2" s="4" t="s">
         <v>25</v>
       </c>
+      <c r="G2" s="2"/>
       <c r="H2" s="2" t="s">
         <v>26</v>
       </c>
@@ -756,10 +823,10 @@
       <c r="K2" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>30</v>
       </c>
+      <c r="M2" s="2"/>
       <c r="N2" s="2" t="s">
         <v>31</v>
       </c>
@@ -783,6 +850,9 @@
       </c>
       <c r="U2" s="2" t="s">
         <v>38</v>
+      </c>
+      <c r="V2" s="2" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -790,29 +860,27 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="F3" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="F3" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="H3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2" t="s">
+        <v>45</v>
+      </c>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
-      <c r="K3" s="2" t="s">
-        <v>45</v>
-      </c>
+      <c r="K3" s="2"/>
       <c r="L3" s="2" t="s">
         <v>46</v>
       </c>
@@ -834,16 +902,81 @@
       <c r="R3" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="S3" s="2"/>
-      <c r="T3" s="2" t="s">
-        <v>37</v>
-      </c>
+      <c r="S3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="T3" s="2"/>
       <c r="U3" s="2" t="s">
-        <v>53</v>
+        <v>38</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="I4" s="2"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
+      <c r="N4" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="T4" s="2"/>
+      <c r="U4" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="V4" s="2" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U3"/>
+  <autoFilter ref="A1:V4"/>
+  <hyperlinks>
+    <hyperlink ref="F2" r:id="rId1" display="www.kava.cn"/>
+    <hyperlink ref="F3" r:id="rId2" display="www.effervescence-lab.com"/>
+    <hyperlink ref="F4" r:id="rId3" display="https://iwasecosfa.eu"/>
+    <hyperlink ref="G4" r:id="rId4" display="https://iwasecosfa-eu.covalo.com/"/>
+  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -851,7 +984,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId1"/>
+  <drawing r:id="rId5"/>
 </worksheet>
 </file>
 
@@ -860,7 +993,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
@@ -869,52 +1002,65 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>55</v>
+      <c r="B1" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B2" s="5" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$3,A2)</f>
+      <c r="A2" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B2" s="6" t="n">
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$4,A2)</f>
         <v>1</v>
       </c>
-      <c r="C2" s="5" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$3,A2,Контакты!$S$2:$S$3,"Высокий")</f>
+      <c r="C2" s="6" t="n">
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$4,A2,Контакты!$T$2:$T$4,"Высокий")</f>
         <v>1</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" s="5" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$3,A3)</f>
+      <c r="A3" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="6" t="n">
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$4,A3)</f>
         <v>1</v>
       </c>
-      <c r="C3" s="5" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$3,A3,Контакты!$S$2:$S$3,"Высокий")</f>
+      <c r="C3" s="6" t="n">
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$4,A3,Контакты!$T$2:$T$4,"Высокий")</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B4" s="6" t="n">
-        <f aca="false">SUM(B2:B3)</f>
-        <v>2</v>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$4,A4)</f>
+        <v>1</v>
       </c>
       <c r="C4" s="6" t="n">
-        <f aca="false">SUM(C2:C3)</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$4,A4,Контакты!$T$2:$T$4,"Высокий")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="B5" s="7" t="n">
+        <f aca="false">SUM(B2:B4)</f>
+        <v>3</v>
+      </c>
+      <c r="C5" s="7" t="n">
+        <f aca="false">SUM(C2:C4)</f>
         <v>1</v>
       </c>
     </row>

--- a/exhibition/contacts.xlsx
+++ b/exhibition/contacts.xlsx
@@ -12,7 +12,7 @@
     <sheet name="По странам" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Контакты!$A$1:$V$4</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Контакты!$A$1:$V$5</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="84">
   <si>
     <t xml:space="preserve">№</t>
   </si>
@@ -189,6 +189,42 @@
   </si>
   <si>
     <t xml:space="preserve">photos/002_effervescence_lab.jpg ; photos/002b_effervescence_lab_brochure.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Шартр (головной офис); производство — О-де-Франс (Невиль-ан-Феррен, под Лиллем), Нормандия; 1 завод в Польше</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vabel Groupe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cosmetic 360, стенд FA31 (Innovation Route — Formulation)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vabel.fr (не проверен)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Полный цикл «промышленник → производитель → дистрибьютор»: разработка и производство под ключ для чужих брендов (CDMO / контрактное производство, в т.ч. private label для сетей) + свои марки. Категории: уход и косметика, парфюмерия, гигиена/салфетки, декоративная косметика (макияж). Собственная R&amp;D-лаборатория, выдув флаконов PE/PET, логистическая платформа</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Шартр, Франция</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Флаер со стенда: «Créateur de beauté, partenaire de confiance», значки сертификатов (ISO, GMP и др.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ни с кем не познакомились — фото стенда и флаера</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Крупная группа: 2000+ сотрудников, ~7 производственных площадок (6 во Франции + 1 в Польше), ~300 000 м², продажи в 80 странах. Ок. 20 собственных марок: Corine de Farme, Cottage, Inessance Paris, Jacomo, Mitosyl и др. В 2023 купили Sarbec Cosmetics (700 сотрудников). Парфюмерные экстракты формулируют в Грасе. Гендиректор — Arnaud Linquette. Внимание: в сети были фейковые вакансии от имени «Vabel cosmétique» — проверять контакты по официальному сайту.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.premiumbeautynews.com/vabel-further-expands-its-vertical,27593 ; https://www.lejournaldesentreprises.com/breve/sarbec-cosmetics-passe-aux-mains-du-groupe-vabel-2069305 ; https://www.lsa-conso.fr/noel-de-corine-de-farme-a-cottage-le-groupe-vabel-cultive-l-art-des-parfums-a-la-francaise,462947 ; https://www.parispackagingweek.com/en/exhibitor/vabel-groupe-2/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Узнать условия контрактного производства (MOQ, сроки, декоративная косметика), найти контакт отдела CDMO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">photos/004_vabel.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">Япония</t>
@@ -701,7 +737,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:V4"/>
+  <dimension ref="A1:V5"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -913,30 +949,28 @@
         <v>54</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="E4" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="G4" s="2"/>
+      <c r="H4" s="2" t="s">
         <v>59</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>61</v>
       </c>
       <c r="I4" s="2"/>
       <c r="J4" s="2"/>
@@ -944,38 +978,94 @@
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
       <c r="N4" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="P4" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="O4" s="2" t="s">
+      <c r="Q4" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="P4" s="2" t="s">
+      <c r="R4" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="Q4" s="2" t="s">
+      <c r="S4" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="R4" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="S4" s="2" t="s">
-        <v>67</v>
       </c>
       <c r="T4" s="2"/>
       <c r="U4" s="2" t="s">
         <v>38</v>
       </c>
       <c r="V4" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>68</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="I5" s="2"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="T5" s="2"/>
+      <c r="U5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="V5" s="2" t="s">
+        <v>80</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V4"/>
+  <autoFilter ref="A1:V5"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1" display="www.kava.cn"/>
     <hyperlink ref="F3" r:id="rId2" display="www.effervescence-lab.com"/>
-    <hyperlink ref="F4" r:id="rId3" display="https://iwasecosfa.eu"/>
-    <hyperlink ref="G4" r:id="rId4" display="https://iwasecosfa-eu.covalo.com/"/>
+    <hyperlink ref="F5" r:id="rId3" display="https://iwasecosfa.eu"/>
+    <hyperlink ref="G5" r:id="rId4" display="https://iwasecosfa-eu.covalo.com/"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1006,10 +1096,10 @@
         <v>1</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>70</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1017,11 +1107,11 @@
         <v>22</v>
       </c>
       <c r="B2" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$4,A2)</f>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$5,A2)</f>
         <v>1</v>
       </c>
       <c r="C2" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$4,A2,Контакты!$T$2:$T$4,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$5,A2,Контакты!$T$2:$T$5,"Высокий")</f>
         <v>1</v>
       </c>
     </row>
@@ -1030,34 +1120,34 @@
         <v>40</v>
       </c>
       <c r="B3" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$4,A3)</f>
-        <v>1</v>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$5,A3)</f>
+        <v>2</v>
       </c>
       <c r="C3" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$4,A3,Контакты!$T$2:$T$4,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$5,A3,Контакты!$T$2:$T$5,"Высокий")</f>
         <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="B4" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$4,A4)</f>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$5,A4)</f>
         <v>1</v>
       </c>
       <c r="C4" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$4,A4,Контакты!$T$2:$T$4,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$5,A4,Контакты!$T$2:$T$5,"Высокий")</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="B5" s="7" t="n">
         <f aca="false">SUM(B2:B4)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" s="7" t="n">
         <f aca="false">SUM(C2:C4)</f>

--- a/exhibition/contacts.xlsx
+++ b/exhibition/contacts.xlsx
@@ -12,7 +12,7 @@
     <sheet name="По странам" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Контакты!$A$1:$V$5</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Контакты!$A$1:$W$7</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="123">
   <si>
     <t xml:space="preserve">№</t>
   </si>
@@ -32,6 +32,9 @@
     <t xml:space="preserve">Страна производства</t>
   </si>
   <si>
+    <t xml:space="preserve">Тип компании</t>
+  </si>
+  <si>
     <t xml:space="preserve">Город / регион</t>
   </si>
   <si>
@@ -92,9 +95,75 @@
     <t xml:space="preserve">Фото</t>
   </si>
   <si>
+    <t xml:space="preserve">Германия</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Логистика</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Головной офис группы: Кемптен, Германия. Французский офис: Шанверри (Вандея); косметический склад — Жанвиль-ан-Бос</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DACHSER France S.A.S. (DACHSER Cosmetics Logistics)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cosmetic 360</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.dachser.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.dachser.com/en/cosmetic-logistics</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Логистика для косметики и парфюмерии: доставка по Европе и миру, контрактное складирование, авиа- и морские перевозки. Доп. услуги: распаковка паллет, возвраты и нераспроданное, сборка и установка дисплеев, комплектация коробок</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alexandre Ilias</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Business Development Manager, DACHSER Cosmetics Logistics — Франция, Магриб, Турция</t>
+  </si>
+  <si>
+    <t xml:space="preserve">alexandre.ilias@dachser.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+33 6 07 86 48 57</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DACHSER France S.A.S., Regional Head Office France &amp; Maghreb, 1 avenue de l'Europe, CS 80007 – La Verrie, 85130 Chanverrie, Франция</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Визитка</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Не общались — взяли визитку на всякий случай</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DACHSER — крупный немецкий логистический оператор. Отраслевое решение Cosmetics Logistics запущено сначала во Франции, затем в Испании и Португалии. Склады заточены под косметику, прямой доступ к европейской транспортной сети. Оценка EcoVadis, статус Full AEO (упрощённое таможенное оформление), ISO 27001; видеонаблюдение на складах, мониторинг машин; электромобили для доставки.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.dachser.com/en/cosmetic-logistics ; https://www.cosmetic-valley.com/en/annuaire-entreprises/dachser-cosmetics-logistics ; https://www.dachser.com/en/mediaroom/Cosmetics-in-expert-hands-21097 ; https://www.industries-cosmetiques.fr/en/a-new-logistics-solution-for-cosmetics-professionals/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">На случай поставок из Франции/ЕС: запросить условия и тарифы на доставку и складирование</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Низкий</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">photos/005_dachser.jpg</t>
+  </si>
+  <si>
     <t xml:space="preserve">Китай</t>
   </si>
   <si>
+    <t xml:space="preserve">Упаковка</t>
+  </si>
+  <si>
     <t xml:space="preserve">Куньшань, пров. Цзянсу (≈50 км от Шанхая)</t>
   </si>
   <si>
@@ -140,15 +209,63 @@
     <t xml:space="preserve">Высокий</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-14</t>
-  </si>
-  <si>
     <t xml:space="preserve">photos/001_kava.jpg</t>
   </si>
   <si>
+    <t xml:space="preserve">Контрактное производство</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Хучжоу, пров. Чжэцзян (фабрика); офис — Линьань (Ханчжоу), Чжэцзян</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lamer Beauty (Huzhou) Co., Ltd / Zhejiang Bohan International Co., Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cosmetic 360, «Beauty Ville» (китайская зона)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">www.lamerbeauty.uk ; www.rsgroup.cn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Вероятно ODM/контрактное производство косметики (по данным о группе Lamer: парфюмерия, уход, декоративная косметика). Уточнить ассортимент</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Freda Tang</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CEO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hzrs@rsgroup.cn ; hzrs@hzlamer.com (размыто — проверить)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mob/WhatsApp: +86 153 0571 6666 ; +86 138 5801 7730 (размыто — проверить)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Офис: RM2805, Yuanxin Starry Center, Dayuan Road, Qingshanhu Sub-district, Lin'an District, Zhejiang 311300. Фабрика: No.20 Yangshanwu Road, Daixi Town, Wuxing District, Huzhou, Zhejiang 313000 (адреса размыты — проверить)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Зашли на стенд, взяли контакты. Продукты для губ — со слов компании «легко сделать». Интересует также разработка парфюмов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Сайт lamerbeauty.uk указывает на группу Lamer (Великобритания): её дочерняя компания Hangzhou Lamer Cosmetics делает ODM — парфюмерию, уход, косметику; выставлялась на InterCHARM 2019 (Москва). Линьань — район Ханчжоу, так что это, скорее всего, та же группа. Про Lamer Beauty (Huzhou) и Zhejiang Bohan отдельной информации не найдено.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://prnewswire.co.uk/news-releases/chinese-cosmetics-giant-hangzhou-lamer-cosmetics-debuts-at-intercharm-2019-872021252.html</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Написать в WhatsApp Freda Tang: каталог; парфюм — свой ли завод и парфюмеры, сертификаты IFRA; губы — образцы, MOQ, сроки; документы для ЕС (GMP ISO 22716, CPSR/PIF); условия ODM под наш бренд</t>
+  </si>
+  <si>
+    <t xml:space="preserve">photos/006_lamer_beauty.jpg</t>
+  </si>
+  <si>
     <t xml:space="preserve">Франция</t>
   </si>
   <si>
+    <t xml:space="preserve">Разработка формул (R&amp;D)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Авиньон</t>
   </si>
   <si>
@@ -230,13 +347,13 @@
     <t xml:space="preserve">Япония</t>
   </si>
   <si>
+    <t xml:space="preserve">Сырьё / ингредиенты</t>
+  </si>
+  <si>
     <t xml:space="preserve">Европейский офис: Леваллуа-Перре (пригород Парижа), Франция. Головной офис: Токио</t>
   </si>
   <si>
     <t xml:space="preserve">Iwase Cosfa Europe (группа Iwase Cosfa)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cosmetic 360</t>
   </si>
   <si>
     <t xml:space="preserve">https://iwasecosfa.eu</t>
@@ -737,28 +854,29 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:V5"/>
+  <dimension ref="A1:W7"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="45"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="9" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="36"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="50"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="32"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="20" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="28"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="45"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="10" style="0" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="20" style="0" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="21" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="18"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -828,244 +946,396 @@
       <c r="V1" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="2" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="113.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" s="2"/>
-      <c r="F2" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>26</v>
       </c>
+      <c r="F2" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>29</v>
+      </c>
       <c r="I2" s="2" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>29</v>
-      </c>
+        <v>31</v>
+      </c>
+      <c r="K2" s="2"/>
       <c r="L2" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="M2" s="2"/>
+        <v>32</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>33</v>
+      </c>
       <c r="N2" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>42</v>
+      </c>
+      <c r="W2" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>41</v>
+        <v>45</v>
       </c>
       <c r="D3" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F3" s="2"/>
+      <c r="G3" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="H3" s="2"/>
+      <c r="I3" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="N3" s="2"/>
+      <c r="O3" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="V3" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E3" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="T3" s="2"/>
-      <c r="U3" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V3" s="2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="W3" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
+        <v>65</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>68</v>
+      </c>
       <c r="K4" s="2"/>
-      <c r="L4" s="2"/>
-      <c r="M4" s="2"/>
+      <c r="L4" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>70</v>
+      </c>
       <c r="N4" s="2" t="s">
-        <v>60</v>
+        <v>71</v>
       </c>
       <c r="O4" s="2" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>64</v>
+        <v>74</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="T4" s="2"/>
-      <c r="U4" s="2" t="s">
-        <v>38</v>
-      </c>
+        <v>75</v>
+      </c>
+      <c r="T4" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="U4" s="2"/>
       <c r="V4" s="2" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>42</v>
+      </c>
+      <c r="W4" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>68</v>
+        <v>79</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>69</v>
+        <v>80</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>71</v>
+        <v>81</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>82</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="I5" s="2"/>
+        <v>83</v>
+      </c>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2" t="s">
+        <v>84</v>
+      </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
+      <c r="M5" s="2" t="s">
+        <v>85</v>
+      </c>
       <c r="N5" s="2" t="s">
-        <v>74</v>
+        <v>86</v>
       </c>
       <c r="O5" s="2" t="s">
-        <v>75</v>
+        <v>87</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="R5" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="T5" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="U5" s="2"/>
+      <c r="V5" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="W5" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="S5" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="T5" s="2"/>
-      <c r="U5" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="V5" s="2" t="s">
-        <v>80</v>
+      <c r="C6" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="2"/>
+      <c r="M6" s="2"/>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q6" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="R6" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="S6" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="T6" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="U6" s="2"/>
+      <c r="V6" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="W6" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2"/>
+      <c r="L7" s="2"/>
+      <c r="M7" s="2"/>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="T7" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="U7" s="2"/>
+      <c r="V7" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="W7" s="2" t="s">
+        <v>119</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:V5"/>
+  <autoFilter ref="A1:W7"/>
   <hyperlinks>
-    <hyperlink ref="F2" r:id="rId1" display="www.kava.cn"/>
-    <hyperlink ref="F3" r:id="rId2" display="www.effervescence-lab.com"/>
-    <hyperlink ref="F5" r:id="rId3" display="https://iwasecosfa.eu"/>
-    <hyperlink ref="G5" r:id="rId4" display="https://iwasecosfa-eu.covalo.com/"/>
+    <hyperlink ref="G2" r:id="rId1" display="https://www.dachser.fr"/>
+    <hyperlink ref="H2" r:id="rId2" display="https://www.dachser.com/en/cosmetic-logistics"/>
+    <hyperlink ref="G3" r:id="rId3" display="www.kava.cn"/>
+    <hyperlink ref="G4" r:id="rId4" display="www.lamerbeauty.uk ; www.rsgroup.cn"/>
+    <hyperlink ref="G5" r:id="rId5" display="www.effervescence-lab.com"/>
+    <hyperlink ref="G7" r:id="rId6" display="https://iwasecosfa.eu"/>
+    <hyperlink ref="H7" r:id="rId7" display="https://iwasecosfa-eu.covalo.com/"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1074,7 +1344,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId5"/>
+  <drawing r:id="rId8"/>
 </worksheet>
 </file>
 
@@ -1083,10 +1353,10 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="28"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20"/>
   </cols>
@@ -1096,63 +1366,140 @@
         <v>1</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>81</v>
+        <v>120</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>82</v>
+        <v>121</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B2" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$5,A2)</f>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$7,A2)</f>
         <v>1</v>
       </c>
       <c r="C2" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$5,A2,Контакты!$T$2:$T$5,"Высокий")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$7,A2,Контакты!$U$2:$U$7,"Высокий")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="6" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="B3" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$5,A3)</f>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$7,A3)</f>
         <v>2</v>
       </c>
       <c r="C3" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$5,A3,Контакты!$T$2:$T$5,"Высокий")</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$7,A3,Контакты!$U$2:$U$7,"Высокий")</f>
+        <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>67</v>
+        <v>78</v>
       </c>
       <c r="B4" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$5,A4)</f>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$7,A4)</f>
+        <v>2</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$7,A4,Контакты!$U$2:$U$7,"Высокий")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="B5" s="6" t="n">
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$7,A5)</f>
         <v>1</v>
       </c>
-      <c r="C4" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$5,A4,Контакты!$T$2:$T$5,"Высокий")</f>
+      <c r="C5" s="6" t="n">
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$7,A5,Контакты!$U$2:$U$7,"Высокий")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="B5" s="7" t="n">
-        <f aca="false">SUM(B2:B4)</f>
-        <v>4</v>
-      </c>
-      <c r="C5" s="7" t="n">
-        <f aca="false">SUM(C2:C4)</f>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="B6" s="7" t="n">
+        <f aca="false">SUM(B2:B5)</f>
+        <v>6</v>
+      </c>
+      <c r="C6" s="7" t="n">
+        <f aca="false">SUM(C2:C5)</f>
         <v>1</v>
       </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6"/>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="C8" s="6"/>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B9" s="6" t="n">
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$7,A9)</f>
+        <v>2</v>
+      </c>
+      <c r="C9" s="6"/>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="6" t="n">
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$7,A10)</f>
+        <v>1</v>
+      </c>
+      <c r="C10" s="6"/>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="6" t="s">
+        <v>79</v>
+      </c>
+      <c r="B11" s="6" t="n">
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$7,A11)</f>
+        <v>1</v>
+      </c>
+      <c r="C11" s="6"/>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="B12" s="6" t="n">
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$7,A12)</f>
+        <v>1</v>
+      </c>
+      <c r="C12" s="6"/>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="B13" s="6" t="n">
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$7,A13)</f>
+        <v>1</v>
+      </c>
+      <c r="C13" s="6"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/exhibition/contacts.xlsx
+++ b/exhibition/contacts.xlsx
@@ -12,7 +12,7 @@
     <sheet name="По странам" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Контакты!$A$1:$W$7</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Контакты!$A$1:$W$8</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="137">
   <si>
     <t xml:space="preserve">№</t>
   </si>
@@ -342,6 +342,48 @@
   </si>
   <si>
     <t xml:space="preserve">photos/004_vabel.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Южная Корея</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Сеул (район Куро-гу)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">COSPLAN Inc. (бренд DERMATHOD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cosmetic 360, стенд LA31 (Innovation Route — Brands &amp; Retail), корейский павильон</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://welcon.kocca.kr/en/directory/company/cosplan-inc--5601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Уход за кожей (skincare), профессиональная косметика. OEM/ODM для других марок: разработка формулы, дизайн и производство под ключ, коллаборации с брендами. Специализация — функциональные упаковки и бьюти-девайсы: запатентованная ампула с микроиглами (airless, одноразовая, для домашнего ухода). Продукты на стенде: Derma Level, Derma EZ Jet, Clearance C4, O2 Tox Peel, Derma Saver Sun Protection, активатор для кожи головы. Парфюма нет; продуктов для губ в источниках не найдено</t>
+  </si>
+  <si>
+    <t xml:space="preserve">На стенде — коммерческий директор (Directeur Commercial, имя на бейдже не читается)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Сеул, Куро-гу, Южная Корея</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Фото стенда</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Производят для других марок; парфюма точно нет, губ, вероятно, тоже нет — в основном skincare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Основана в 2019 г. Все процессы от R&amp;D до дизайна — в головном офисе в Сеуле. Флагман — Dermaijet Multi Effector Ampoule: airless-ампула с микроиглами, длина регулируется в два этапа. Бренд DERMATHOD — профессиональный уход для покупателей и косметологов (пилинги, пилинг-пэды, средства для кожного барьера). В 2026 г. участвовали в Pitti Fragranze (Флоренция) в зоне Code Korea при KOCCA — со skincare, не с парфюмом. Цены, MOQ и клиенты OEM в открытых источниках не найдены.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://welcon.kocca.kr/en/directory/company/cosplan-inc--5601 ; https://welcon.kocca.kr/en/directory/content/dermathod--10859 ; https://fragranze.pittimmagine.com/en/exhibitors/D/dermathod---code-korea ; https://bykinaesthetics.com/pages/dermathod</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Взять контакт коммерческого директора; запросить условия OEM для skincare и ампул с микроиглами (MOQ, сроки, цены)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">photos/007_cosplan.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">Япония</t>
@@ -854,7 +896,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:W7"/>
+  <dimension ref="A1:W8"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -1267,7 +1309,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
@@ -1275,29 +1317,29 @@
         <v>106</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G7" s="4" t="s">
+      <c r="G7" s="2"/>
+      <c r="H7" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="I7" s="2" t="s">
         <v>111</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>112</v>
       </c>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
+      <c r="L7" s="2" t="s">
+        <v>112</v>
+      </c>
       <c r="M7" s="2"/>
       <c r="N7" s="2"/>
       <c r="O7" s="2" t="s">
@@ -1326,16 +1368,76 @@
         <v>119</v>
       </c>
     </row>
+    <row r="8" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="2"/>
+      <c r="M8" s="2"/>
+      <c r="N8" s="2"/>
+      <c r="O8" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="R8" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="S8" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="T8" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="U8" s="2"/>
+      <c r="V8" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="W8" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:W7"/>
+  <autoFilter ref="A1:W8"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1" display="https://www.dachser.fr"/>
     <hyperlink ref="H2" r:id="rId2" display="https://www.dachser.com/en/cosmetic-logistics"/>
     <hyperlink ref="G3" r:id="rId3" display="www.kava.cn"/>
     <hyperlink ref="G4" r:id="rId4" display="www.lamerbeauty.uk ; www.rsgroup.cn"/>
     <hyperlink ref="G5" r:id="rId5" display="www.effervescence-lab.com"/>
-    <hyperlink ref="G7" r:id="rId6" display="https://iwasecosfa.eu"/>
-    <hyperlink ref="H7" r:id="rId7" display="https://iwasecosfa-eu.covalo.com/"/>
+    <hyperlink ref="H7" r:id="rId6" display="https://welcon.kocca.kr/en/directory/company/cosplan-inc--5601"/>
+    <hyperlink ref="G8" r:id="rId7" display="https://iwasecosfa.eu"/>
+    <hyperlink ref="H8" r:id="rId8" display="https://iwasecosfa-eu.covalo.com/"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1344,7 +1446,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId8"/>
+  <drawing r:id="rId9"/>
 </worksheet>
 </file>
 
@@ -1353,7 +1455,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C14"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="28"/>
@@ -1366,10 +1468,10 @@
         <v>1</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>120</v>
+        <v>134</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>121</v>
+        <v>135</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1377,11 +1479,11 @@
         <v>23</v>
       </c>
       <c r="B2" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$7,A2)</f>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$8,A2)</f>
         <v>1</v>
       </c>
       <c r="C2" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$7,A2,Контакты!$U$2:$U$7,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$8,A2,Контакты!$U$2:$U$8,"Высокий")</f>
         <v>0</v>
       </c>
     </row>
@@ -1390,11 +1492,11 @@
         <v>44</v>
       </c>
       <c r="B3" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$7,A3)</f>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$8,A3)</f>
         <v>2</v>
       </c>
       <c r="C3" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$7,A3,Контакты!$U$2:$U$7,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$8,A3,Контакты!$U$2:$U$8,"Высокий")</f>
         <v>1</v>
       </c>
     </row>
@@ -1403,11 +1505,11 @@
         <v>78</v>
       </c>
       <c r="B4" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$7,A4)</f>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$8,A4)</f>
         <v>2</v>
       </c>
       <c r="C4" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$7,A4,Контакты!$U$2:$U$7,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$8,A4,Контакты!$U$2:$U$8,"Высокий")</f>
         <v>0</v>
       </c>
     </row>
@@ -1416,90 +1518,103 @@
         <v>106</v>
       </c>
       <c r="B5" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$7,A5)</f>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$8,A5)</f>
         <v>1</v>
       </c>
       <c r="C5" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$7,A5,Контакты!$U$2:$U$7,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$8,A5,Контакты!$U$2:$U$8,"Высокий")</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="B6" s="7" t="n">
-        <f aca="false">SUM(B2:B5)</f>
-        <v>6</v>
-      </c>
-      <c r="C6" s="7" t="n">
-        <f aca="false">SUM(C2:C5)</f>
+      <c r="A6" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="B6" s="6" t="n">
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$8,A6)</f>
         <v>1</v>
       </c>
+      <c r="C6" s="6" t="n">
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$8,A6,Контакты!$U$2:$U$8,"Высокий")</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6"/>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
+      <c r="A7" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="B7" s="7" t="n">
+        <f aca="false">SUM(B2:B6)</f>
+        <v>7</v>
+      </c>
+      <c r="C7" s="7" t="n">
+        <f aca="false">SUM(C2:C6)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>120</v>
-      </c>
+      <c r="A8" s="6"/>
+      <c r="B8" s="6"/>
       <c r="C8" s="6"/>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="B9" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$7,A9)</f>
         <v>2</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>134</v>
       </c>
       <c r="C9" s="6"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>24</v>
+        <v>62</v>
       </c>
       <c r="B10" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$7,A10)</f>
-        <v>1</v>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$8,A10)</f>
+        <v>3</v>
       </c>
       <c r="C10" s="6"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>79</v>
+        <v>24</v>
       </c>
       <c r="B11" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$7,A11)</f>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$8,A11)</f>
         <v>1</v>
       </c>
       <c r="C11" s="6"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="B12" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$7,A12)</f>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$8,A12)</f>
         <v>1</v>
       </c>
       <c r="C12" s="6"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="B13" s="6" t="n">
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$8,A13)</f>
+        <v>1</v>
+      </c>
+      <c r="C13" s="6"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B13" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$7,A13)</f>
+      <c r="B14" s="6" t="n">
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$8,A14)</f>
         <v>1</v>
       </c>
-      <c r="C13" s="6"/>
+      <c r="C14" s="6"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/exhibition/contacts.xlsx
+++ b/exhibition/contacts.xlsx
@@ -12,7 +12,7 @@
     <sheet name="По странам" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Контакты!$A$1:$W$8</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Контакты!$A$1:$W$9</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="137">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="145">
   <si>
     <t xml:space="preserve">№</t>
   </si>
@@ -384,6 +384,30 @@
   </si>
   <si>
     <t xml:space="preserve">photos/007_cosplan.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">THREEDAYSLOVE Co., Ltd. (бренд EXOMERE / TIME72)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cosmetic 360, стенд LB38 (Innovation Route — Brands &amp; Retail), корейский павильон</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OEM/ODM (указано на стенде) + свой бренд EXOMERE. Технология «спикулы + экзосомы» (запатентована, патент KR 10-2023-0121591; экзосомы из мандарина Халла, о. Чеджу). На стенде: регенерирующие ампулы (EGF, PDRN), восстанавливающий бальзам, кушон со спикулами и экзосомами (тональное средство), сыворотки, кремы, наборы ампул. ISO 9001. «25 лет экспертизы»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Производят для других (со слов: «для коди корея производят» — уточнить, что имелось в виду)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Компании принадлежат товарные знаки TIME72 и «TIME 72 EXOMERE» (поданы в 2024 г., США): косметика, эксфолианты, антивозрастные средства, питательные кремы. Сайта, адреса и подробностей про OEM в открытых источниках не найдено.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://trademark.justia.com/owners/threedayslove-co-ltd-5842403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Взять контакт; запросить условия OEM/ODM: спикулы/экзосомы, кушоны (есть ли другие продукты макияжа, губы), MOQ, сроки</t>
+  </si>
+  <si>
+    <t xml:space="preserve">photos/008_threedayslove.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">Япония</t>
@@ -896,7 +920,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:W8"/>
+  <dimension ref="A1:W9"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -1368,67 +1392,118 @@
         <v>119</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2" t="s">
         <v>122</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G8" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="H8" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>126</v>
       </c>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
-      <c r="O8" s="2" t="s">
-        <v>127</v>
-      </c>
+      <c r="O8" s="2"/>
       <c r="P8" s="2" t="s">
-        <v>128</v>
+        <v>114</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>130</v>
+        <v>124</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>131</v>
+        <v>125</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>132</v>
+        <v>126</v>
       </c>
       <c r="U8" s="2"/>
       <c r="V8" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W8" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="H9" s="4" t="s">
         <v>133</v>
       </c>
+      <c r="I9" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="R9" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="S9" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="T9" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="U9" s="2"/>
+      <c r="V9" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="W9" s="2" t="s">
+        <v>141</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W8"/>
+  <autoFilter ref="A1:W9"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1" display="https://www.dachser.fr"/>
     <hyperlink ref="H2" r:id="rId2" display="https://www.dachser.com/en/cosmetic-logistics"/>
@@ -1436,8 +1511,8 @@
     <hyperlink ref="G4" r:id="rId4" display="www.lamerbeauty.uk ; www.rsgroup.cn"/>
     <hyperlink ref="G5" r:id="rId5" display="www.effervescence-lab.com"/>
     <hyperlink ref="H7" r:id="rId6" display="https://welcon.kocca.kr/en/directory/company/cosplan-inc--5601"/>
-    <hyperlink ref="G8" r:id="rId7" display="https://iwasecosfa.eu"/>
-    <hyperlink ref="H8" r:id="rId8" display="https://iwasecosfa-eu.covalo.com/"/>
+    <hyperlink ref="G9" r:id="rId7" display="https://iwasecosfa.eu"/>
+    <hyperlink ref="H9" r:id="rId8" display="https://iwasecosfa-eu.covalo.com/"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1468,10 +1543,10 @@
         <v>1</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>135</v>
+        <v>143</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1479,11 +1554,11 @@
         <v>23</v>
       </c>
       <c r="B2" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$8,A2)</f>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$9,A2)</f>
         <v>1</v>
       </c>
       <c r="C2" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$8,A2,Контакты!$U$2:$U$8,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$9,A2,Контакты!$U$2:$U$9,"Высокий")</f>
         <v>0</v>
       </c>
     </row>
@@ -1492,11 +1567,11 @@
         <v>44</v>
       </c>
       <c r="B3" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$8,A3)</f>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$9,A3)</f>
         <v>2</v>
       </c>
       <c r="C3" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$8,A3,Контакты!$U$2:$U$8,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$9,A3,Контакты!$U$2:$U$9,"Высокий")</f>
         <v>1</v>
       </c>
     </row>
@@ -1505,11 +1580,11 @@
         <v>78</v>
       </c>
       <c r="B4" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$8,A4)</f>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$9,A4)</f>
         <v>2</v>
       </c>
       <c r="C4" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$8,A4,Контакты!$U$2:$U$8,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$9,A4,Контакты!$U$2:$U$9,"Высокий")</f>
         <v>0</v>
       </c>
     </row>
@@ -1518,34 +1593,34 @@
         <v>106</v>
       </c>
       <c r="B5" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$8,A5)</f>
-        <v>1</v>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$9,A5)</f>
+        <v>2</v>
       </c>
       <c r="C5" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$8,A5,Контакты!$U$2:$U$8,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$9,A5,Контакты!$U$2:$U$9,"Высокий")</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="B6" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$8,A6)</f>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$9,A6)</f>
         <v>1</v>
       </c>
       <c r="C6" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$8,A6,Контакты!$U$2:$U$8,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$9,A6,Контакты!$U$2:$U$9,"Высокий")</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>136</v>
+        <v>144</v>
       </c>
       <c r="B7" s="7" t="n">
         <f aca="false">SUM(B2:B6)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C7" s="7" t="n">
         <f aca="false">SUM(C2:C6)</f>
@@ -1562,7 +1637,7 @@
         <v>2</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="C9" s="6"/>
     </row>
@@ -1571,8 +1646,8 @@
         <v>62</v>
       </c>
       <c r="B10" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$8,A10)</f>
-        <v>3</v>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$9,A10)</f>
+        <v>4</v>
       </c>
       <c r="C10" s="6"/>
     </row>
@@ -1581,7 +1656,7 @@
         <v>24</v>
       </c>
       <c r="B11" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$8,A11)</f>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$9,A11)</f>
         <v>1</v>
       </c>
       <c r="C11" s="6"/>
@@ -1591,17 +1666,17 @@
         <v>79</v>
       </c>
       <c r="B12" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$8,A12)</f>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$9,A12)</f>
         <v>1</v>
       </c>
       <c r="C12" s="6"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="B13" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$8,A13)</f>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$9,A13)</f>
         <v>1</v>
       </c>
       <c r="C13" s="6"/>
@@ -1611,7 +1686,7 @@
         <v>45</v>
       </c>
       <c r="B14" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$8,A14)</f>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$9,A14)</f>
         <v>1</v>
       </c>
       <c r="C14" s="6"/>

--- a/exhibition/contacts.xlsx
+++ b/exhibition/contacts.xlsx
@@ -395,7 +395,7 @@
     <t xml:space="preserve">OEM/ODM (указано на стенде) + свой бренд EXOMERE. Технология «спикулы + экзосомы» (запатентована, патент KR 10-2023-0121591; экзосомы из мандарина Халла, о. Чеджу). На стенде: регенерирующие ампулы (EGF, PDRN), восстанавливающий бальзам, кушон со спикулами и экзосомами (тональное средство), сыворотки, кремы, наборы ампул. ISO 9001. «25 лет экспертизы»</t>
   </si>
   <si>
-    <t xml:space="preserve">Производят для других (со слов: «для коди корея производят» — уточнить, что имелось в виду)</t>
+    <t xml:space="preserve">Производят для других марок косметику для кожи (skincare)</t>
   </si>
   <si>
     <t xml:space="preserve">Компании принадлежат товарные знаки TIME72 и «TIME 72 EXOMERE» (поданы в 2024 г., США): косметика, эксфолианты, антивозрастные средства, питательные кремы. Сайта, адреса и подробностей про OEM в открытых источниках не найдено.</t>
@@ -404,7 +404,7 @@
     <t xml:space="preserve">https://trademark.justia.com/owners/threedayslove-co-ltd-5842403</t>
   </si>
   <si>
-    <t xml:space="preserve">Взять контакт; запросить условия OEM/ODM: спикулы/экзосомы, кушоны (есть ли другие продукты макияжа, губы), MOQ, сроки</t>
+    <t xml:space="preserve">Взять контакт; запросить условия OEM/ODM по уходу за кожей (спикулы/экзосомы, ампулы, кремы), MOQ, сроки; уточнить, делают ли кушоны/макияж</t>
   </si>
   <si>
     <t xml:space="preserve">photos/008_threedayslove.jpg</t>

--- a/exhibition/contacts.xlsx
+++ b/exhibition/contacts.xlsx
@@ -12,7 +12,7 @@
     <sheet name="По странам" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Контакты!$A$1:$W$9</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Контакты!$A$1:$W$10</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="156">
   <si>
     <t xml:space="preserve">№</t>
   </si>
@@ -306,6 +306,39 @@
   </si>
   <si>
     <t xml:space="preserve">photos/002_effervescence_lab.jpg ; photos/002b_effervescence_lab_brochure.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Марсель</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laboratoires Biotic Phocea</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cosmetic 360, стенд GC58 (Innovation Route — Formulation)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">biotic.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Private label под ключ (full service), Made in France: готовые или индивидуальные формулы; R&amp;D, упаковка, регуляторика, тесты. Производство от 400 шт. Натуральная и органическая (bio) косметика. На стенде: сыворотки (Dark Spot Serum — от пигментных пятен), масла/эликсиры во флаконах-капельницах, бальзамы, кремы; есть линейка для салонов красоты</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16-18 Boulevard Michelet, 13008 Marseille, Франция (по открытым источникам; в справочнике Cosmebio — Immeuble Le Performance, 13008 Marseille)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Фото стенда; на стенде QR-код на форму обратной связи</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Более 10 лет специализируются на производстве натуральной и органической косметики под чужой маркой для малых и средних компаний и брендов. Есть готовая линейка «под ваш бренд» и разработка по ТЗ. Член ассоциации Cosmebio (органическая косметика). Развивают экспорт и R&amp;D.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.cosmebio.org/en/professional-information/cosmebio-members-directory/952/ ; https://www.lejournaldesentreprises.com/article/marseille-le-laboratoire-biotic-phocea-lance-une-gamme-de-cosmetiques-personnalisable-pour-les-103794 ; https://www.cosmed.fr/societes/biotic-phocea-laboratoires ; https://www.lejournaldesentreprises.com/article/coronavirus-les-laboratoires-biotic-phocea-misent-sur-lexport-et-la-rd-488787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Запросить каталог готовых формул и цены от 400 шт.; уточнить, делают ли продукты для губ и парфюм</t>
+  </si>
+  <si>
+    <t xml:space="preserve">photos/009_biotic_phocea.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">Шартр (головной офис); производство — О-де-Франс (Невиль-ан-Феррен, под Лиллем), Нормандия; 1 завод в Польше</t>
@@ -920,7 +953,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:W9"/>
+  <dimension ref="A1:W10"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -1313,206 +1346,261 @@
       <c r="P6" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="Q6" s="2" t="s">
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="R6" s="2" t="s">
+      <c r="S6" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="S6" s="2" t="s">
+      <c r="T6" s="2" t="s">
         <v>103</v>
-      </c>
-      <c r="T6" s="2" t="s">
-        <v>104</v>
       </c>
       <c r="U6" s="2"/>
       <c r="V6" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W6" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>106</v>
+        <v>78</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>62</v>
       </c>
       <c r="D7" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="G7" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="H7" s="2"/>
+      <c r="I7" s="2" t="s">
         <v>109</v>
-      </c>
-      <c r="G7" s="2"/>
-      <c r="H7" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>111</v>
       </c>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
-      <c r="L7" s="2" t="s">
-        <v>112</v>
-      </c>
+      <c r="L7" s="2"/>
       <c r="M7" s="2"/>
       <c r="N7" s="2"/>
       <c r="O7" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="R7" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="P7" s="2" t="s">
+      <c r="S7" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="Q7" s="2" t="s">
+      <c r="T7" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="R7" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="S7" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="T7" s="2" t="s">
-        <v>118</v>
       </c>
       <c r="U7" s="2"/>
       <c r="V7" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W7" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D8" s="2"/>
+      <c r="D8" s="2" t="s">
+        <v>118</v>
+      </c>
       <c r="E8" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="G8" s="2"/>
+      <c r="H8" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
       <c r="I8" s="2" t="s">
         <v>122</v>
       </c>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
+      <c r="L8" s="2" t="s">
+        <v>123</v>
+      </c>
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
-      <c r="O8" s="2"/>
+      <c r="O8" s="2" t="s">
+        <v>124</v>
+      </c>
       <c r="P8" s="2" t="s">
-        <v>114</v>
+        <v>125</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="U8" s="2"/>
       <c r="V8" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W8" s="2" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>130</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="D9" s="2"/>
       <c r="E9" s="2" t="s">
         <v>131</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G9" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2" t="s">
         <v>133</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>134</v>
       </c>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
-      <c r="O9" s="2" t="s">
+      <c r="O9" s="2"/>
+      <c r="P9" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="R9" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="P9" s="2" t="s">
+      <c r="S9" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="Q9" s="2" t="s">
+      <c r="T9" s="2" t="s">
         <v>137</v>
-      </c>
-      <c r="R9" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="S9" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="T9" s="2" t="s">
-        <v>140</v>
       </c>
       <c r="U9" s="2"/>
       <c r="V9" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W9" s="2" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>141</v>
       </c>
+      <c r="E10" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="2"/>
+      <c r="M10" s="2"/>
+      <c r="N10" s="2"/>
+      <c r="O10" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="Q10" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="R10" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="S10" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="T10" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="U10" s="2"/>
+      <c r="V10" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="W10" s="2" t="s">
+        <v>152</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W9"/>
+  <autoFilter ref="A1:W10"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1" display="https://www.dachser.fr"/>
     <hyperlink ref="H2" r:id="rId2" display="https://www.dachser.com/en/cosmetic-logistics"/>
     <hyperlink ref="G3" r:id="rId3" display="www.kava.cn"/>
     <hyperlink ref="G4" r:id="rId4" display="www.lamerbeauty.uk ; www.rsgroup.cn"/>
     <hyperlink ref="G5" r:id="rId5" display="www.effervescence-lab.com"/>
-    <hyperlink ref="H7" r:id="rId6" display="https://welcon.kocca.kr/en/directory/company/cosplan-inc--5601"/>
-    <hyperlink ref="G9" r:id="rId7" display="https://iwasecosfa.eu"/>
-    <hyperlink ref="H9" r:id="rId8" display="https://iwasecosfa-eu.covalo.com/"/>
+    <hyperlink ref="H8" r:id="rId6" display="https://welcon.kocca.kr/en/directory/company/cosplan-inc--5601"/>
+    <hyperlink ref="G10" r:id="rId7" display="https://iwasecosfa.eu"/>
+    <hyperlink ref="H10" r:id="rId8" display="https://iwasecosfa-eu.covalo.com/"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1543,10 +1631,10 @@
         <v>1</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>143</v>
+        <v>154</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1554,11 +1642,11 @@
         <v>23</v>
       </c>
       <c r="B2" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$9,A2)</f>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$10,A2)</f>
         <v>1</v>
       </c>
       <c r="C2" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$9,A2,Контакты!$U$2:$U$9,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$10,A2,Контакты!$U$2:$U$10,"Высокий")</f>
         <v>0</v>
       </c>
     </row>
@@ -1567,11 +1655,11 @@
         <v>44</v>
       </c>
       <c r="B3" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$9,A3)</f>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$10,A3)</f>
         <v>2</v>
       </c>
       <c r="C3" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$9,A3,Контакты!$U$2:$U$9,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$10,A3,Контакты!$U$2:$U$10,"Высокий")</f>
         <v>1</v>
       </c>
     </row>
@@ -1580,47 +1668,47 @@
         <v>78</v>
       </c>
       <c r="B4" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$9,A4)</f>
-        <v>2</v>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$10,A4)</f>
+        <v>3</v>
       </c>
       <c r="C4" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$9,A4,Контакты!$U$2:$U$9,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$10,A4,Контакты!$U$2:$U$10,"Высокий")</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="B5" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$9,A5)</f>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$10,A5)</f>
         <v>2</v>
       </c>
       <c r="C5" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$9,A5,Контакты!$U$2:$U$9,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$10,A5,Контакты!$U$2:$U$10,"Высокий")</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>128</v>
+        <v>139</v>
       </c>
       <c r="B6" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$9,A6)</f>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$10,A6)</f>
         <v>1</v>
       </c>
       <c r="C6" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$9,A6,Контакты!$U$2:$U$9,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$10,A6,Контакты!$U$2:$U$10,"Высокий")</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>144</v>
+        <v>155</v>
       </c>
       <c r="B7" s="7" t="n">
         <f aca="false">SUM(B2:B6)</f>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C7" s="7" t="n">
         <f aca="false">SUM(C2:C6)</f>
@@ -1637,7 +1725,7 @@
         <v>2</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>142</v>
+        <v>153</v>
       </c>
       <c r="C9" s="6"/>
     </row>
@@ -1646,8 +1734,8 @@
         <v>62</v>
       </c>
       <c r="B10" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$9,A10)</f>
-        <v>4</v>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$10,A10)</f>
+        <v>5</v>
       </c>
       <c r="C10" s="6"/>
     </row>
@@ -1656,7 +1744,7 @@
         <v>24</v>
       </c>
       <c r="B11" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$9,A11)</f>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$10,A11)</f>
         <v>1</v>
       </c>
       <c r="C11" s="6"/>
@@ -1666,17 +1754,17 @@
         <v>79</v>
       </c>
       <c r="B12" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$9,A12)</f>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$10,A12)</f>
         <v>1</v>
       </c>
       <c r="C12" s="6"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>129</v>
+        <v>140</v>
       </c>
       <c r="B13" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$9,A13)</f>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$10,A13)</f>
         <v>1</v>
       </c>
       <c r="C13" s="6"/>
@@ -1686,7 +1774,7 @@
         <v>45</v>
       </c>
       <c r="B14" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$9,A14)</f>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$10,A14)</f>
         <v>1</v>
       </c>
       <c r="C14" s="6"/>

--- a/exhibition/contacts.xlsx
+++ b/exhibition/contacts.xlsx
@@ -12,7 +12,7 @@
     <sheet name="По странам" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Контакты!$A$1:$W$10</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Контакты!$A$1:$W$11</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="166">
   <si>
     <t xml:space="preserve">№</t>
   </si>
@@ -308,6 +308,39 @@
     <t xml:space="preserve">photos/002_effervescence_lab.jpg ; photos/002b_effervescence_lab_brochure.jpg</t>
   </si>
   <si>
+    <t xml:space="preserve">Сырьё / ингредиенты</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Лион (головной офис); лаборатория и склад — Сен-Вюльба (Эн)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Formulance Group (Groupe Formulance)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cosmetic 360, стенд GB51 (Innovation Route — Raw Materials)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Дистрибьютор косметического сырья. Направления со стенда: устойчивые альтернативы (био-пигменты чёрного цвета, натуральные замены синтетике, веганская замена ланолину, замена баттерам, 100% растительный воск); натуральные ингредиенты (эфирные и растительные масла, гидролаты, CO2-экстракты, растительные экстракты, натуральные активы); микрокапсулирование (активов и отдушек, под ключ); сырьё для ароматов и вкусов (fragrance &amp; flavour); защитные углеводороды (вазелин, парафины, белое масло); полимеры (замутнители, кондиционеры, загустители). На стенде — образцы ароматического сырья: ветивер, сандал Muhuhu, африканский бессмертник, белая вербена, Resurrection Bush; замены силикона (SILIKE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13 rue des Émeraudes, Лион, Франция (индекс 69006 или 69000 — уточнить)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Фото стенда; QR-код на их LinkedIn; буклет «Jungle Forever» (сохранение тропических лесов)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Основана в 2013 г. 4 направления: промышленность, здравоохранение, ингредиенты, парфюмерия (Fragrance). Есть натуральные замены силиконам, активы, пигменты, эфирные масла, цветочные воды, растительные масла. EcoVadis Silver, ISO 9001:2015. Полезны как поставщик сырья для парфюма (натуральные ароматические компоненты).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.cosmetic-valley.com/en/annuaire-entreprises/groupe-formulance ; https://cdn-assets.inwink.com/29c113f5-ef83-40fc-9c73-90e2bb328e9c/9673b4e4-74d3-47f5-b854-5daec598b6a6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Найти контакт (сайт / LinkedIn); запросить каталог, особенно парфюмерное сырьё и натуральные замены — если пойдём в разработку парфюма</t>
+  </si>
+  <si>
+    <t xml:space="preserve">photos/010_formulance.jpg</t>
+  </si>
+  <si>
     <t xml:space="preserve">Марсель</t>
   </si>
   <si>
@@ -444,9 +477,6 @@
   </si>
   <si>
     <t xml:space="preserve">Япония</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Сырьё / ингредиенты</t>
   </si>
   <si>
     <t xml:space="preserve">Европейский офис: Леваллуа-Перре (пригород Парижа), Франция. Головной офис: Токио</t>
@@ -953,7 +983,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:W10"/>
+  <dimension ref="A1:W11"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -1309,7 +1339,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="180.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
@@ -1317,20 +1347,18 @@
         <v>78</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="G6" s="2" t="s">
         <v>97</v>
       </c>
+      <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2" t="s">
         <v>98</v>
@@ -1401,206 +1429,261 @@
       <c r="P7" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="Q7" s="2" t="s">
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="R7" s="2" t="s">
+      <c r="S7" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="S7" s="2" t="s">
+      <c r="T7" s="2" t="s">
         <v>114</v>
-      </c>
-      <c r="T7" s="2" t="s">
-        <v>115</v>
       </c>
       <c r="U7" s="2"/>
       <c r="V7" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W7" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>117</v>
+        <v>78</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>62</v>
       </c>
       <c r="D8" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="G8" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="H8" s="2"/>
+      <c r="I8" s="2" t="s">
         <v>120</v>
-      </c>
-      <c r="G8" s="2"/>
-      <c r="H8" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>122</v>
       </c>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
-      <c r="L8" s="2" t="s">
-        <v>123</v>
-      </c>
+      <c r="L8" s="2"/>
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
       <c r="O8" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="R8" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="P8" s="2" t="s">
+      <c r="S8" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="Q8" s="2" t="s">
+      <c r="T8" s="2" t="s">
         <v>126</v>
-      </c>
-      <c r="R8" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="S8" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="T8" s="2" t="s">
-        <v>129</v>
       </c>
       <c r="U8" s="2"/>
       <c r="V8" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W8" s="2" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D9" s="2"/>
+      <c r="D9" s="2" t="s">
+        <v>129</v>
+      </c>
       <c r="E9" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="F9" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="G9" s="2"/>
+      <c r="H9" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
       <c r="I9" s="2" t="s">
         <v>133</v>
       </c>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
-      <c r="L9" s="2"/>
+      <c r="L9" s="2" t="s">
+        <v>134</v>
+      </c>
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
-      <c r="O9" s="2"/>
+      <c r="O9" s="2" t="s">
+        <v>135</v>
+      </c>
       <c r="P9" s="2" t="s">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="U9" s="2"/>
       <c r="V9" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W9" s="2" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>141</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="D10" s="2"/>
       <c r="E10" s="2" t="s">
         <v>142</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G10" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="G10" s="2"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2" t="s">
         <v>144</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>145</v>
       </c>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
-      <c r="O10" s="2" t="s">
+      <c r="O10" s="2"/>
+      <c r="P10" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="Q10" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="R10" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="P10" s="2" t="s">
+      <c r="S10" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="Q10" s="2" t="s">
+      <c r="T10" s="2" t="s">
         <v>148</v>
-      </c>
-      <c r="R10" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="S10" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="T10" s="2" t="s">
-        <v>151</v>
       </c>
       <c r="U10" s="2"/>
       <c r="V10" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W10" s="2" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>152</v>
       </c>
+      <c r="F11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G11" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="2"/>
+      <c r="M11" s="2"/>
+      <c r="N11" s="2"/>
+      <c r="O11" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="R11" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="S11" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="T11" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="U11" s="2"/>
+      <c r="V11" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="W11" s="2" t="s">
+        <v>162</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W10"/>
+  <autoFilter ref="A1:W11"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1" display="https://www.dachser.fr"/>
     <hyperlink ref="H2" r:id="rId2" display="https://www.dachser.com/en/cosmetic-logistics"/>
     <hyperlink ref="G3" r:id="rId3" display="www.kava.cn"/>
     <hyperlink ref="G4" r:id="rId4" display="www.lamerbeauty.uk ; www.rsgroup.cn"/>
     <hyperlink ref="G5" r:id="rId5" display="www.effervescence-lab.com"/>
-    <hyperlink ref="H8" r:id="rId6" display="https://welcon.kocca.kr/en/directory/company/cosplan-inc--5601"/>
-    <hyperlink ref="G10" r:id="rId7" display="https://iwasecosfa.eu"/>
-    <hyperlink ref="H10" r:id="rId8" display="https://iwasecosfa-eu.covalo.com/"/>
+    <hyperlink ref="H9" r:id="rId6" display="https://welcon.kocca.kr/en/directory/company/cosplan-inc--5601"/>
+    <hyperlink ref="G11" r:id="rId7" display="https://iwasecosfa.eu"/>
+    <hyperlink ref="H11" r:id="rId8" display="https://iwasecosfa-eu.covalo.com/"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1631,10 +1714,10 @@
         <v>1</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1642,11 +1725,11 @@
         <v>23</v>
       </c>
       <c r="B2" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$10,A2)</f>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$11,A2)</f>
         <v>1</v>
       </c>
       <c r="C2" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$10,A2,Контакты!$U$2:$U$10,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$11,A2,Контакты!$U$2:$U$11,"Высокий")</f>
         <v>0</v>
       </c>
     </row>
@@ -1655,11 +1738,11 @@
         <v>44</v>
       </c>
       <c r="B3" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$10,A3)</f>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$11,A3)</f>
         <v>2</v>
       </c>
       <c r="C3" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$10,A3,Контакты!$U$2:$U$10,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$11,A3,Контакты!$U$2:$U$11,"Высокий")</f>
         <v>1</v>
       </c>
     </row>
@@ -1668,47 +1751,47 @@
         <v>78</v>
       </c>
       <c r="B4" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$10,A4)</f>
-        <v>3</v>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$11,A4)</f>
+        <v>4</v>
       </c>
       <c r="C4" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$10,A4,Контакты!$U$2:$U$10,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$11,A4,Контакты!$U$2:$U$11,"Высокий")</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>117</v>
+        <v>128</v>
       </c>
       <c r="B5" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$10,A5)</f>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$11,A5)</f>
         <v>2</v>
       </c>
       <c r="C5" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$10,A5,Контакты!$U$2:$U$10,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$11,A5,Контакты!$U$2:$U$11,"Высокий")</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>139</v>
+        <v>150</v>
       </c>
       <c r="B6" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$10,A6)</f>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$11,A6)</f>
         <v>1</v>
       </c>
       <c r="C6" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$10,A6,Контакты!$U$2:$U$10,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$11,A6,Контакты!$U$2:$U$11,"Высокий")</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="B7" s="7" t="n">
         <f aca="false">SUM(B2:B6)</f>
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C7" s="7" t="n">
         <f aca="false">SUM(C2:C6)</f>
@@ -1725,7 +1808,7 @@
         <v>2</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="C9" s="6"/>
     </row>
@@ -1734,7 +1817,7 @@
         <v>62</v>
       </c>
       <c r="B10" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$10,A10)</f>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$11,A10)</f>
         <v>5</v>
       </c>
       <c r="C10" s="6"/>
@@ -1744,7 +1827,7 @@
         <v>24</v>
       </c>
       <c r="B11" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$10,A11)</f>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$11,A11)</f>
         <v>1</v>
       </c>
       <c r="C11" s="6"/>
@@ -1754,18 +1837,18 @@
         <v>79</v>
       </c>
       <c r="B12" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$10,A12)</f>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$11,A12)</f>
         <v>1</v>
       </c>
       <c r="C12" s="6"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>140</v>
+        <v>94</v>
       </c>
       <c r="B13" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$10,A13)</f>
-        <v>1</v>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$11,A13)</f>
+        <v>2</v>
       </c>
       <c r="C13" s="6"/>
     </row>
@@ -1774,7 +1857,7 @@
         <v>45</v>
       </c>
       <c r="B14" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$10,A14)</f>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$11,A14)</f>
         <v>1</v>
       </c>
       <c r="C14" s="6"/>

--- a/exhibition/contacts.xlsx
+++ b/exhibition/contacts.xlsx
@@ -12,7 +12,7 @@
     <sheet name="По странам" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Контакты!$A$1:$W$11</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Контакты!$A$1:$W$12</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="177">
   <si>
     <t xml:space="preserve">№</t>
   </si>
@@ -263,6 +263,42 @@
     <t xml:space="preserve">Франция</t>
   </si>
   <si>
+    <t xml:space="preserve">Под Парижем (рядом с аэропортом Руасси — Шарль-де-Голль); есть также производство в Азии</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desjardin Metal Packaging</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.desjardin.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.desjardin.fr/en/categories/cosmetic-packaging</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Металлическая упаковка (жесть и алюминий) под заказ: круглые баночки с винтовой или надвижной крышкой, прямоугольные и овальные формы, крышки (в т.ч. для стеклянных банок), подарочные коробки, тревел-баночки, вакуумные жестяные контейнеры для сырья. Стандарт или индивидуальная печать/отделка. Подходит для бальзамов, кремов, твёрдых продуктов, бальзамов для губ, подарочных наборов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">contact@desjardin.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Франция, рядом с аэропортом Paris Roissy-Charles-de-Gaulle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Фото стенда</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Работают с 1848 г. Делают металлическую упаковку для фармы, косметики, еды и напитков. Партии от 5 000 шт. до нескольких миллионов. На стенде — упаковка для известных брендов: L'Occitane, Roger &amp; Gallet, Biolane, Babor, La Biosthétique, Pommade Nova и др.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.desjardin.fr/about-us?hsLang=en ; https://www.desjardin.fr/en/categories/cosmetic-packaging ; https://www.desjardin.fr/en/our-history</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Если нужны металлические баночки (бальзамы, твёрдые средства, подарочные наборы): написать на contact@desjardin.fr, запросить каталог и цены от 5 000 шт.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">photos/011_desjardin.jpg</t>
+  </si>
+  <si>
     <t xml:space="preserve">Разработка формул (R&amp;D)</t>
   </si>
   <si>
@@ -432,9 +468,6 @@
   </si>
   <si>
     <t xml:space="preserve">Сеул, Куро-гу, Южная Корея</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Фото стенда</t>
   </si>
   <si>
     <t xml:space="preserve">Производят для других марок; парфюма точно нет, губ, вероятно, тоже нет — в основном skincare</t>
@@ -983,7 +1016,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:W11"/>
+  <dimension ref="A1:W12"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -1286,60 +1319,58 @@
         <v>78</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="E5" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="H5" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="G5" s="4" t="s">
+      <c r="I5" s="2" t="s">
         <v>83</v>
-      </c>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2" t="s">
-        <v>84</v>
       </c>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
       <c r="M5" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="N5" s="2" t="s">
+      <c r="P5" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="O5" s="2" t="s">
+      <c r="Q5" s="2"/>
+      <c r="R5" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="P5" s="2" t="s">
+      <c r="S5" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="Q5" s="2" t="s">
+      <c r="T5" s="2" t="s">
         <v>89</v>
-      </c>
-      <c r="R5" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="S5" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="T5" s="2" t="s">
-        <v>92</v>
       </c>
       <c r="U5" s="2"/>
       <c r="V5" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W5" s="2" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="180.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
@@ -1347,52 +1378,60 @@
         <v>78</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="G6" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="G6" s="2"/>
       <c r="H6" s="2"/>
       <c r="I6" s="2" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
-      <c r="N6" s="2"/>
+      <c r="M6" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>98</v>
+      </c>
       <c r="O6" s="2" t="s">
         <v>99</v>
       </c>
       <c r="P6" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="Q6" s="2"/>
+      <c r="Q6" s="2" t="s">
+        <v>101</v>
+      </c>
       <c r="R6" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="U6" s="2"/>
       <c r="V6" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W6" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="180.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
@@ -1400,23 +1439,21 @@
         <v>78</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>62</v>
+        <v>106</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>108</v>
-      </c>
+        <v>109</v>
+      </c>
+      <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
@@ -1424,27 +1461,27 @@
       <c r="M7" s="2"/>
       <c r="N7" s="2"/>
       <c r="O7" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Q7" s="2"/>
       <c r="R7" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="U7" s="2"/>
       <c r="V7" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W7" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1458,20 +1495,20 @@
         <v>62</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
@@ -1479,14 +1516,12 @@
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
       <c r="O8" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="Q8" s="2" t="s">
         <v>123</v>
       </c>
+      <c r="Q8" s="2"/>
       <c r="R8" s="2" t="s">
         <v>124</v>
       </c>
@@ -1504,76 +1539,76 @@
         <v>127</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>128</v>
+        <v>78</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>62</v>
       </c>
       <c r="D9" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="G9" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="G9" s="2"/>
-      <c r="H9" s="4" t="s">
+      <c r="H9" s="2"/>
+      <c r="I9" s="2" t="s">
         <v>132</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>133</v>
       </c>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
-      <c r="L9" s="2" t="s">
-        <v>134</v>
-      </c>
+      <c r="L9" s="2"/>
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
       <c r="O9" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="Q9" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="P9" s="2" t="s">
+      <c r="R9" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="Q9" s="2" t="s">
+      <c r="S9" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="R9" s="2" t="s">
+      <c r="T9" s="2" t="s">
         <v>138</v>
-      </c>
-      <c r="S9" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="T9" s="2" t="s">
-        <v>140</v>
       </c>
       <c r="U9" s="2"/>
       <c r="V9" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W9" s="2" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="D10" s="2"/>
+      <c r="D10" s="2" t="s">
+        <v>141</v>
+      </c>
       <c r="E10" s="2" t="s">
         <v>142</v>
       </c>
@@ -1581,64 +1616,64 @@
         <v>143</v>
       </c>
       <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
+      <c r="H10" s="4" t="s">
+        <v>144</v>
+      </c>
       <c r="I10" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
+      <c r="L10" s="2" t="s">
+        <v>146</v>
+      </c>
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
-      <c r="O10" s="2"/>
+      <c r="O10" s="2" t="s">
+        <v>147</v>
+      </c>
       <c r="P10" s="2" t="s">
-        <v>136</v>
+        <v>86</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="U10" s="2"/>
       <c r="V10" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W10" s="2" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>151</v>
-      </c>
+        <v>62</v>
+      </c>
+      <c r="D11" s="2"/>
       <c r="E11" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>153</v>
-      </c>
-      <c r="H11" s="4" t="s">
         <v>154</v>
       </c>
+      <c r="G11" s="2"/>
+      <c r="H11" s="2"/>
       <c r="I11" s="2" t="s">
         <v>155</v>
       </c>
@@ -1647,43 +1682,102 @@
       <c r="L11" s="2"/>
       <c r="M11" s="2"/>
       <c r="N11" s="2"/>
-      <c r="O11" s="2" t="s">
+      <c r="O11" s="2"/>
+      <c r="P11" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="Q11" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="P11" s="2" t="s">
+      <c r="R11" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="Q11" s="2" t="s">
+      <c r="S11" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="R11" s="2" t="s">
+      <c r="T11" s="2" t="s">
         <v>159</v>
-      </c>
-      <c r="S11" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="T11" s="2" t="s">
-        <v>161</v>
       </c>
       <c r="U11" s="2"/>
       <c r="V11" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W11" s="2" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="2" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="D12" s="2" t="s">
         <v>162</v>
       </c>
+      <c r="E12" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G12" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2"/>
+      <c r="L12" s="2"/>
+      <c r="M12" s="2"/>
+      <c r="N12" s="2"/>
+      <c r="O12" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="T12" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="U12" s="2"/>
+      <c r="V12" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="W12" s="2" t="s">
+        <v>173</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W11"/>
+  <autoFilter ref="A1:W12"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1" display="https://www.dachser.fr"/>
     <hyperlink ref="H2" r:id="rId2" display="https://www.dachser.com/en/cosmetic-logistics"/>
     <hyperlink ref="G3" r:id="rId3" display="www.kava.cn"/>
     <hyperlink ref="G4" r:id="rId4" display="www.lamerbeauty.uk ; www.rsgroup.cn"/>
-    <hyperlink ref="G5" r:id="rId5" display="www.effervescence-lab.com"/>
-    <hyperlink ref="H9" r:id="rId6" display="https://welcon.kocca.kr/en/directory/company/cosplan-inc--5601"/>
-    <hyperlink ref="G11" r:id="rId7" display="https://iwasecosfa.eu"/>
-    <hyperlink ref="H11" r:id="rId8" display="https://iwasecosfa-eu.covalo.com/"/>
+    <hyperlink ref="G5" r:id="rId5" display="https://www.desjardin.fr"/>
+    <hyperlink ref="H5" r:id="rId6" display="https://www.desjardin.fr/en/categories/cosmetic-packaging"/>
+    <hyperlink ref="G6" r:id="rId7" display="www.effervescence-lab.com"/>
+    <hyperlink ref="H10" r:id="rId8" display="https://welcon.kocca.kr/en/directory/company/cosplan-inc--5601"/>
+    <hyperlink ref="G12" r:id="rId9" display="https://iwasecosfa.eu"/>
+    <hyperlink ref="H12" r:id="rId10" display="https://iwasecosfa-eu.covalo.com/"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1692,7 +1786,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId9"/>
+  <drawing r:id="rId11"/>
 </worksheet>
 </file>
 
@@ -1714,10 +1808,10 @@
         <v>1</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1725,11 +1819,11 @@
         <v>23</v>
       </c>
       <c r="B2" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$11,A2)</f>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$12,A2)</f>
         <v>1</v>
       </c>
       <c r="C2" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$11,A2,Контакты!$U$2:$U$11,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$12,A2,Контакты!$U$2:$U$12,"Высокий")</f>
         <v>0</v>
       </c>
     </row>
@@ -1738,11 +1832,11 @@
         <v>44</v>
       </c>
       <c r="B3" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$11,A3)</f>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$12,A3)</f>
         <v>2</v>
       </c>
       <c r="C3" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$11,A3,Контакты!$U$2:$U$11,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$12,A3,Контакты!$U$2:$U$12,"Высокий")</f>
         <v>1</v>
       </c>
     </row>
@@ -1751,47 +1845,47 @@
         <v>78</v>
       </c>
       <c r="B4" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$11,A4)</f>
-        <v>4</v>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$12,A4)</f>
+        <v>5</v>
       </c>
       <c r="C4" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$11,A4,Контакты!$U$2:$U$11,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$12,A4,Контакты!$U$2:$U$12,"Высокий")</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>128</v>
+        <v>140</v>
       </c>
       <c r="B5" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$11,A5)</f>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$12,A5)</f>
         <v>2</v>
       </c>
       <c r="C5" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$11,A5,Контакты!$U$2:$U$11,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$12,A5,Контакты!$U$2:$U$12,"Высокий")</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="B6" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$11,A6)</f>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$12,A6)</f>
         <v>1</v>
       </c>
       <c r="C6" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$11,A6,Контакты!$U$2:$U$11,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$12,A6,Контакты!$U$2:$U$12,"Высокий")</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="B7" s="7" t="n">
         <f aca="false">SUM(B2:B6)</f>
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C7" s="7" t="n">
         <f aca="false">SUM(C2:C6)</f>
@@ -1808,7 +1902,7 @@
         <v>2</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="C9" s="6"/>
     </row>
@@ -1817,7 +1911,7 @@
         <v>62</v>
       </c>
       <c r="B10" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$11,A10)</f>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$12,A10)</f>
         <v>5</v>
       </c>
       <c r="C10" s="6"/>
@@ -1827,27 +1921,27 @@
         <v>24</v>
       </c>
       <c r="B11" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$11,A11)</f>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$12,A11)</f>
         <v>1</v>
       </c>
       <c r="C11" s="6"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>79</v>
+        <v>91</v>
       </c>
       <c r="B12" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$11,A12)</f>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$12,A12)</f>
         <v>1</v>
       </c>
       <c r="C12" s="6"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="B13" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$11,A13)</f>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$12,A13)</f>
         <v>2</v>
       </c>
       <c r="C13" s="6"/>
@@ -1857,8 +1951,8 @@
         <v>45</v>
       </c>
       <c r="B14" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$11,A14)</f>
-        <v>1</v>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$12,A14)</f>
+        <v>2</v>
       </c>
       <c r="C14" s="6"/>
     </row>

--- a/exhibition/contacts.xlsx
+++ b/exhibition/contacts.xlsx
@@ -12,7 +12,7 @@
     <sheet name="По странам" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Контакты!$A$1:$W$12</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Контакты!$A$1:$W$13</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="187">
   <si>
     <t xml:space="preserve">№</t>
   </si>
@@ -161,6 +161,67 @@
     <t xml:space="preserve">Китай</t>
   </si>
   <si>
+    <t xml:space="preserve">Сырьё / ингредиенты</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Шанхай</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHANDO Group (Shanghai CHANDO Group Co., Ltd., ранее JALA Group)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cosmetic 360, стенд GB64 (Innovation Route — Raw Materials), зона C-Beauty Journey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://en.chandogroup.com</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Крупная китайская косметическая группа (основана в 2001 г. в Шанхае). На выставке — собственные запатентованные ингредиенты: HiMurchaSin® пептид (антивозрастной, разработан с помощью ИИ, из полярных дрожжей), PDRN, Space Ginseng Yeast, экстракт горечавки (Gentiana Veitchiorum), Hicustos®, BIO-Revive, Photo-Shield 509. Свои бренды: CHANDO (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">自然堂</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">), MAYSU, Biorrier, Spring Summer, imine</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Шанхай, Китай</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Фото стенда</t>
+  </si>
+  <si>
+    <t xml:space="preserve">В январе 2024 JALA Group переименована в Shanghai CHANDO Group. Пептид HiMurchaSin найден вместе с институтом Университета Цинхуа: ИИ перебрал 2,8 млн белков дрожжей; используется в 7-м поколении их антивозрастной сыворотки (апрель 2026). 20 научных докладов на конгрессе IFSCC 2026. Данные об эффективности — из пресс-релизов компании. Неясно, продают ли ингредиенты сторонним брендам и делают ли контрактное производство — уточнить.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://en.chandogroup.com/news/40 ; https://kyodonewsprwire.jp/release/202610067388 ; https://www.chinadailyhk.com/article/640844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Уточнить, продают ли свои ингредиенты (HiMurchaSin, PDRN) другим брендам и на каких условиях; есть ли OEM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">photos/012_chando.jpg</t>
+  </si>
+  <si>
     <t xml:space="preserve">Упаковка</t>
   </si>
   <si>
@@ -284,9 +345,6 @@
     <t xml:space="preserve">Франция, рядом с аэропортом Paris Roissy-Charles-de-Gaulle</t>
   </si>
   <si>
-    <t xml:space="preserve">Фото стенда</t>
-  </si>
-  <si>
     <t xml:space="preserve">Работают с 1848 г. Делают металлическую упаковку для фармы, косметики, еды и напитков. Партии от 5 000 шт. до нескольких миллионов. На стенде — упаковка для известных брендов: L'Occitane, Roger &amp; Gallet, Biolane, Babor, La Biosthétique, Pommade Nova и др.</t>
   </si>
   <si>
@@ -342,9 +400,6 @@
   </si>
   <si>
     <t xml:space="preserve">photos/002_effervescence_lab.jpg ; photos/002b_effervescence_lab_brochure.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Сырьё / ингредиенты</t>
   </si>
   <si>
     <t xml:space="preserve">Лион (головной офис); лаборатория и склад — Сен-Вюльба (Эн)</t>
@@ -564,7 +619,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -615,6 +670,11 @@
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="WenQuanYi Zen Hei"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1016,7 +1076,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:W12"/>
+  <dimension ref="A1:W13"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -1181,7 +1241,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="103.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
@@ -1197,56 +1257,46 @@
       <c r="E3" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="F3" s="2"/>
+      <c r="F3" s="2" t="s">
+        <v>48</v>
+      </c>
       <c r="G3" s="4" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="J3" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="K3" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>53</v>
-      </c>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="2"/>
+      <c r="M3" s="2"/>
       <c r="N3" s="2"/>
       <c r="O3" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q3" s="2"/>
+      <c r="R3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="S3" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="T3" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="Q3" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="U3" s="2" t="s">
-        <v>60</v>
-      </c>
+      <c r="U3" s="2"/>
       <c r="V3" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W3" s="2" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
@@ -1254,120 +1304,126 @@
         <v>44</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>62</v>
+        <v>57</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>65</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="F4" s="2"/>
       <c r="G4" s="4" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="H4" s="2"/>
       <c r="I4" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="M4" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="N4" s="2"/>
+      <c r="O4" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="P4" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="Q4" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="K4" s="2"/>
-      <c r="L4" s="2" t="s">
+      <c r="R4" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="S4" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="T4" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="O4" s="2" t="s">
+      <c r="U4" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="P4" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q4" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="R4" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="S4" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="T4" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="U4" s="2"/>
       <c r="V4" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W4" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G5" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D5" s="2" t="s">
+      <c r="H5" s="2"/>
+      <c r="I5" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="J5" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G5" s="4" t="s">
+      <c r="K5" s="2"/>
+      <c r="L5" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="M5" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="N5" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2" t="s">
+      <c r="O5" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="N5" s="2"/>
-      <c r="O5" s="2" t="s">
+      <c r="P5" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q5" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="P5" s="2" t="s">
+      <c r="R5" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="Q5" s="2"/>
-      <c r="R5" s="2" t="s">
+      <c r="S5" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="S5" s="2" t="s">
+      <c r="T5" s="2" t="s">
         <v>88</v>
-      </c>
-      <c r="T5" s="2" t="s">
-        <v>89</v>
       </c>
       <c r="U5" s="2"/>
       <c r="V5" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W5" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1375,98 +1431,104 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G6" s="4" t="s">
         <v>93</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="H6" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="G6" s="4" t="s">
+      <c r="I6" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2" t="s">
-        <v>96</v>
       </c>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="N6" s="2"/>
+      <c r="O6" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="N6" s="2" t="s">
+      <c r="P6" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q6" s="2"/>
+      <c r="R6" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="O6" s="2" t="s">
+      <c r="S6" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="P6" s="2" t="s">
+      <c r="T6" s="2" t="s">
         <v>100</v>
-      </c>
-      <c r="Q6" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="R6" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="S6" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="T6" s="2" t="s">
-        <v>104</v>
       </c>
       <c r="U6" s="2"/>
       <c r="V6" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W6" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="180.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="G7" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="G7" s="2"/>
       <c r="H7" s="2"/>
       <c r="I7" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
-      <c r="M7" s="2"/>
-      <c r="N7" s="2"/>
+      <c r="M7" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>109</v>
+      </c>
       <c r="O7" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="P7" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="P7" s="2" t="s">
+      <c r="Q7" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="Q7" s="2"/>
       <c r="R7" s="2" t="s">
         <v>113</v>
       </c>
@@ -1484,15 +1546,15 @@
         <v>116</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="180.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>62</v>
+        <v>45</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>117</v>
@@ -1503,12 +1565,10 @@
       <c r="F8" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="G8" s="2" t="s">
-        <v>120</v>
-      </c>
+      <c r="G8" s="2"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
@@ -1516,27 +1576,27 @@
       <c r="M8" s="2"/>
       <c r="N8" s="2"/>
       <c r="O8" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="P8" s="2" t="s">
         <v>122</v>
-      </c>
-      <c r="P8" s="2" t="s">
-        <v>123</v>
       </c>
       <c r="Q8" s="2"/>
       <c r="R8" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="S8" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="S8" s="2" t="s">
+      <c r="T8" s="2" t="s">
         <v>125</v>
-      </c>
-      <c r="T8" s="2" t="s">
-        <v>126</v>
       </c>
       <c r="U8" s="2"/>
       <c r="V8" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W8" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1544,26 +1604,26 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="D9" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="G9" s="2" t="s">
         <v>130</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>131</v>
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
@@ -1571,213 +1631,269 @@
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
       <c r="O9" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="P9" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="P9" s="2" t="s">
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="Q9" s="2" t="s">
+      <c r="S9" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="R9" s="2" t="s">
+      <c r="T9" s="2" t="s">
         <v>136</v>
-      </c>
-      <c r="S9" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="T9" s="2" t="s">
-        <v>138</v>
       </c>
       <c r="U9" s="2"/>
       <c r="V9" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W9" s="2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D10" s="2" t="s">
+      <c r="G10" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="H10" s="2"/>
+      <c r="I10" s="2" t="s">
         <v>142</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="G10" s="2"/>
-      <c r="H10" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>145</v>
       </c>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
-      <c r="L10" s="2" t="s">
-        <v>146</v>
-      </c>
+      <c r="L10" s="2"/>
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
       <c r="O10" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q10" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="R10" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="S10" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="P10" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="Q10" s="2" t="s">
+      <c r="T10" s="2" t="s">
         <v>148</v>
-      </c>
-      <c r="R10" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="S10" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="T10" s="2" t="s">
-        <v>151</v>
       </c>
       <c r="U10" s="2"/>
       <c r="V10" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W10" s="2" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D11" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>151</v>
+      </c>
       <c r="E11" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="G11" s="2"/>
+      <c r="H11" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
       <c r="I11" s="2" t="s">
         <v>155</v>
       </c>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
+      <c r="L11" s="2" t="s">
+        <v>156</v>
+      </c>
       <c r="M11" s="2"/>
       <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
+      <c r="O11" s="2" t="s">
+        <v>157</v>
+      </c>
       <c r="P11" s="2" t="s">
-        <v>86</v>
+        <v>52</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="U11" s="2"/>
       <c r="V11" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W11" s="2" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>162</v>
-      </c>
+        <v>74</v>
+      </c>
+      <c r="D12" s="2"/>
       <c r="E12" s="2" t="s">
         <v>163</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G12" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="H12" s="4" t="s">
+      <c r="G12" s="2"/>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2" t="s">
         <v>165</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>166</v>
       </c>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
-      <c r="O12" s="2" t="s">
+      <c r="O12" s="2"/>
+      <c r="P12" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="R12" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="P12" s="2" t="s">
+      <c r="S12" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="Q12" s="2" t="s">
+      <c r="T12" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="R12" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="S12" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="T12" s="2" t="s">
-        <v>172</v>
       </c>
       <c r="U12" s="2"/>
       <c r="V12" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W12" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>173</v>
       </c>
+      <c r="F13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2"/>
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="T13" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="U13" s="2"/>
+      <c r="V13" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="W13" s="2" t="s">
+        <v>183</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W12"/>
+  <autoFilter ref="A1:W13"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1" display="https://www.dachser.fr"/>
     <hyperlink ref="H2" r:id="rId2" display="https://www.dachser.com/en/cosmetic-logistics"/>
-    <hyperlink ref="G3" r:id="rId3" display="www.kava.cn"/>
-    <hyperlink ref="G4" r:id="rId4" display="www.lamerbeauty.uk ; www.rsgroup.cn"/>
-    <hyperlink ref="G5" r:id="rId5" display="https://www.desjardin.fr"/>
-    <hyperlink ref="H5" r:id="rId6" display="https://www.desjardin.fr/en/categories/cosmetic-packaging"/>
-    <hyperlink ref="G6" r:id="rId7" display="www.effervescence-lab.com"/>
-    <hyperlink ref="H10" r:id="rId8" display="https://welcon.kocca.kr/en/directory/company/cosplan-inc--5601"/>
-    <hyperlink ref="G12" r:id="rId9" display="https://iwasecosfa.eu"/>
-    <hyperlink ref="H12" r:id="rId10" display="https://iwasecosfa-eu.covalo.com/"/>
+    <hyperlink ref="G3" r:id="rId3" display="https://en.chandogroup.com"/>
+    <hyperlink ref="G4" r:id="rId4" display="www.kava.cn"/>
+    <hyperlink ref="G5" r:id="rId5" display="www.lamerbeauty.uk ; www.rsgroup.cn"/>
+    <hyperlink ref="G6" r:id="rId6" display="https://www.desjardin.fr"/>
+    <hyperlink ref="H6" r:id="rId7" display="https://www.desjardin.fr/en/categories/cosmetic-packaging"/>
+    <hyperlink ref="G7" r:id="rId8" display="www.effervescence-lab.com"/>
+    <hyperlink ref="H11" r:id="rId9" display="https://welcon.kocca.kr/en/directory/company/cosplan-inc--5601"/>
+    <hyperlink ref="G13" r:id="rId10" display="https://iwasecosfa.eu"/>
+    <hyperlink ref="H13" r:id="rId11" display="https://iwasecosfa-eu.covalo.com/"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1786,7 +1902,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId11"/>
+  <drawing r:id="rId12"/>
 </worksheet>
 </file>
 
@@ -1808,10 +1924,10 @@
         <v>1</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>175</v>
+        <v>185</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1819,11 +1935,11 @@
         <v>23</v>
       </c>
       <c r="B2" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$12,A2)</f>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$13,A2)</f>
         <v>1</v>
       </c>
       <c r="C2" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$12,A2,Контакты!$U$2:$U$12,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$13,A2,Контакты!$U$2:$U$13,"Высокий")</f>
         <v>0</v>
       </c>
     </row>
@@ -1832,60 +1948,60 @@
         <v>44</v>
       </c>
       <c r="B3" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$12,A3)</f>
-        <v>2</v>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$13,A3)</f>
+        <v>3</v>
       </c>
       <c r="C3" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$12,A3,Контакты!$U$2:$U$12,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$13,A3,Контакты!$U$2:$U$13,"Высокий")</f>
         <v>1</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>78</v>
+        <v>90</v>
       </c>
       <c r="B4" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$12,A4)</f>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$13,A4)</f>
         <v>5</v>
       </c>
       <c r="C4" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$12,A4,Контакты!$U$2:$U$12,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$13,A4,Контакты!$U$2:$U$13,"Высокий")</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="B5" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$12,A5)</f>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$13,A5)</f>
         <v>2</v>
       </c>
       <c r="C5" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$12,A5,Контакты!$U$2:$U$12,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$13,A5,Контакты!$U$2:$U$13,"Высокий")</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="B6" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$12,A6)</f>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$13,A6)</f>
         <v>1</v>
       </c>
       <c r="C6" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$12,A6,Контакты!$U$2:$U$12,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$13,A6,Контакты!$U$2:$U$13,"Высокий")</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="B7" s="7" t="n">
         <f aca="false">SUM(B2:B6)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7" s="7" t="n">
         <f aca="false">SUM(C2:C6)</f>
@@ -1902,16 +2018,16 @@
         <v>2</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>174</v>
+        <v>184</v>
       </c>
       <c r="C9" s="6"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="B10" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$12,A10)</f>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$13,A10)</f>
         <v>5</v>
       </c>
       <c r="C10" s="6"/>
@@ -1921,37 +2037,37 @@
         <v>24</v>
       </c>
       <c r="B11" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$12,A11)</f>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$13,A11)</f>
         <v>1</v>
       </c>
       <c r="C11" s="6"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>91</v>
+        <v>102</v>
       </c>
       <c r="B12" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$12,A12)</f>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$13,A12)</f>
         <v>1</v>
       </c>
       <c r="C12" s="6"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>106</v>
+        <v>45</v>
       </c>
       <c r="B13" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$12,A13)</f>
-        <v>2</v>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$13,A13)</f>
+        <v>3</v>
       </c>
       <c r="C13" s="6"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>45</v>
+        <v>57</v>
       </c>
       <c r="B14" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$12,A14)</f>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$13,A14)</f>
         <v>2</v>
       </c>
       <c r="C14" s="6"/>

--- a/exhibition/contacts.xlsx
+++ b/exhibition/contacts.xlsx
@@ -12,7 +12,7 @@
     <sheet name="По странам" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Контакты!$A$1:$W$13</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Контакты!$A$1:$W$14</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="198">
   <si>
     <t xml:space="preserve">№</t>
   </si>
@@ -225,6 +225,42 @@
     <t xml:space="preserve">Упаковка</t>
   </si>
   <si>
+    <t xml:space="preserve">Гонконг (офис); производство — партнёрские фабрики в Китае</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cypress Sourcing Company Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cosmetic 360, стенд GB60 (Innovation Route — Packaging &amp; Packing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Упаковка для парфюма и косметики: подарочные и жёсткие коробки (в т.ч. с двойным открыванием, деревянные), экологичная фольга, устойчивая упаковка; на стенде также флаконы для парфюма, диффузоры, стеклянные подсвечники, тубы. Работают как поставщик-посредник через партнёрские фабрики</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Гонконг</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Добавили в WeChat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Делают упаковку для парфюма. Могут отправлять в Россию. Минимальная партия — 10 000 шт.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Основана в 2004 г. в Гонконге, поставщик декоративной/подарочной упаковки через 7 партнёрских фабрик: картонные жёсткие и складные коробки, жестяные коробки, пластиковые пакеты, вакуумная формовка. По таможенным данным США — 63 поставки (бумага/картон, пластик, керамика). То есть это торговая компания, а не сама фабрика — уточнить, какая фабрика будет делать заказ.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://directory.designnews.com/cypress-sourcing-company-ltd-comp225768.html ; https://cn.panjiva.com/Cypress-Sourcing-Co-Ltd/67317206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Связь в WeChat: каталог упаковки для парфюма, цены на 10 000 шт., сроки и стоимость доставки в Россию, образцы; уточнить фабрику-производителя</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Высокий</t>
+  </si>
+  <si>
+    <t xml:space="preserve">photos/013_cypress.jpg</t>
+  </si>
+  <si>
     <t xml:space="preserve">Куньшань, пров. Цзянсу (≈50 км от Шанхая)</t>
   </si>
   <si>
@@ -265,9 +301,6 @@
   </si>
   <si>
     <t xml:space="preserve">Запросить каталог/образцы косметической упаковки, MOQ, цены; уточнить работу с Estée Lauder</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Высокий</t>
   </si>
   <si>
     <t xml:space="preserve">photos/001_kava.jpg</t>
@@ -1076,7 +1109,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:W13"/>
+  <dimension ref="A1:W14"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -1296,7 +1329,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
@@ -1312,56 +1345,48 @@
       <c r="E4" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="F4" s="2"/>
-      <c r="G4" s="4" t="s">
+      <c r="F4" s="2" t="s">
         <v>60</v>
       </c>
+      <c r="G4" s="2"/>
       <c r="H4" s="2"/>
       <c r="I4" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="J4" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="K4" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>65</v>
-      </c>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="2"/>
+      <c r="M4" s="2"/>
       <c r="N4" s="2"/>
       <c r="O4" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="S4" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="P4" s="2" t="s">
+      <c r="T4" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="Q4" s="2" t="s">
+      <c r="U4" s="2" t="s">
         <v>68</v>
-      </c>
-      <c r="R4" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="S4" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="T4" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="U4" s="2" t="s">
-        <v>72</v>
       </c>
       <c r="V4" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W4" s="2" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
@@ -1369,120 +1394,126 @@
         <v>44</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>74</v>
+        <v>57</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>77</v>
-      </c>
+        <v>71</v>
+      </c>
+      <c r="F5" s="2"/>
       <c r="G5" s="4" t="s">
-        <v>78</v>
+        <v>72</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="M5" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="N5" s="2"/>
+      <c r="O5" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="P5" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="Q5" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="K5" s="2"/>
-      <c r="L5" s="2" t="s">
+      <c r="R5" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="M5" s="2" t="s">
+      <c r="S5" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="N5" s="2" t="s">
+      <c r="T5" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="O5" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="P5" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q5" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="R5" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="S5" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="T5" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="U5" s="2"/>
+      <c r="U5" s="2" t="s">
+        <v>68</v>
+      </c>
       <c r="V5" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W5" s="2" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G6" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D6" s="2" t="s">
+      <c r="J6" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="K6" s="2"/>
+      <c r="L6" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G6" s="4" t="s">
+      <c r="M6" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="N6" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="I6" s="2" t="s">
+      <c r="O6" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2" t="s">
+      <c r="P6" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q6" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="N6" s="2"/>
-      <c r="O6" s="2" t="s">
+      <c r="R6" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="P6" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q6" s="2"/>
-      <c r="R6" s="2" t="s">
+      <c r="S6" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="S6" s="2" t="s">
+      <c r="T6" s="2" t="s">
         <v>99</v>
-      </c>
-      <c r="T6" s="2" t="s">
-        <v>100</v>
       </c>
       <c r="U6" s="2"/>
       <c r="V6" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W6" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1490,137 +1521,141 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D7" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="H7" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="I7" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2" t="s">
-        <v>107</v>
       </c>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
       <c r="M7" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="N7" s="2" t="s">
+      <c r="P7" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q7" s="2"/>
+      <c r="R7" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="O7" s="2" t="s">
+      <c r="S7" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="P7" s="2" t="s">
+      <c r="T7" s="2" t="s">
         <v>111</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="R7" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="S7" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="T7" s="2" t="s">
-        <v>115</v>
       </c>
       <c r="U7" s="2"/>
       <c r="V7" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W7" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="180.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>45</v>
+        <v>113</v>
       </c>
       <c r="D8" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="G8" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="G8" s="2"/>
       <c r="H8" s="2"/>
       <c r="I8" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
+      <c r="M8" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>120</v>
+      </c>
       <c r="O8" s="2" t="s">
         <v>121</v>
       </c>
       <c r="P8" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="Q8" s="2"/>
+      <c r="Q8" s="2" t="s">
+        <v>123</v>
+      </c>
       <c r="R8" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="U8" s="2"/>
       <c r="V8" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W8" s="2" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="180.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>74</v>
+        <v>45</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="G9" s="2" t="s">
         <v>130</v>
       </c>
+      <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2" t="s">
         <v>131</v>
@@ -1659,10 +1694,10 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>138</v>
@@ -1691,96 +1726,94 @@
       <c r="P10" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="Q10" s="2" t="s">
+      <c r="Q10" s="2"/>
+      <c r="R10" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="R10" s="2" t="s">
+      <c r="S10" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="S10" s="2" t="s">
+      <c r="T10" s="2" t="s">
         <v>147</v>
-      </c>
-      <c r="T10" s="2" t="s">
-        <v>148</v>
       </c>
       <c r="U10" s="2"/>
       <c r="V10" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W10" s="2" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D11" s="2" t="s">
+      <c r="F11" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="G11" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="H11" s="2"/>
+      <c r="I11" s="2" t="s">
         <v>153</v>
-      </c>
-      <c r="G11" s="2"/>
-      <c r="H11" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>155</v>
       </c>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
-      <c r="L11" s="2" t="s">
-        <v>156</v>
-      </c>
+      <c r="L11" s="2"/>
       <c r="M11" s="2"/>
       <c r="N11" s="2"/>
       <c r="O11" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="R11" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="P11" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q11" s="2" t="s">
+      <c r="S11" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="R11" s="2" t="s">
+      <c r="T11" s="2" t="s">
         <v>159</v>
-      </c>
-      <c r="S11" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="T11" s="2" t="s">
-        <v>161</v>
       </c>
       <c r="U11" s="2"/>
       <c r="V11" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W11" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D12" s="2"/>
+        <v>85</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>162</v>
+      </c>
       <c r="E12" s="2" t="s">
         <v>163</v>
       </c>
@@ -1788,64 +1821,64 @@
         <v>164</v>
       </c>
       <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
+      <c r="H12" s="4" t="s">
+        <v>165</v>
+      </c>
       <c r="I12" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
+      <c r="L12" s="2" t="s">
+        <v>167</v>
+      </c>
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
+      <c r="O12" s="2" t="s">
+        <v>168</v>
+      </c>
       <c r="P12" s="2" t="s">
         <v>52</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="U12" s="2"/>
       <c r="V12" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>171</v>
+        <v>161</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>172</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="D13" s="2"/>
       <c r="E13" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="H13" s="4" t="s">
         <v>175</v>
       </c>
+      <c r="G13" s="2"/>
+      <c r="H13" s="2"/>
       <c r="I13" s="2" t="s">
         <v>176</v>
       </c>
@@ -1854,46 +1887,103 @@
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
-      <c r="O13" s="2" t="s">
+      <c r="O13" s="2"/>
+      <c r="P13" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q13" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="P13" s="2" t="s">
+      <c r="R13" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="Q13" s="2" t="s">
+      <c r="S13" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="R13" s="2" t="s">
+      <c r="T13" s="2" t="s">
         <v>180</v>
-      </c>
-      <c r="S13" s="2" t="s">
-        <v>181</v>
-      </c>
-      <c r="T13" s="2" t="s">
-        <v>182</v>
       </c>
       <c r="U13" s="2"/>
       <c r="V13" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W13" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="2" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D14" s="2" t="s">
         <v>183</v>
       </c>
+      <c r="E14" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="2"/>
+      <c r="O14" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="S14" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="T14" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="U14" s="2"/>
+      <c r="V14" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="W14" s="2" t="s">
+        <v>194</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W13"/>
+  <autoFilter ref="A1:W14"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1" display="https://www.dachser.fr"/>
     <hyperlink ref="H2" r:id="rId2" display="https://www.dachser.com/en/cosmetic-logistics"/>
     <hyperlink ref="G3" r:id="rId3" display="https://en.chandogroup.com"/>
-    <hyperlink ref="G4" r:id="rId4" display="www.kava.cn"/>
-    <hyperlink ref="G5" r:id="rId5" display="www.lamerbeauty.uk ; www.rsgroup.cn"/>
-    <hyperlink ref="G6" r:id="rId6" display="https://www.desjardin.fr"/>
-    <hyperlink ref="H6" r:id="rId7" display="https://www.desjardin.fr/en/categories/cosmetic-packaging"/>
-    <hyperlink ref="G7" r:id="rId8" display="www.effervescence-lab.com"/>
-    <hyperlink ref="H11" r:id="rId9" display="https://welcon.kocca.kr/en/directory/company/cosplan-inc--5601"/>
-    <hyperlink ref="G13" r:id="rId10" display="https://iwasecosfa.eu"/>
-    <hyperlink ref="H13" r:id="rId11" display="https://iwasecosfa-eu.covalo.com/"/>
+    <hyperlink ref="G5" r:id="rId4" display="www.kava.cn"/>
+    <hyperlink ref="G6" r:id="rId5" display="www.lamerbeauty.uk ; www.rsgroup.cn"/>
+    <hyperlink ref="G7" r:id="rId6" display="https://www.desjardin.fr"/>
+    <hyperlink ref="H7" r:id="rId7" display="https://www.desjardin.fr/en/categories/cosmetic-packaging"/>
+    <hyperlink ref="G8" r:id="rId8" display="www.effervescence-lab.com"/>
+    <hyperlink ref="H12" r:id="rId9" display="https://welcon.kocca.kr/en/directory/company/cosplan-inc--5601"/>
+    <hyperlink ref="G14" r:id="rId10" display="https://iwasecosfa.eu"/>
+    <hyperlink ref="H14" r:id="rId11" display="https://iwasecosfa-eu.covalo.com/"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1924,10 +2014,10 @@
         <v>1</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>185</v>
+        <v>196</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1935,11 +2025,11 @@
         <v>23</v>
       </c>
       <c r="B2" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$13,A2)</f>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$14,A2)</f>
         <v>1</v>
       </c>
       <c r="C2" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$13,A2,Контакты!$U$2:$U$13,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$14,A2,Контакты!$U$2:$U$14,"Высокий")</f>
         <v>0</v>
       </c>
     </row>
@@ -1948,64 +2038,64 @@
         <v>44</v>
       </c>
       <c r="B3" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$13,A3)</f>
-        <v>3</v>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$14,A3)</f>
+        <v>4</v>
       </c>
       <c r="C3" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$13,A3,Контакты!$U$2:$U$13,"Высокий")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$14,A3,Контакты!$U$2:$U$14,"Высокий")</f>
+        <v>2</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>90</v>
+        <v>101</v>
       </c>
       <c r="B4" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$13,A4)</f>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$14,A4)</f>
         <v>5</v>
       </c>
       <c r="C4" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$13,A4,Контакты!$U$2:$U$13,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$14,A4,Контакты!$U$2:$U$14,"Высокий")</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>150</v>
+        <v>161</v>
       </c>
       <c r="B5" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$13,A5)</f>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$14,A5)</f>
         <v>2</v>
       </c>
       <c r="C5" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$13,A5,Контакты!$U$2:$U$13,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$14,A5,Контакты!$U$2:$U$14,"Высокий")</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
       <c r="B6" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$13,A6)</f>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$14,A6)</f>
         <v>1</v>
       </c>
       <c r="C6" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$13,A6,Контакты!$U$2:$U$13,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$14,A6,Контакты!$U$2:$U$14,"Высокий")</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>186</v>
+        <v>197</v>
       </c>
       <c r="B7" s="7" t="n">
         <f aca="false">SUM(B2:B6)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" s="7" t="n">
         <f aca="false">SUM(C2:C6)</f>
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2018,16 +2108,16 @@
         <v>2</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>184</v>
+        <v>195</v>
       </c>
       <c r="C9" s="6"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="B10" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$13,A10)</f>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$14,A10)</f>
         <v>5</v>
       </c>
       <c r="C10" s="6"/>
@@ -2037,17 +2127,17 @@
         <v>24</v>
       </c>
       <c r="B11" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$13,A11)</f>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$14,A11)</f>
         <v>1</v>
       </c>
       <c r="C11" s="6"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>102</v>
+        <v>113</v>
       </c>
       <c r="B12" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$13,A12)</f>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$14,A12)</f>
         <v>1</v>
       </c>
       <c r="C12" s="6"/>
@@ -2057,7 +2147,7 @@
         <v>45</v>
       </c>
       <c r="B13" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$13,A13)</f>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$14,A13)</f>
         <v>3</v>
       </c>
       <c r="C13" s="6"/>
@@ -2067,8 +2157,8 @@
         <v>57</v>
       </c>
       <c r="B14" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$13,A14)</f>
-        <v>2</v>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$14,A14)</f>
+        <v>3</v>
       </c>
       <c r="C14" s="6"/>
     </row>

--- a/exhibition/contacts.xlsx
+++ b/exhibition/contacts.xlsx
@@ -234,7 +234,7 @@
     <t xml:space="preserve">Cosmetic 360, стенд GB60 (Innovation Route — Packaging &amp; Packing)</t>
   </si>
   <si>
-    <t xml:space="preserve">Упаковка для парфюма и косметики: подарочные и жёсткие коробки (в т.ч. с двойным открыванием, деревянные), экологичная фольга, устойчивая упаковка; на стенде также флаконы для парфюма, диффузоры, стеклянные подсвечники, тубы. Работают как поставщик-посредник через партнёрские фабрики</t>
+    <t xml:space="preserve">Упаковка для парфюма и косметики: подарочные и жёсткие коробки (в т.ч. с двойным открыванием, деревянные), экологичная фольга, устойчивая упаковка; на стенде также флаконы для парфюма, диффузоры, стеклянные подсвечники, тубы. Работают как поставщик-посредник через партнёрские фабрики. На видео со стенда: компактные флаконы для парфюма (тревел-формат / ролики 10–15 мл) с цветным декоративным стеклом и узором «под янтарь/мрамор» (синий, оранжевый, красный), чёрные колпачки, фигурные флаконы; к ним — подарочные коробки</t>
   </si>
   <si>
     <t xml:space="preserve">Гонконг</t>
@@ -258,7 +258,7 @@
     <t xml:space="preserve">Высокий</t>
   </si>
   <si>
-    <t xml:space="preserve">photos/013_cypress.jpg</t>
+    <t xml:space="preserve">photos/013_cypress.jpg ; photos/013b_cypress_video.MOV</t>
   </si>
   <si>
     <t xml:space="preserve">Куньшань, пров. Цзянсу (≈50 км от Шанхая)</t>
@@ -1329,7 +1329,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>

--- a/exhibition/contacts.xlsx
+++ b/exhibition/contacts.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="200">
   <si>
     <t xml:space="preserve">№</t>
   </si>
@@ -237,6 +237,12 @@
     <t xml:space="preserve">Упаковка для парфюма и косметики: подарочные и жёсткие коробки (в т.ч. с двойным открыванием, деревянные), экологичная фольга, устойчивая упаковка; на стенде также флаконы для парфюма, диффузоры, стеклянные подсвечники, тубы. Работают как поставщик-посредник через партнёрские фабрики. На видео со стенда: компактные флаконы для парфюма (тревел-формат / ролики 10–15 мл) с цветным декоративным стеклом и узором «под янтарь/мрамор» (синий, оранжевый, красный), чёрные колпачки, фигурные флаконы; к ним — подарочные коробки</t>
   </si>
   <si>
+    <t xml:space="preserve">Janis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+86 137 9887 7125 (WeChat)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Гонконг</t>
   </si>
   <si>
@@ -252,7 +258,7 @@
     <t xml:space="preserve">https://directory.designnews.com/cypress-sourcing-company-ltd-comp225768.html ; https://cn.panjiva.com/Cypress-Sourcing-Co-Ltd/67317206</t>
   </si>
   <si>
-    <t xml:space="preserve">Связь в WeChat: каталог упаковки для парфюма, цены на 10 000 шт., сроки и стоимость доставки в Россию, образцы; уточнить фабрику-производителя</t>
+    <t xml:space="preserve">Написать Janis в WeChat (+86 137 9887 7125): каталог упаковки и флаконов для парфюма, цены на 10 000 шт., сроки и стоимость доставки в Россию, образцы; уточнить фабрику-производителя</t>
   </si>
   <si>
     <t xml:space="preserve">Высокий</t>
@@ -1353,37 +1359,41 @@
       <c r="I4" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="J4" s="2"/>
+      <c r="J4" s="2" t="s">
+        <v>62</v>
+      </c>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
+      <c r="N4" s="2" t="s">
+        <v>63</v>
+      </c>
       <c r="O4" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="U4" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="V4" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W4" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1397,58 +1407,58 @@
         <v>57</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="4" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="P5" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="R5" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="S5" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="T5" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="U5" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="V5" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W5" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1459,61 +1469,61 @@
         <v>44</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="G6" s="4" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="K6" s="2"/>
       <c r="L6" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="N6" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="O6" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="P6" s="2" t="s">
         <v>36</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="U6" s="2"/>
       <c r="V6" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W6" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1521,58 +1531,58 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>57</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>27</v>
       </c>
       <c r="G7" s="4" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="H7" s="4" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
       <c r="M7" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="P7" s="2" t="s">
         <v>52</v>
       </c>
       <c r="Q7" s="2"/>
       <c r="R7" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="U7" s="2"/>
       <c r="V7" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W7" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1580,60 +1590,60 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="G8" s="4" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
       <c r="M8" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="N8" s="2" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="O8" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="U8" s="2"/>
       <c r="V8" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W8" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="180.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1641,24 +1651,24 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>45</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
@@ -1666,27 +1676,27 @@
       <c r="M9" s="2"/>
       <c r="N9" s="2"/>
       <c r="O9" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="U9" s="2"/>
       <c r="V9" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W9" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1694,26 +1704,26 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
@@ -1721,27 +1731,27 @@
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
       <c r="O10" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="Q10" s="2"/>
       <c r="R10" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="U10" s="2"/>
       <c r="V10" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W10" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1749,26 +1759,26 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="H11" s="2"/>
       <c r="I11" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
@@ -1776,29 +1786,29 @@
       <c r="M11" s="2"/>
       <c r="N11" s="2"/>
       <c r="O11" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="U11" s="2"/>
       <c r="V11" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W11" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1806,58 +1816,58 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="G12" s="2"/>
       <c r="H12" s="4" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
       <c r="L12" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
       <c r="O12" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="P12" s="2" t="s">
         <v>52</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="U12" s="2"/>
       <c r="V12" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1865,22 +1875,22 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D13" s="2"/>
       <c r="E13" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
@@ -1892,23 +1902,23 @@
         <v>52</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="U13" s="2"/>
       <c r="V13" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W13" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1916,28 +1926,28 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>45</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>27</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
@@ -1945,29 +1955,29 @@
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
       <c r="O14" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="U14" s="2"/>
       <c r="V14" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W14" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
   </sheetData>
@@ -2014,10 +2024,10 @@
         <v>1</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2048,7 +2058,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="B4" s="6" t="n">
         <f aca="false">COUNTIF(Контакты!$B$2:$B$14,A4)</f>
@@ -2061,7 +2071,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B5" s="6" t="n">
         <f aca="false">COUNTIF(Контакты!$B$2:$B$14,A5)</f>
@@ -2074,7 +2084,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="B6" s="6" t="n">
         <f aca="false">COUNTIF(Контакты!$B$2:$B$14,A6)</f>
@@ -2087,7 +2097,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="B7" s="7" t="n">
         <f aca="false">SUM(B2:B6)</f>
@@ -2108,13 +2118,13 @@
         <v>2</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C9" s="6"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B10" s="6" t="n">
         <f aca="false">COUNTIF(Контакты!$C$2:$C$14,A10)</f>
@@ -2134,7 +2144,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="B12" s="6" t="n">
         <f aca="false">COUNTIF(Контакты!$C$2:$C$14,A12)</f>

--- a/exhibition/contacts.xlsx
+++ b/exhibition/contacts.xlsx
@@ -10,9 +10,11 @@
   <sheets>
     <sheet name="Контакты" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="По странам" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="Стенд INPD (Китай)" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Контакты!$A$1:$W$14</definedName>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Стенд INPD (Китай)'!$A$1:$D$43</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -24,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="248" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="283">
   <si>
     <t xml:space="preserve">№</t>
   </si>
@@ -649,6 +651,680 @@
   </si>
   <si>
     <t xml:space="preserve">Итого</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Тип</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Комментарий</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Проверка</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">全丽 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BIOTRULY</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Можно заказать (OEM/ODM)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Шанхай. ODM: натуральная и ферментированная косметика без консервантов, 9 фабрик, свои формулы, производство тары, ISO 22716 (GMP). Делали для Herborist, Yunnan Baiyao, AFU и др. Сайт biotruly.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Подтверждено</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cypress Sourcing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Упаковка (уже в таблице контактов)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">佳嘉乐 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">JAJALE Biotech</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Ханчжоу. Ферментированные масла и активы (продаётся через Brenntag); упоминают OEM, но про готовую косметику не ясно</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Частично</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LFC Laboratoire France Cosmetic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Не удалось проверить</t>
+  </si>
+  <si>
+    <t xml:space="preserve">«Since 1994». Во Франции с 1994 г. зарегистрирована France OEM Cosmetic (Лион, «Laboratoire France Cosmetic»), оптовая торговля парфюмерией и косметикой — возможно, это она; связь с Китаем не подтверждена</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Не подтверждено</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">华熙生物 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Bloomage Biotech</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Крупнейший производитель гиалуроновой кислоты; также свои бренды (BioHyalux, Quadha и др.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">По общим данным</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">福瑞达 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FREDA</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Гиалуроновая кислота и сырьё + свои бренды</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">湃肽生物 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">XPC (Zhejiang Peptites Biotech)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Пептиды для косметики; премия INPD за сырьё 2025</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">自然堂集团 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CHANDO Group</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Свои ингредиенты + бренды (уже в таблице контактов)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">PROYA </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">珀莱雅</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Своя марка (бренд)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Крупная группа брендов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAOGEPING</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Бренд декоративной косметики и ухода</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">OSM </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">欧诗漫</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Бренд (жемчужная косметика)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BTN </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">贝泰妮 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Botanee Group</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Группа брендов (Winona), спонсор китайской зоны</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">林清轩 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Forest Cabin</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Бренд ухода (масла, камелия)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">花西子 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Florasis</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Бренд макияжа, в т.ч. губы; сам заказывает производство у контрактных фабрик</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">上美 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">CHICMAX</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Группа брендов (KANS, One Leaf)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">谷雨 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Guyu</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Бренд ухода; премия INPD за сырьё 2025</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">完美 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Perfect</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Компания прямых продаж, свои марки</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">珂谧 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">KeyC</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Бренд ухода</t>
+  </si>
+  <si>
+    <t xml:space="preserve">三草两木</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">谜奇 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MiQi</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Бренд; премия INPD за сырьё 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">樊文花</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Сеть салонов ухода за лицом / бренд</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">阿芙 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">AFU</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Бренд эфирных масел; премии INPD 2025</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">和治友德 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">FOHERB</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">植物医生 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">DR PLANT</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Бренд ухода, своя розница</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HBN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lilybyred</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Корейский бренд макияжа (тинты для губ)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">半亩花田</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Бренд ухода за телом</t>
+  </si>
+  <si>
+    <t xml:space="preserve">逐本</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Бренд (гидрофильные масла)</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">玫瑰颂 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Absolute Rose</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Бренд на розе; премия INPD за сырьё 2025</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">少女本色 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Girl Begin</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Бренд, был в китайском павильоне INPD 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tokalon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Исторический бренд Tokalon Paris</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MONO Skincare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">la french beauty</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Бренд</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ACYMER </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">娇诗美</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">—</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">循理 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Surely</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">养固健 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">orlherb / BEAUTRIO</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">uniquederma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ricalyn</t>
+  </si>
+  <si>
+    <t xml:space="preserve">燃</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">SkinVision Lab </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">肤见未来实验室</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HAUTEBIO </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">慧柏研究院</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Название похоже на исследовательский институт — уточнить на стенде</t>
+  </si>
+  <si>
+    <t xml:space="preserve">植美馥予</t>
   </si>
 </sst>
 </file>
@@ -785,7 +1461,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -816,6 +1492,14 @@
     </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -932,6 +1616,10 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </file>
 
@@ -2181,4 +2869,617 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:D43"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="70"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>200</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>201</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="C2" s="9" t="s">
+        <v>205</v>
+      </c>
+      <c r="D2" s="9" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="9" t="s">
+        <v>207</v>
+      </c>
+      <c r="B3" s="9" t="s">
+        <v>204</v>
+      </c>
+      <c r="C3" s="9" t="s">
+        <v>208</v>
+      </c>
+      <c r="D3" s="9" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>210</v>
+      </c>
+      <c r="D4" s="9" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="9" t="s">
+        <v>212</v>
+      </c>
+      <c r="B5" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C6" s="9" t="s">
+        <v>217</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>220</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C8" s="9" t="s">
+        <v>222</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="B9" s="9" t="s">
+        <v>45</v>
+      </c>
+      <c r="C9" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="D9" s="9" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="B10" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>227</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="9" t="s">
+        <v>230</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>231</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="9" t="s">
+        <v>232</v>
+      </c>
+      <c r="B13" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>233</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="8" t="s">
+        <v>234</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>235</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="B15" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>237</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="B16" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>239</v>
+      </c>
+      <c r="D16" s="9" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="B17" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="C17" s="9" t="s">
+        <v>241</v>
+      </c>
+      <c r="D17" s="9" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="B18" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="D18" s="9" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="D19" s="9" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="D20" s="9" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="8" t="s">
+        <v>247</v>
+      </c>
+      <c r="B21" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="C21" s="9" t="s">
+        <v>248</v>
+      </c>
+      <c r="D21" s="9" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="8" t="s">
+        <v>249</v>
+      </c>
+      <c r="B22" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>250</v>
+      </c>
+      <c r="D22" s="9" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="B23" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="C23" s="9" t="s">
+        <v>252</v>
+      </c>
+      <c r="D23" s="9" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>243</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>255</v>
+      </c>
+      <c r="D25" s="9" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="9" t="s">
+        <v>256</v>
+      </c>
+      <c r="B26" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="D26" s="9" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="9" t="s">
+        <v>257</v>
+      </c>
+      <c r="B27" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>258</v>
+      </c>
+      <c r="D27" s="9" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="B28" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>260</v>
+      </c>
+      <c r="D28" s="9" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="B29" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="D29" s="9" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="C30" s="9" t="s">
+        <v>264</v>
+      </c>
+      <c r="D30" s="9" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="B31" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="C31" s="9" t="s">
+        <v>266</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="9" t="s">
+        <v>267</v>
+      </c>
+      <c r="B32" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>268</v>
+      </c>
+      <c r="D32" s="9" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="9" t="s">
+        <v>269</v>
+      </c>
+      <c r="B33" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>245</v>
+      </c>
+      <c r="D33" s="9" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="9" t="s">
+        <v>270</v>
+      </c>
+      <c r="B34" s="9" t="s">
+        <v>226</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="D34" s="9" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="9" t="s">
+        <v>272</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="C35" s="9"/>
+      <c r="D35" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="8" t="s">
+        <v>274</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="C36" s="9"/>
+      <c r="D36" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="8" t="s">
+        <v>275</v>
+      </c>
+      <c r="B37" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="9" t="s">
+        <v>276</v>
+      </c>
+      <c r="B38" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="C38" s="9"/>
+      <c r="D38" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="9" t="s">
+        <v>277</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="C39" s="9"/>
+      <c r="D39" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="8" t="s">
+        <v>278</v>
+      </c>
+      <c r="B40" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="C40" s="9"/>
+      <c r="D40" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="9" t="s">
+        <v>279</v>
+      </c>
+      <c r="B41" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="C41" s="9"/>
+      <c r="D41" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="9" t="s">
+        <v>280</v>
+      </c>
+      <c r="B42" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="C42" s="9" t="s">
+        <v>281</v>
+      </c>
+      <c r="D42" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="8" t="s">
+        <v>282</v>
+      </c>
+      <c r="B43" s="9" t="s">
+        <v>213</v>
+      </c>
+      <c r="C43" s="9"/>
+      <c r="D43" s="9" t="s">
+        <v>273</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:D43"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>
--- a/exhibition/contacts.xlsx
+++ b/exhibition/contacts.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Стенд INPD (Китай)" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Контакты!$A$1:$W$14</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Контакты!$A$1:$W$15</definedName>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Стенд INPD (Китай)'!$A$1:$D$43</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="412" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="296">
   <si>
     <t xml:space="preserve">№</t>
   </si>
@@ -163,29 +163,20 @@
     <t xml:space="preserve">Китай</t>
   </si>
   <si>
-    <t xml:space="preserve">Сырьё / ингредиенты</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Шанхай</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CHANDO Group (Shanghai CHANDO Group Co., Ltd., ранее JALA Group)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cosmetic 360, стенд GB64 (Innovation Route — Raw Materials), зона C-Beauty Journey</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://en.chandogroup.com</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Крупная китайская косметическая группа (основана в 2001 г. в Шанхае). На выставке — собственные запатентованные ингредиенты: HiMurchaSin® пептид (антивозрастной, разработан с помощью ИИ, из полярных дрожжей), PDRN, Space Ginseng Yeast, экстракт горечавки (Gentiana Veitchiorum), Hicustos®, BIO-Revive, Photo-Shield 509. Свои бренды: CHANDO (</t>
+    <t xml:space="preserve">Контрактное производство</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Шанхай, промзона Цзиньшань</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">BIOTRULY </t>
     </r>
     <r>
       <rPr>
@@ -193,6 +184,262 @@
         <rFont val="WenQuanYi Zen Hei"/>
         <family val="2"/>
       </rPr>
+      <t xml:space="preserve">全丽 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(Shanghai Quanli / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">上海全丽生物科技有限公司</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Cosmetic 360 / INPD, китайская зона (логотип на общем стенде)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.biotruly.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.biotruly.com/zh-CN/project</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ODM: разработка и массовое производство натурального ухода за кожей, акцент на ферментацию растений и продукты без консервантов. Полный цикл: собственные ферментированные ингредиенты, производство косметики, производство тары (флаконов/банок). Свои формулы и оборудование</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Промзона Цзиньшань (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">金山工业区</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">), Шанхай, Китай — точный адрес не найден</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Логотип на стене китайских компаний (INPD)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Не общались — нашли по стене стенда</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Основана в октябре 2014 г. По сайту: «тайваньская компания, фабрики в Китае», 9 фабрик. Сертификат ISO 22716 (GMP для косметики, версия ЕС). По данным статьи на Zhihu (может быть устаревшей), делали продукцию для Herborist (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">佰草集</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">), Yunnan Baiyao, AFU (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">阿芙</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">), Kans (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">高姿</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">), Morita, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">御泥坊 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">и др.; свои марки — </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">猪猪家</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">才木始</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">. В отраслевых отчётах упоминается среди ключевых OEM/ODM-производителей. Контакты (телефон, почта) в открытых источниках не найдены; сайт из этой сессии не открывается.</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.biotruly.com/zh-CN/about ; https://www.biotruly.com/zh-CN/facility ; https://pitchhub.36kr.com/project/2012747365434885 ; https://zhuanlan.zhihu.com/p/32074190</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Открыть biotruly.com → раздел «</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">联系我们</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">» (контакты) или найти их стенд в китайской зоне; запросить: портфолио ODM, MOQ, сроки, есть ли продукты для губ, экспорт в Россию</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Высокий</t>
+  </si>
+  <si>
+    <t xml:space="preserve">photos/014_inpd_wall.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Сырьё / ингредиенты</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Шанхай</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHANDO Group (Shanghai CHANDO Group Co., Ltd., ранее JALA Group)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cosmetic 360, стенд GB64 (Innovation Route — Raw Materials), зона C-Beauty Journey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://en.chandogroup.com</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Крупная китайская косметическая группа (основана в 2001 г. в Шанхае). На выставке — собственные запатентованные ингредиенты: HiMurchaSin® пептид (антивозрастной, разработан с помощью ИИ, из полярных дрожжей), PDRN, Space Ginseng Yeast, экстракт горечавки (Gentiana Veitchiorum), Hicustos®, BIO-Revive, Photo-Shield 509. Свои бренды: CHANDO (</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <rFont val="WenQuanYi Zen Hei"/>
+        <family val="2"/>
+      </rPr>
       <t xml:space="preserve">自然堂</t>
     </r>
     <r>
@@ -263,9 +510,6 @@
     <t xml:space="preserve">Написать Janis в WeChat (+86 137 9887 7125): каталог упаковки и флаконов для парфюма, цены на 10 000 шт., сроки и стоимость доставки в Россию, образцы; уточнить фабрику-производителя</t>
   </si>
   <si>
-    <t xml:space="preserve">Высокий</t>
-  </si>
-  <si>
     <t xml:space="preserve">photos/013_cypress.jpg ; photos/013b_cypress_video.MOV</t>
   </si>
   <si>
@@ -312,9 +556,6 @@
   </si>
   <si>
     <t xml:space="preserve">photos/001_kava.jpg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Контрактное производство</t>
   </si>
   <si>
     <t xml:space="preserve">Хучжоу, пров. Чжэцзян (фабрика); офис — Линьань (Ханчжоу), Чжэцзян</t>
@@ -1803,7 +2044,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:W14"/>
+  <dimension ref="A1:W15"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -1968,7 +2209,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="103.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="117.9" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
@@ -1990,9 +2231,11 @@
       <c r="G3" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="H3" s="2"/>
+      <c r="H3" s="4" t="s">
+        <v>50</v>
+      </c>
       <c r="I3" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
@@ -2000,30 +2243,34 @@
       <c r="M3" s="2"/>
       <c r="N3" s="2"/>
       <c r="O3" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q3" s="2"/>
+        <v>53</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>54</v>
+      </c>
       <c r="R3" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="U3" s="2"/>
+        <v>57</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="V3" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W3" s="2" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="103.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
@@ -2031,52 +2278,46 @@
         <v>44</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="G4" s="2"/>
+        <v>63</v>
+      </c>
+      <c r="G4" s="4" t="s">
+        <v>64</v>
+      </c>
       <c r="H4" s="2"/>
       <c r="I4" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>62</v>
-      </c>
+        <v>65</v>
+      </c>
+      <c r="J4" s="2"/>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
-      <c r="N4" s="2" t="s">
-        <v>63</v>
-      </c>
+      <c r="N4" s="2"/>
       <c r="O4" s="2" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q4" s="2" t="s">
-        <v>66</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="Q4" s="2"/>
       <c r="R4" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="S4" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="U4" s="2" t="s">
         <v>70</v>
       </c>
+      <c r="U4" s="2"/>
       <c r="V4" s="2" t="s">
         <v>42</v>
       </c>
@@ -2084,7 +2325,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="135.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
@@ -2092,64 +2333,60 @@
         <v>44</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="F5" s="2"/>
-      <c r="G5" s="4" t="s">
         <v>74</v>
       </c>
+      <c r="F5" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G5" s="2"/>
       <c r="H5" s="2"/>
       <c r="I5" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="K5" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="L5" s="2" t="s">
+      <c r="K5" s="2"/>
+      <c r="L5" s="2"/>
+      <c r="M5" s="2"/>
+      <c r="N5" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="M5" s="2" t="s">
+      <c r="O5" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="N5" s="2"/>
-      <c r="O5" s="2" t="s">
+      <c r="P5" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="P5" s="2" t="s">
+      <c r="Q5" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="Q5" s="2" t="s">
+      <c r="R5" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="R5" s="2" t="s">
+      <c r="S5" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="S5" s="2" t="s">
+      <c r="T5" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="T5" s="2" t="s">
-        <v>85</v>
-      </c>
       <c r="U5" s="2" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="V5" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W5" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
@@ -2157,120 +2394,126 @@
         <v>44</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="F6" s="2"/>
+      <c r="G6" s="4" t="s">
         <v>88</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>91</v>
       </c>
       <c r="H6" s="2"/>
       <c r="I6" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="L6" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="M6" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2" t="s">
+      <c r="N6" s="2"/>
+      <c r="O6" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="M6" s="2" t="s">
+      <c r="P6" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="N6" s="2" t="s">
+      <c r="Q6" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="O6" s="2" t="s">
+      <c r="R6" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="P6" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="Q6" s="2" t="s">
+      <c r="S6" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="R6" s="2" t="s">
+      <c r="T6" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="S6" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="T6" s="2" t="s">
-        <v>101</v>
-      </c>
-      <c r="U6" s="2"/>
+      <c r="U6" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="V6" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W6" s="2" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="C7" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D7" s="2" t="s">
+      <c r="G7" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="H7" s="2"/>
+      <c r="I7" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G7" s="4" t="s">
+      <c r="J7" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="K7" s="2"/>
+      <c r="L7" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="I7" s="2" t="s">
+      <c r="M7" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
-      <c r="M7" s="2" t="s">
+      <c r="N7" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="N7" s="2"/>
       <c r="O7" s="2" t="s">
         <v>110</v>
       </c>
       <c r="P7" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="Q7" s="2"/>
+        <v>36</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>111</v>
+      </c>
       <c r="R7" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="U7" s="2"/>
       <c r="V7" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W7" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2278,82 +2521,82 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>115</v>
+        <v>72</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>118</v>
+        <v>27</v>
       </c>
       <c r="G8" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="H8" s="2"/>
+      <c r="H8" s="4" t="s">
+        <v>120</v>
+      </c>
       <c r="I8" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
       <c r="M8" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="N8" s="2" t="s">
         <v>122</v>
       </c>
+      <c r="N8" s="2"/>
       <c r="O8" s="2" t="s">
         <v>123</v>
       </c>
       <c r="P8" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q8" s="2"/>
+      <c r="R8" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="Q8" s="2" t="s">
+      <c r="S8" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="R8" s="2" t="s">
+      <c r="T8" s="2" t="s">
         <v>126</v>
-      </c>
-      <c r="S8" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="T8" s="2" t="s">
-        <v>128</v>
       </c>
       <c r="U8" s="2"/>
       <c r="V8" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W8" s="2" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="180.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>45</v>
+        <v>128</v>
       </c>
       <c r="D9" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="G9" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="G9" s="2"/>
       <c r="H9" s="2"/>
       <c r="I9" s="2" t="s">
         <v>133</v>
@@ -2361,57 +2604,61 @@
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
-      <c r="M9" s="2"/>
-      <c r="N9" s="2"/>
+      <c r="M9" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>135</v>
+      </c>
       <c r="O9" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="Q9" s="2"/>
+        <v>137</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>138</v>
+      </c>
       <c r="R9" s="2" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="U9" s="2"/>
       <c r="V9" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W9" s="2" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="180.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>87</v>
+        <v>60</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>143</v>
-      </c>
+        <v>145</v>
+      </c>
+      <c r="G10" s="2"/>
       <c r="H10" s="2"/>
       <c r="I10" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
@@ -2419,27 +2666,27 @@
       <c r="M10" s="2"/>
       <c r="N10" s="2"/>
       <c r="O10" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="Q10" s="2"/>
       <c r="R10" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="U10" s="2"/>
       <c r="V10" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W10" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2447,26 +2694,26 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>87</v>
+        <v>45</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="H11" s="2"/>
       <c r="I11" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
@@ -2474,40 +2721,38 @@
       <c r="M11" s="2"/>
       <c r="N11" s="2"/>
       <c r="O11" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="Q11" s="2" t="s">
-        <v>158</v>
-      </c>
+        <v>159</v>
+      </c>
+      <c r="Q11" s="2"/>
       <c r="R11" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="U11" s="2"/>
       <c r="V11" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W11" s="2" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>163</v>
+        <v>116</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>87</v>
+        <v>45</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>164</v>
@@ -2518,25 +2763,23 @@
       <c r="F12" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="G12" s="2"/>
-      <c r="H12" s="4" t="s">
+      <c r="G12" s="2" t="s">
         <v>167</v>
       </c>
+      <c r="H12" s="2"/>
       <c r="I12" s="2" t="s">
         <v>168</v>
       </c>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
-      <c r="L12" s="2" t="s">
-        <v>169</v>
-      </c>
+      <c r="L12" s="2"/>
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
       <c r="O12" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="P12" s="2" t="s">
         <v>170</v>
-      </c>
-      <c r="P12" s="2" t="s">
-        <v>52</v>
       </c>
       <c r="Q12" s="2" t="s">
         <v>171</v>
@@ -2558,95 +2801,95 @@
         <v>175</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D13" s="2"/>
+        <v>45</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>177</v>
+      </c>
       <c r="E13" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
+      <c r="H13" s="4" t="s">
+        <v>180</v>
+      </c>
       <c r="I13" s="2" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
+      <c r="L13" s="2" t="s">
+        <v>182</v>
+      </c>
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
-      <c r="O13" s="2"/>
+      <c r="O13" s="2" t="s">
+        <v>183</v>
+      </c>
       <c r="P13" s="2" t="s">
-        <v>52</v>
+        <v>67</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="U13" s="2"/>
       <c r="V13" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W13" s="2" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>185</v>
-      </c>
+      <c r="D14" s="2"/>
       <c r="E14" s="2" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>187</v>
-      </c>
-      <c r="H14" s="4" t="s">
-        <v>188</v>
-      </c>
+        <v>190</v>
+      </c>
+      <c r="G14" s="2"/>
+      <c r="H14" s="2"/>
       <c r="I14" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
-      <c r="O14" s="2" t="s">
-        <v>190</v>
-      </c>
+      <c r="O14" s="2"/>
       <c r="P14" s="2" t="s">
-        <v>191</v>
+        <v>67</v>
       </c>
       <c r="Q14" s="2" t="s">
         <v>192</v>
@@ -2668,20 +2911,81 @@
         <v>196</v>
       </c>
     </row>
+    <row r="15" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="2" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="S15" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="T15" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="U15" s="2"/>
+      <c r="V15" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="W15" s="2" t="s">
+        <v>209</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:W14"/>
+  <autoFilter ref="A1:W15"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1" display="https://www.dachser.fr"/>
     <hyperlink ref="H2" r:id="rId2" display="https://www.dachser.com/en/cosmetic-logistics"/>
-    <hyperlink ref="G3" r:id="rId3" display="https://en.chandogroup.com"/>
-    <hyperlink ref="G5" r:id="rId4" display="www.kava.cn"/>
-    <hyperlink ref="G6" r:id="rId5" display="www.lamerbeauty.uk ; www.rsgroup.cn"/>
-    <hyperlink ref="G7" r:id="rId6" display="https://www.desjardin.fr"/>
-    <hyperlink ref="H7" r:id="rId7" display="https://www.desjardin.fr/en/categories/cosmetic-packaging"/>
-    <hyperlink ref="G8" r:id="rId8" display="www.effervescence-lab.com"/>
-    <hyperlink ref="H12" r:id="rId9" display="https://welcon.kocca.kr/en/directory/company/cosplan-inc--5601"/>
-    <hyperlink ref="G14" r:id="rId10" display="https://iwasecosfa.eu"/>
-    <hyperlink ref="H14" r:id="rId11" display="https://iwasecosfa-eu.covalo.com/"/>
+    <hyperlink ref="G3" r:id="rId3" display="https://www.biotruly.com"/>
+    <hyperlink ref="H3" r:id="rId4" display="https://www.biotruly.com/zh-CN/project"/>
+    <hyperlink ref="G4" r:id="rId5" display="https://en.chandogroup.com"/>
+    <hyperlink ref="G6" r:id="rId6" display="www.kava.cn"/>
+    <hyperlink ref="G7" r:id="rId7" display="www.lamerbeauty.uk ; www.rsgroup.cn"/>
+    <hyperlink ref="G8" r:id="rId8" display="https://www.desjardin.fr"/>
+    <hyperlink ref="H8" r:id="rId9" display="https://www.desjardin.fr/en/categories/cosmetic-packaging"/>
+    <hyperlink ref="G9" r:id="rId10" display="www.effervescence-lab.com"/>
+    <hyperlink ref="H13" r:id="rId11" display="https://welcon.kocca.kr/en/directory/company/cosplan-inc--5601"/>
+    <hyperlink ref="G15" r:id="rId12" display="https://iwasecosfa.eu"/>
+    <hyperlink ref="H15" r:id="rId13" display="https://iwasecosfa-eu.covalo.com/"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2690,7 +2994,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId12"/>
+  <drawing r:id="rId14"/>
 </worksheet>
 </file>
 
@@ -2712,10 +3016,10 @@
         <v>1</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2723,11 +3027,11 @@
         <v>23</v>
       </c>
       <c r="B2" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$14,A2)</f>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$15,A2)</f>
         <v>1</v>
       </c>
       <c r="C2" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$14,A2,Контакты!$U$2:$U$14,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$15,A2,Контакты!$U$2:$U$15,"Высокий")</f>
         <v>0</v>
       </c>
     </row>
@@ -2736,64 +3040,64 @@
         <v>44</v>
       </c>
       <c r="B3" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$14,A3)</f>
-        <v>4</v>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$15,A3)</f>
+        <v>5</v>
       </c>
       <c r="C3" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$14,A3,Контакты!$U$2:$U$14,"Высокий")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$15,A3,Контакты!$U$2:$U$15,"Высокий")</f>
+        <v>3</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>103</v>
+        <v>116</v>
       </c>
       <c r="B4" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$14,A4)</f>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$15,A4)</f>
         <v>5</v>
       </c>
       <c r="C4" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$14,A4,Контакты!$U$2:$U$14,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$15,A4,Контакты!$U$2:$U$15,"Высокий")</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="B5" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$14,A5)</f>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$15,A5)</f>
         <v>2</v>
       </c>
       <c r="C5" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$14,A5,Контакты!$U$2:$U$14,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$15,A5,Контакты!$U$2:$U$15,"Высокий")</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="B6" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$14,A6)</f>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$15,A6)</f>
         <v>1</v>
       </c>
       <c r="C6" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$14,A6,Контакты!$U$2:$U$14,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$15,A6,Контакты!$U$2:$U$15,"Высокий")</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="B7" s="7" t="n">
         <f aca="false">SUM(B2:B6)</f>
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C7" s="7" t="n">
         <f aca="false">SUM(C2:C6)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2806,17 +3110,17 @@
         <v>2</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="C9" s="6"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>87</v>
+        <v>45</v>
       </c>
       <c r="B10" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$14,A10)</f>
-        <v>5</v>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$15,A10)</f>
+        <v>6</v>
       </c>
       <c r="C10" s="6"/>
     </row>
@@ -2825,37 +3129,37 @@
         <v>24</v>
       </c>
       <c r="B11" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$14,A11)</f>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$15,A11)</f>
         <v>1</v>
       </c>
       <c r="C11" s="6"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>115</v>
+        <v>128</v>
       </c>
       <c r="B12" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$14,A12)</f>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$15,A12)</f>
         <v>1</v>
       </c>
       <c r="C12" s="6"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="B13" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$14,A13)</f>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$15,A13)</f>
         <v>3</v>
       </c>
       <c r="C13" s="6"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>57</v>
+        <v>72</v>
       </c>
       <c r="B14" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$14,A14)</f>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$15,A14)</f>
         <v>3</v>
       </c>
       <c r="C14" s="6"/>
@@ -2890,585 +3194,585 @@
         <v>4</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>208</v>
+        <v>221</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>210</v>
+        <v>223</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>221</v>
+        <v>234</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>222</v>
+        <v>235</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>223</v>
+        <v>236</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>224</v>
+        <v>237</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>225</v>
+        <v>238</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>227</v>
+        <v>240</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>228</v>
+        <v>241</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>229</v>
+        <v>242</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>230</v>
+        <v>243</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="C12" s="9" t="s">
+        <v>244</v>
+      </c>
+      <c r="D12" s="9" t="s">
         <v>231</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>232</v>
+        <v>245</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>233</v>
+        <v>246</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>234</v>
+        <v>247</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>235</v>
+        <v>248</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>236</v>
+        <v>249</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>237</v>
+        <v>250</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>238</v>
+        <v>251</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>239</v>
+        <v>252</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>240</v>
+        <v>253</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>241</v>
+        <v>254</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>244</v>
+        <v>257</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>246</v>
+        <v>259</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>248</v>
+        <v>261</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>249</v>
+        <v>262</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>250</v>
+        <v>263</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>251</v>
+        <v>264</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>252</v>
+        <v>265</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>253</v>
+        <v>266</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>254</v>
+        <v>267</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>255</v>
+        <v>268</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="9" t="s">
-        <v>256</v>
+        <v>269</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="9" t="s">
-        <v>257</v>
+        <v>270</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>258</v>
+        <v>271</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="s">
-        <v>259</v>
+        <v>272</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>260</v>
+        <v>273</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="s">
-        <v>261</v>
+        <v>274</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>262</v>
+        <v>275</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="s">
-        <v>263</v>
+        <v>276</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>264</v>
+        <v>277</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="s">
-        <v>265</v>
+        <v>278</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>266</v>
+        <v>279</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="9" t="s">
-        <v>267</v>
+        <v>280</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>268</v>
+        <v>281</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="9" t="s">
-        <v>269</v>
+        <v>282</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>245</v>
+        <v>258</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="9" t="s">
-        <v>270</v>
+        <v>283</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>226</v>
+        <v>239</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>271</v>
+        <v>284</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="9" t="s">
-        <v>272</v>
+        <v>285</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="9" t="s">
-        <v>273</v>
+        <v>286</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="s">
-        <v>274</v>
+        <v>287</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="9" t="s">
-        <v>273</v>
+        <v>286</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="9" t="s">
-        <v>273</v>
+        <v>286</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="9" t="s">
-        <v>276</v>
+        <v>289</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="C38" s="9"/>
       <c r="D38" s="9" t="s">
-        <v>273</v>
+        <v>286</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="9" t="s">
-        <v>277</v>
+        <v>290</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="9" t="s">
-        <v>273</v>
+        <v>286</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="8" t="s">
-        <v>278</v>
+        <v>291</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="C40" s="9"/>
       <c r="D40" s="9" t="s">
-        <v>273</v>
+        <v>286</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="9" t="s">
-        <v>279</v>
+        <v>292</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="9" t="s">
-        <v>273</v>
+        <v>286</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="9" t="s">
-        <v>280</v>
+        <v>293</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>281</v>
+        <v>294</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>273</v>
+        <v>286</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="8" t="s">
-        <v>282</v>
+        <v>295</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="9" t="s">
-        <v>273</v>
+        <v>286</v>
       </c>
     </row>
   </sheetData>

--- a/exhibition/contacts.xlsx
+++ b/exhibition/contacts.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Стенд INPD (Китай)" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Контакты!$A$1:$W$15</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Контакты!$A$1:$W$16</definedName>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Стенд INPD (Китай)'!$A$1:$D$43</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="306">
   <si>
     <t xml:space="preserve">№</t>
   </si>
@@ -745,6 +745,36 @@
   </si>
   <si>
     <t xml:space="preserve">photos/009_biotic_phocea.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Мейссак (Коррез), Новая Аквитания; второй сайт — Юссак</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SIMAH (группа SOTHYS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://simah-cosmetiques.fr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Контрактное производство (CDMO / façonnier) высокоэффективной косметики, Made in France: адаптация и доработка готовых формул, создание формул на заказ, промышленное производство формул клиента. Кремы и уход (по буклету — розлив кремов в банки, реакторы-смесители)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usine Le Gôt, 890 route de Chauffour, 19500 Meyssac, Франция</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Буклет «SIMAH 1971 — Cosmetic Manufacturer», на столе — анкета-запрос для клиентов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Основан в 1971 г. семьёй Мас; производственное подразделение группы SOTHYS (профессиональная салонная косметика), которое открыло завод для сторонних брендов. ~140 сотрудников, оборот ~20 млн € (2024). Сертификаты ISO 22716 (GMP) и COSMOS (органика). Юрлицо SAS, SIREN 451 195 325.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.cosmetic-valley.com/en/annuaire-entreprises/simah ; https://www.lejournaldesentreprises.com/article/sothys-souvre-la-production-facon-2111197 ; https://www.leaderreunion.fr/en/projets-de-cosmetiques-simah-change-la-donne/ ; https://presseagence.fr/paris-simah-ouvre-son-savoir-faire-a-lexterne-une-opportunite-unique-pour-les-marques-du-secteur-cosmetique/ ; https://www.xerfi.com/etudes-par-entreprise/simah_451195325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Заполнить их анкету-запрос на стенде или через сайт; уточнить MOQ, сроки, делают ли продукты для губ и парфюм</t>
+  </si>
+  <si>
+    <t xml:space="preserve">photos/015_simah.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">Шартр (головной офис); производство — О-де-Франс (Невиль-ан-Феррен, под Лиллем), Нормандия; 1 завод в Польше</t>
@@ -2044,7 +2074,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:W15"/>
+  <dimension ref="A1:W16"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -2761,14 +2791,14 @@
         <v>165</v>
       </c>
       <c r="F12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G12" s="4" t="s">
         <v>166</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>167</v>
       </c>
       <c r="H12" s="2"/>
       <c r="I12" s="2" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
@@ -2776,202 +2806,257 @@
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
       <c r="O12" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="P12" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="P12" s="2" t="s">
+      <c r="Q12" s="2"/>
+      <c r="R12" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="Q12" s="2" t="s">
+      <c r="S12" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="R12" s="2" t="s">
+      <c r="T12" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="S12" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="T12" s="2" t="s">
-        <v>174</v>
       </c>
       <c r="U12" s="2"/>
       <c r="V12" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>176</v>
+        <v>116</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>45</v>
       </c>
       <c r="D13" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="G13" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="H13" s="2"/>
+      <c r="I13" s="2" t="s">
         <v>178</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="4" t="s">
-        <v>180</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>181</v>
       </c>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
-      <c r="L13" s="2" t="s">
-        <v>182</v>
-      </c>
+      <c r="L13" s="2"/>
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
       <c r="O13" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="S13" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="P13" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q13" s="2" t="s">
+      <c r="T13" s="2" t="s">
         <v>184</v>
-      </c>
-      <c r="R13" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="S13" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="T13" s="2" t="s">
-        <v>187</v>
       </c>
       <c r="U13" s="2"/>
       <c r="V13" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W13" s="2" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D14" s="2"/>
+      <c r="D14" s="2" t="s">
+        <v>187</v>
+      </c>
       <c r="E14" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="F14" s="2" t="s">
         <v>189</v>
       </c>
-      <c r="F14" s="2" t="s">
+      <c r="G14" s="2"/>
+      <c r="H14" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
       <c r="I14" s="2" t="s">
         <v>191</v>
       </c>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
+      <c r="L14" s="2" t="s">
+        <v>192</v>
+      </c>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
-      <c r="O14" s="2"/>
+      <c r="O14" s="2" t="s">
+        <v>193</v>
+      </c>
       <c r="P14" s="2" t="s">
         <v>67</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="U14" s="2"/>
       <c r="V14" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W14" s="2" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>198</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="D15" s="2"/>
       <c r="E15" s="2" t="s">
         <v>199</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G15" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="H15" s="4" t="s">
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2" t="s">
         <v>201</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>202</v>
       </c>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
       <c r="M15" s="2"/>
       <c r="N15" s="2"/>
-      <c r="O15" s="2" t="s">
+      <c r="O15" s="2"/>
+      <c r="P15" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="R15" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="P15" s="2" t="s">
+      <c r="S15" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="Q15" s="2" t="s">
+      <c r="T15" s="2" t="s">
         <v>205</v>
-      </c>
-      <c r="R15" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="S15" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="T15" s="2" t="s">
-        <v>208</v>
       </c>
       <c r="U15" s="2"/>
       <c r="V15" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W15" s="2" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>209</v>
       </c>
+      <c r="F16" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="2"/>
+      <c r="O16" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="P16" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="R16" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="S16" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="T16" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="U16" s="2"/>
+      <c r="V16" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="W16" s="2" t="s">
+        <v>219</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W15"/>
+  <autoFilter ref="A1:W16"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1" display="https://www.dachser.fr"/>
     <hyperlink ref="H2" r:id="rId2" display="https://www.dachser.com/en/cosmetic-logistics"/>
@@ -2983,9 +3068,10 @@
     <hyperlink ref="G8" r:id="rId8" display="https://www.desjardin.fr"/>
     <hyperlink ref="H8" r:id="rId9" display="https://www.desjardin.fr/en/categories/cosmetic-packaging"/>
     <hyperlink ref="G9" r:id="rId10" display="www.effervescence-lab.com"/>
-    <hyperlink ref="H13" r:id="rId11" display="https://welcon.kocca.kr/en/directory/company/cosplan-inc--5601"/>
-    <hyperlink ref="G15" r:id="rId12" display="https://iwasecosfa.eu"/>
-    <hyperlink ref="H15" r:id="rId13" display="https://iwasecosfa-eu.covalo.com/"/>
+    <hyperlink ref="G12" r:id="rId11" display="https://simah-cosmetiques.fr"/>
+    <hyperlink ref="H14" r:id="rId12" display="https://welcon.kocca.kr/en/directory/company/cosplan-inc--5601"/>
+    <hyperlink ref="G16" r:id="rId13" display="https://iwasecosfa.eu"/>
+    <hyperlink ref="H16" r:id="rId14" display="https://iwasecosfa-eu.covalo.com/"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2994,7 +3080,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId14"/>
+  <drawing r:id="rId15"/>
 </worksheet>
 </file>
 
@@ -3016,10 +3102,10 @@
         <v>1</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>211</v>
+        <v>221</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3027,11 +3113,11 @@
         <v>23</v>
       </c>
       <c r="B2" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$15,A2)</f>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$16,A2)</f>
         <v>1</v>
       </c>
       <c r="C2" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$15,A2,Контакты!$U$2:$U$15,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$16,A2,Контакты!$U$2:$U$16,"Высокий")</f>
         <v>0</v>
       </c>
     </row>
@@ -3040,11 +3126,11 @@
         <v>44</v>
       </c>
       <c r="B3" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$15,A3)</f>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$16,A3)</f>
         <v>5</v>
       </c>
       <c r="C3" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$15,A3,Контакты!$U$2:$U$15,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$16,A3,Контакты!$U$2:$U$16,"Высокий")</f>
         <v>3</v>
       </c>
     </row>
@@ -3053,47 +3139,47 @@
         <v>116</v>
       </c>
       <c r="B4" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$15,A4)</f>
-        <v>5</v>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$16,A4)</f>
+        <v>6</v>
       </c>
       <c r="C4" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$15,A4,Контакты!$U$2:$U$15,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$16,A4,Контакты!$U$2:$U$16,"Высокий")</f>
         <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>176</v>
+        <v>186</v>
       </c>
       <c r="B5" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$15,A5)</f>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$16,A5)</f>
         <v>2</v>
       </c>
       <c r="C5" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$15,A5,Контакты!$U$2:$U$15,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$16,A5,Контакты!$U$2:$U$16,"Высокий")</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="B6" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$15,A6)</f>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$16,A6)</f>
         <v>1</v>
       </c>
       <c r="C6" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$15,A6,Контакты!$U$2:$U$15,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$16,A6,Контакты!$U$2:$U$16,"Высокий")</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>212</v>
+        <v>222</v>
       </c>
       <c r="B7" s="7" t="n">
         <f aca="false">SUM(B2:B6)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7" s="7" t="n">
         <f aca="false">SUM(C2:C6)</f>
@@ -3110,7 +3196,7 @@
         <v>2</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="C9" s="6"/>
     </row>
@@ -3119,8 +3205,8 @@
         <v>45</v>
       </c>
       <c r="B10" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$15,A10)</f>
-        <v>6</v>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$16,A10)</f>
+        <v>7</v>
       </c>
       <c r="C10" s="6"/>
     </row>
@@ -3129,7 +3215,7 @@
         <v>24</v>
       </c>
       <c r="B11" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$15,A11)</f>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$16,A11)</f>
         <v>1</v>
       </c>
       <c r="C11" s="6"/>
@@ -3139,7 +3225,7 @@
         <v>128</v>
       </c>
       <c r="B12" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$15,A12)</f>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$16,A12)</f>
         <v>1</v>
       </c>
       <c r="C12" s="6"/>
@@ -3149,7 +3235,7 @@
         <v>60</v>
       </c>
       <c r="B13" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$15,A13)</f>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$16,A13)</f>
         <v>3</v>
       </c>
       <c r="C13" s="6"/>
@@ -3159,7 +3245,7 @@
         <v>72</v>
       </c>
       <c r="B14" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$15,A14)</f>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$16,A14)</f>
         <v>3</v>
       </c>
       <c r="C14" s="6"/>
@@ -3194,585 +3280,585 @@
         <v>4</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>213</v>
+        <v>223</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>214</v>
+        <v>224</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>216</v>
+        <v>226</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>217</v>
+        <v>227</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>60</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>60</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>60</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
       <c r="B8" s="9" t="s">
         <v>60</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>60</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
+        <v>251</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>252</v>
+      </c>
+      <c r="D11" s="9" t="s">
         <v>241</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>239</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>242</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
+        <v>259</v>
+      </c>
+      <c r="B15" s="9" t="s">
         <v>249</v>
       </c>
-      <c r="B15" s="9" t="s">
-        <v>239</v>
-      </c>
       <c r="C15" s="9" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
+        <v>276</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>249</v>
+      </c>
+      <c r="C24" s="9" t="s">
         <v>266</v>
       </c>
-      <c r="B24" s="9" t="s">
-        <v>239</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>256</v>
-      </c>
       <c r="D24" s="9" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="9" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="9" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="s">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="9" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="9" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="9" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="9" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="9" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="9" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="9" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="9" t="s">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="C38" s="9"/>
       <c r="D38" s="9" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="9" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="9" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="8" t="s">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="C40" s="9"/>
       <c r="D40" s="9" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="9" t="s">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="9" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="9" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="8" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="9" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
     </row>
   </sheetData>

--- a/exhibition/contacts.xlsx
+++ b/exhibition/contacts.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Стенд INPD (Китай)" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Контакты!$A$1:$W$16</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Контакты!$A$1:$W$17</definedName>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Стенд INPD (Китай)'!$A$1:$D$43</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="306">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="316">
   <si>
     <t xml:space="preserve">№</t>
   </si>
@@ -604,6 +604,36 @@
   </si>
   <si>
     <t xml:space="preserve">Франция</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Франция (головной офис); заводы во Франции, Испании, Калифорнии (США) и Канаде</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANJAC Health &amp; Beauty (группа; на стенде — SICAF и др.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cosmetic 360 (секция Formulation)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Крупная семейная французская промышленная группа: разработка и производство под ключ для брендов красоты и здоровья, от сырья до готового продукта. Подразделения: SICAF — уход и премиальные текстуры; Shadeline — дермокосметика; Aircos — пудровая косметика (лидер во Франции); Pascual Cosmétiques — литьевые и жидкие продукты, СТИКИ (помады/бальзамы для губ); Roval Cosmétiques — 2 завода во Франции + Испания; Cosmetix West (Лос-Анджелес); APR Beauty (Торонто). На стенде акцент: «K-Beauty &amp; K-Derma экспертиза для ваших продуктов» (уход в корейском стиле, патчи от прыщей и т.п.)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Фото стенда; контакты менеджера — будут</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Изучали стенд (уход в стиле K-beauty/K-derma)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Около 16–22 площадок R&amp;D и производства (цифры разнятся по источникам) во Франции, Испании, Калифорнии и Канаде. У SICAF новое здание R&amp;D 1 100 м², команда ~20 человек, 3 лаборатории разработки. Охватывают почти все категории: уход, макияж (пудры, стики, литьевые продукты), дермокосметика — то есть потенциально и продукты для губ.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://pharmaboardroom.com/interviews/interview-aurelien-chaufour-managing-director-anjac-france/ ; https://www.premiumbeautynews.com/fr/sicaf-se-dote-d-un-nouveau,18374 ; https://www.premiumbeautynews.com/en/anjac-h-b-group-keeps-growing-with,16583 ; https://www.gcimagazine.com/brands-products/contract-manufacturing-services/news/22914175/anjac-health-beautys-investment-in-apr-beauty-boosts-beauty-turnkey-capabilities ; https://cosmetic-valley.com/en/directory_organization/4114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Получить контакт менеджера; запросить условия: MOQ, сроки, K-beauty уход, стики/продукты для губ (Pascual), макияж (Aircos)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">photos/016_anjac.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">Под Парижем (рядом с аэропортом Руасси — Шарль-де-Голль); есть также производство в Азии</t>
@@ -2074,7 +2104,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:W16"/>
+  <dimension ref="A1:W17"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -2546,7 +2576,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="202.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
@@ -2554,7 +2584,7 @@
         <v>116</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>117</v>
@@ -2563,46 +2593,44 @@
         <v>118</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G8" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2" t="s">
         <v>120</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>121</v>
       </c>
       <c r="J8" s="2"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
-      <c r="M8" s="2" t="s">
-        <v>122</v>
-      </c>
+      <c r="M8" s="2"/>
       <c r="N8" s="2"/>
       <c r="O8" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="R8" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="P8" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q8" s="2"/>
-      <c r="R8" s="2" t="s">
+      <c r="S8" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="S8" s="2" t="s">
+      <c r="T8" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="T8" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="U8" s="2"/>
+      <c r="U8" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="V8" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W8" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2613,60 +2641,58 @@
         <v>116</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="F9" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="H9" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="I9" s="2" t="s">
         <v>131</v>
-      </c>
-      <c r="G9" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2" t="s">
-        <v>133</v>
       </c>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
       <c r="M9" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q9" s="2"/>
+      <c r="R9" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="N9" s="2" t="s">
+      <c r="S9" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="O9" s="2" t="s">
+      <c r="T9" s="2" t="s">
         <v>136</v>
-      </c>
-      <c r="P9" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="R9" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="S9" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="T9" s="2" t="s">
-        <v>141</v>
       </c>
       <c r="U9" s="2"/>
       <c r="V9" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W9" s="2" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="180.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
@@ -2674,34 +2700,42 @@
         <v>116</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>60</v>
+        <v>138</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="G10" s="2"/>
+        <v>141</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>142</v>
+      </c>
       <c r="H10" s="2"/>
       <c r="I10" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
-      <c r="N10" s="2"/>
+      <c r="M10" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>145</v>
+      </c>
       <c r="O10" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="P10" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="P10" s="2" t="s">
+      <c r="Q10" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="Q10" s="2"/>
       <c r="R10" s="2" t="s">
         <v>149</v>
       </c>
@@ -2719,7 +2753,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="180.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
@@ -2727,7 +2761,7 @@
         <v>116</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>153</v>
@@ -2738,12 +2772,10 @@
       <c r="F11" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="G11" s="2" t="s">
-        <v>156</v>
-      </c>
+      <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
@@ -2751,27 +2783,27 @@
       <c r="M11" s="2"/>
       <c r="N11" s="2"/>
       <c r="O11" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="P11" s="2" t="s">
         <v>158</v>
-      </c>
-      <c r="P11" s="2" t="s">
-        <v>159</v>
       </c>
       <c r="Q11" s="2"/>
       <c r="R11" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="S11" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="S11" s="2" t="s">
+      <c r="T11" s="2" t="s">
         <v>161</v>
-      </c>
-      <c r="T11" s="2" t="s">
-        <v>162</v>
       </c>
       <c r="U11" s="2"/>
       <c r="V11" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W11" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2785,15 +2817,15 @@
         <v>45</v>
       </c>
       <c r="D12" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="F12" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G12" s="4" t="s">
+      <c r="G12" s="2" t="s">
         <v>166</v>
       </c>
       <c r="H12" s="2"/>
@@ -2846,14 +2878,14 @@
         <v>175</v>
       </c>
       <c r="F13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G13" s="4" t="s">
         <v>176</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>177</v>
       </c>
       <c r="H13" s="2"/>
       <c r="I13" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
@@ -2861,202 +2893,257 @@
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
       <c r="O13" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="P13" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="P13" s="2" t="s">
+      <c r="Q13" s="2"/>
+      <c r="R13" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="Q13" s="2" t="s">
+      <c r="S13" s="2" t="s">
         <v>181</v>
       </c>
-      <c r="R13" s="2" t="s">
+      <c r="T13" s="2" t="s">
         <v>182</v>
-      </c>
-      <c r="S13" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="T13" s="2" t="s">
-        <v>184</v>
       </c>
       <c r="U13" s="2"/>
       <c r="V13" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W13" s="2" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>186</v>
+        <v>116</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>45</v>
       </c>
       <c r="D14" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="G14" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="H14" s="2"/>
+      <c r="I14" s="2" t="s">
         <v>188</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="G14" s="2"/>
-      <c r="H14" s="4" t="s">
-        <v>190</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>191</v>
       </c>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
-      <c r="L14" s="2" t="s">
-        <v>192</v>
-      </c>
+      <c r="L14" s="2"/>
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
       <c r="O14" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="S14" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="P14" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q14" s="2" t="s">
+      <c r="T14" s="2" t="s">
         <v>194</v>
-      </c>
-      <c r="R14" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="S14" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="T14" s="2" t="s">
-        <v>197</v>
       </c>
       <c r="U14" s="2"/>
       <c r="V14" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W14" s="2" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D15" s="2"/>
+      <c r="D15" s="2" t="s">
+        <v>197</v>
+      </c>
       <c r="E15" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="F15" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="F15" s="2" t="s">
+      <c r="G15" s="2"/>
+      <c r="H15" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
       <c r="I15" s="2" t="s">
         <v>201</v>
       </c>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
+      <c r="L15" s="2" t="s">
+        <v>202</v>
+      </c>
       <c r="M15" s="2"/>
       <c r="N15" s="2"/>
-      <c r="O15" s="2"/>
+      <c r="O15" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="P15" s="2" t="s">
         <v>67</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="U15" s="2"/>
       <c r="V15" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W15" s="2" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>208</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="D16" s="2"/>
       <c r="E16" s="2" t="s">
         <v>209</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G16" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="H16" s="4" t="s">
+      <c r="G16" s="2"/>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2" t="s">
         <v>211</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>212</v>
       </c>
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
       <c r="M16" s="2"/>
       <c r="N16" s="2"/>
-      <c r="O16" s="2" t="s">
+      <c r="O16" s="2"/>
+      <c r="P16" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="R16" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="P16" s="2" t="s">
+      <c r="S16" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="Q16" s="2" t="s">
+      <c r="T16" s="2" t="s">
         <v>215</v>
-      </c>
-      <c r="R16" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="S16" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="T16" s="2" t="s">
-        <v>218</v>
       </c>
       <c r="U16" s="2"/>
       <c r="V16" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W16" s="2" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="2" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>219</v>
       </c>
+      <c r="F17" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="P17" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="Q17" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="R17" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="S17" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="T17" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="U17" s="2"/>
+      <c r="V17" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="W17" s="2" t="s">
+        <v>229</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W16"/>
+  <autoFilter ref="A1:W17"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1" display="https://www.dachser.fr"/>
     <hyperlink ref="H2" r:id="rId2" display="https://www.dachser.com/en/cosmetic-logistics"/>
@@ -3065,13 +3152,13 @@
     <hyperlink ref="G4" r:id="rId5" display="https://en.chandogroup.com"/>
     <hyperlink ref="G6" r:id="rId6" display="www.kava.cn"/>
     <hyperlink ref="G7" r:id="rId7" display="www.lamerbeauty.uk ; www.rsgroup.cn"/>
-    <hyperlink ref="G8" r:id="rId8" display="https://www.desjardin.fr"/>
-    <hyperlink ref="H8" r:id="rId9" display="https://www.desjardin.fr/en/categories/cosmetic-packaging"/>
-    <hyperlink ref="G9" r:id="rId10" display="www.effervescence-lab.com"/>
-    <hyperlink ref="G12" r:id="rId11" display="https://simah-cosmetiques.fr"/>
-    <hyperlink ref="H14" r:id="rId12" display="https://welcon.kocca.kr/en/directory/company/cosplan-inc--5601"/>
-    <hyperlink ref="G16" r:id="rId13" display="https://iwasecosfa.eu"/>
-    <hyperlink ref="H16" r:id="rId14" display="https://iwasecosfa-eu.covalo.com/"/>
+    <hyperlink ref="G9" r:id="rId8" display="https://www.desjardin.fr"/>
+    <hyperlink ref="H9" r:id="rId9" display="https://www.desjardin.fr/en/categories/cosmetic-packaging"/>
+    <hyperlink ref="G10" r:id="rId10" display="www.effervescence-lab.com"/>
+    <hyperlink ref="G13" r:id="rId11" display="https://simah-cosmetiques.fr"/>
+    <hyperlink ref="H15" r:id="rId12" display="https://welcon.kocca.kr/en/directory/company/cosplan-inc--5601"/>
+    <hyperlink ref="G17" r:id="rId13" display="https://iwasecosfa.eu"/>
+    <hyperlink ref="H17" r:id="rId14" display="https://iwasecosfa-eu.covalo.com/"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3102,10 +3189,10 @@
         <v>1</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3113,11 +3200,11 @@
         <v>23</v>
       </c>
       <c r="B2" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$16,A2)</f>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$17,A2)</f>
         <v>1</v>
       </c>
       <c r="C2" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$16,A2,Контакты!$U$2:$U$16,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$17,A2,Контакты!$U$2:$U$17,"Высокий")</f>
         <v>0</v>
       </c>
     </row>
@@ -3126,11 +3213,11 @@
         <v>44</v>
       </c>
       <c r="B3" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$16,A3)</f>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$17,A3)</f>
         <v>5</v>
       </c>
       <c r="C3" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$16,A3,Контакты!$U$2:$U$16,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$17,A3,Контакты!$U$2:$U$17,"Высокий")</f>
         <v>3</v>
       </c>
     </row>
@@ -3139,51 +3226,51 @@
         <v>116</v>
       </c>
       <c r="B4" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$16,A4)</f>
-        <v>6</v>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$17,A4)</f>
+        <v>7</v>
       </c>
       <c r="C4" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$16,A4,Контакты!$U$2:$U$16,"Высокий")</f>
-        <v>0</v>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$17,A4,Контакты!$U$2:$U$17,"Высокий")</f>
+        <v>1</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="B5" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$16,A5)</f>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$17,A5)</f>
         <v>2</v>
       </c>
       <c r="C5" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$16,A5,Контакты!$U$2:$U$16,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$17,A5,Контакты!$U$2:$U$17,"Высокий")</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="B6" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$16,A6)</f>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$17,A6)</f>
         <v>1</v>
       </c>
       <c r="C6" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$16,A6,Контакты!$U$2:$U$16,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$17,A6,Контакты!$U$2:$U$17,"Высокий")</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="B7" s="7" t="n">
         <f aca="false">SUM(B2:B6)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" s="7" t="n">
         <f aca="false">SUM(C2:C6)</f>
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3196,7 +3283,7 @@
         <v>2</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>220</v>
+        <v>230</v>
       </c>
       <c r="C9" s="6"/>
     </row>
@@ -3205,8 +3292,8 @@
         <v>45</v>
       </c>
       <c r="B10" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$16,A10)</f>
-        <v>7</v>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$17,A10)</f>
+        <v>8</v>
       </c>
       <c r="C10" s="6"/>
     </row>
@@ -3215,17 +3302,17 @@
         <v>24</v>
       </c>
       <c r="B11" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$16,A11)</f>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$17,A11)</f>
         <v>1</v>
       </c>
       <c r="C11" s="6"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="B12" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$16,A12)</f>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$17,A12)</f>
         <v>1</v>
       </c>
       <c r="C12" s="6"/>
@@ -3235,7 +3322,7 @@
         <v>60</v>
       </c>
       <c r="B13" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$16,A13)</f>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$17,A13)</f>
         <v>3</v>
       </c>
       <c r="C13" s="6"/>
@@ -3245,7 +3332,7 @@
         <v>72</v>
       </c>
       <c r="B14" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$16,A14)</f>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$17,A14)</f>
         <v>3</v>
       </c>
       <c r="C14" s="6"/>
@@ -3280,585 +3367,585 @@
         <v>4</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>224</v>
+        <v>234</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>225</v>
+        <v>235</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>226</v>
+        <v>236</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>228</v>
+        <v>238</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>230</v>
+        <v>240</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>227</v>
+        <v>237</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>232</v>
+        <v>242</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>60</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>233</v>
+        <v>243</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>234</v>
+        <v>244</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>235</v>
+        <v>245</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>238</v>
+        <v>248</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>239</v>
+        <v>249</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>60</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>240</v>
+        <v>250</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>242</v>
+        <v>252</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>60</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="B8" s="9" t="s">
         <v>60</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>60</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
+        <v>261</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>262</v>
+      </c>
+      <c r="D11" s="9" t="s">
         <v>251</v>
-      </c>
-      <c r="B11" s="9" t="s">
-        <v>249</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>252</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="B15" s="9" t="s">
         <v>259</v>
       </c>
-      <c r="B15" s="9" t="s">
-        <v>249</v>
-      </c>
       <c r="C15" s="9" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="B24" s="9" t="s">
+        <v>259</v>
+      </c>
+      <c r="C24" s="9" t="s">
         <v>276</v>
       </c>
-      <c r="B24" s="9" t="s">
-        <v>249</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>266</v>
-      </c>
       <c r="D24" s="9" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="9" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="9" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>229</v>
+        <v>239</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="9" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="9" t="s">
-        <v>292</v>
+        <v>302</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="9" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>241</v>
+        <v>251</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="9" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="9" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="9" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="s">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="9" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="9" t="s">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="C38" s="9"/>
       <c r="D38" s="9" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="9" t="s">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="9" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="8" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="C40" s="9"/>
       <c r="D40" s="9" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="9" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="9" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="9" t="s">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="8" t="s">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="9" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
     </row>
   </sheetData>

--- a/exhibition/contacts.xlsx
+++ b/exhibition/contacts.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="458" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="322">
   <si>
     <t xml:space="preserve">№</t>
   </si>
@@ -609,16 +609,34 @@
     <t xml:space="preserve">Франция (головной офис); заводы во Франции, Испании, Калифорнии (США) и Канаде</t>
   </si>
   <si>
-    <t xml:space="preserve">ANJAC Health &amp; Beauty (группа; на стенде — SICAF и др.)</t>
+    <t xml:space="preserve">ANJAC Health &amp; Beauty (группа) — Aircos Pascual (макияж: пудры, стики, литьевые продукты); на стенде также SICAF</t>
   </si>
   <si>
     <t xml:space="preserve">Cosmetic 360 (секция Formulation)</t>
   </si>
   <si>
+    <t xml:space="preserve">https://www.aircospascual-anjac.com</t>
+  </si>
+  <si>
     <t xml:space="preserve">Крупная семейная французская промышленная группа: разработка и производство под ключ для брендов красоты и здоровья, от сырья до готового продукта. Подразделения: SICAF — уход и премиальные текстуры; Shadeline — дермокосметика; Aircos — пудровая косметика (лидер во Франции); Pascual Cosmétiques — литьевые и жидкие продукты, СТИКИ (помады/бальзамы для губ); Roval Cosmétiques — 2 завода во Франции + Испания; Cosmetix West (Лос-Анджелес); APR Beauty (Торонто). На стенде акцент: «K-Beauty &amp; K-Derma экспертиза для ваших продуктов» (уход в корейском стиле, патчи от прыщей и т.п.)</t>
   </si>
   <si>
-    <t xml:space="preserve">Фото стенда; контакты менеджера — будут</t>
+    <t xml:space="preserve">Cindy MARAIS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Key Account Manager, Aircos Pascual (ANJAC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cmarais@aircospascual.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+33 6 07 63 89 17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aircos Pascual: 151 Boulevard Victor Hugo, 92110 Clichy, Франция</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Визитка Cindy Marais (Aircos Pascual — ANJAC)</t>
   </si>
   <si>
     <t xml:space="preserve">Изучали стенд (уход в стиле K-beauty/K-derma)</t>
@@ -630,10 +648,10 @@
     <t xml:space="preserve">https://pharmaboardroom.com/interviews/interview-aurelien-chaufour-managing-director-anjac-france/ ; https://www.premiumbeautynews.com/fr/sicaf-se-dote-d-un-nouveau,18374 ; https://www.premiumbeautynews.com/en/anjac-h-b-group-keeps-growing-with,16583 ; https://www.gcimagazine.com/brands-products/contract-manufacturing-services/news/22914175/anjac-health-beautys-investment-in-apr-beauty-boosts-beauty-turnkey-capabilities ; https://cosmetic-valley.com/en/directory_organization/4114</t>
   </si>
   <si>
-    <t xml:space="preserve">Получить контакт менеджера; запросить условия: MOQ, сроки, K-beauty уход, стики/продукты для губ (Pascual), макияж (Aircos)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">photos/016_anjac.jpg</t>
+    <t xml:space="preserve">Написать Cindy Marais (cmarais@aircospascual.com): продукты для губ (стики, помады, бальзамы), пудры/макияж, MOQ, сроки, цены; уход K-beauty — через SICAF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">photos/016_anjac.jpg ; photos/016b_anjac_aircos_pascual_card.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">Под Парижем (рядом с аэропортом Руасси — Шарль-де-Голль); есть также производство в Азии</t>
@@ -2595,33 +2613,43 @@
       <c r="F8" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="G8" s="2"/>
+      <c r="G8" s="4" t="s">
+        <v>120</v>
+      </c>
       <c r="H8" s="2"/>
       <c r="I8" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="J8" s="2"/>
+        <v>121</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>122</v>
+      </c>
       <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
+      <c r="L8" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>125</v>
+      </c>
       <c r="O8" s="2" t="s">
-        <v>116</v>
+        <v>126</v>
       </c>
       <c r="P8" s="2" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="U8" s="2" t="s">
         <v>58</v>
@@ -2630,7 +2658,7 @@
         <v>42</v>
       </c>
       <c r="W8" s="2" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2644,52 +2672,52 @@
         <v>72</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>27</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="H9" s="4" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
       <c r="J9" s="2"/>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
       <c r="M9" s="2" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="P9" s="2" t="s">
         <v>67</v>
       </c>
       <c r="Q9" s="2"/>
       <c r="R9" s="2" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="U9" s="2"/>
       <c r="V9" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W9" s="2" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2700,57 +2728,57 @@
         <v>116</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="G10" s="4" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="2" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="J10" s="2"/>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
       <c r="M10" s="2" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="O10" s="2" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="U10" s="2"/>
       <c r="V10" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W10" s="2" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="180.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2764,18 +2792,18 @@
         <v>60</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="G11" s="2"/>
       <c r="H11" s="2"/>
       <c r="I11" s="2" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="J11" s="2"/>
       <c r="K11" s="2"/>
@@ -2783,27 +2811,27 @@
       <c r="M11" s="2"/>
       <c r="N11" s="2"/>
       <c r="O11" s="2" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="Q11" s="2"/>
       <c r="R11" s="2" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="U11" s="2"/>
       <c r="V11" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W11" s="2" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2817,20 +2845,20 @@
         <v>45</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="H12" s="2"/>
       <c r="I12" s="2" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
@@ -2838,27 +2866,27 @@
       <c r="M12" s="2"/>
       <c r="N12" s="2"/>
       <c r="O12" s="2" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="Q12" s="2"/>
       <c r="R12" s="2" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="U12" s="2"/>
       <c r="V12" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2872,20 +2900,20 @@
         <v>45</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>27</v>
       </c>
       <c r="G13" s="4" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="H13" s="2"/>
       <c r="I13" s="2" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
@@ -2893,27 +2921,27 @@
       <c r="M13" s="2"/>
       <c r="N13" s="2"/>
       <c r="O13" s="2" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" s="2" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="U13" s="2"/>
       <c r="V13" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W13" s="2" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2927,20 +2955,20 @@
         <v>45</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="H14" s="2"/>
       <c r="I14" s="2" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="J14" s="2"/>
       <c r="K14" s="2"/>
@@ -2948,29 +2976,29 @@
       <c r="M14" s="2"/>
       <c r="N14" s="2"/>
       <c r="O14" s="2" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="U14" s="2"/>
       <c r="V14" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W14" s="2" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2978,58 +3006,58 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>45</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="G15" s="2"/>
       <c r="H15" s="4" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
       <c r="L15" s="2" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="M15" s="2"/>
       <c r="N15" s="2"/>
       <c r="O15" s="2" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="P15" s="2" t="s">
         <v>67</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="U15" s="2"/>
       <c r="V15" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W15" s="2" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3037,22 +3065,22 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>45</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="G16" s="2"/>
       <c r="H16" s="2"/>
       <c r="I16" s="2" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
@@ -3064,23 +3092,23 @@
         <v>67</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="T16" s="2" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="U16" s="2"/>
       <c r="V16" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W16" s="2" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3088,28 +3116,28 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>60</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>27</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="H17" s="4" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
@@ -3117,29 +3145,29 @@
       <c r="M17" s="2"/>
       <c r="N17" s="2"/>
       <c r="O17" s="2" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="R17" s="2" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="T17" s="2" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="U17" s="2"/>
       <c r="V17" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W17" s="2" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
     </row>
   </sheetData>
@@ -3152,13 +3180,14 @@
     <hyperlink ref="G4" r:id="rId5" display="https://en.chandogroup.com"/>
     <hyperlink ref="G6" r:id="rId6" display="www.kava.cn"/>
     <hyperlink ref="G7" r:id="rId7" display="www.lamerbeauty.uk ; www.rsgroup.cn"/>
-    <hyperlink ref="G9" r:id="rId8" display="https://www.desjardin.fr"/>
-    <hyperlink ref="H9" r:id="rId9" display="https://www.desjardin.fr/en/categories/cosmetic-packaging"/>
-    <hyperlink ref="G10" r:id="rId10" display="www.effervescence-lab.com"/>
-    <hyperlink ref="G13" r:id="rId11" display="https://simah-cosmetiques.fr"/>
-    <hyperlink ref="H15" r:id="rId12" display="https://welcon.kocca.kr/en/directory/company/cosplan-inc--5601"/>
-    <hyperlink ref="G17" r:id="rId13" display="https://iwasecosfa.eu"/>
-    <hyperlink ref="H17" r:id="rId14" display="https://iwasecosfa-eu.covalo.com/"/>
+    <hyperlink ref="G8" r:id="rId8" display="https://www.aircospascual-anjac.com"/>
+    <hyperlink ref="G9" r:id="rId9" display="https://www.desjardin.fr"/>
+    <hyperlink ref="H9" r:id="rId10" display="https://www.desjardin.fr/en/categories/cosmetic-packaging"/>
+    <hyperlink ref="G10" r:id="rId11" display="www.effervescence-lab.com"/>
+    <hyperlink ref="G13" r:id="rId12" display="https://simah-cosmetiques.fr"/>
+    <hyperlink ref="H15" r:id="rId13" display="https://welcon.kocca.kr/en/directory/company/cosplan-inc--5601"/>
+    <hyperlink ref="G17" r:id="rId14" display="https://iwasecosfa.eu"/>
+    <hyperlink ref="H17" r:id="rId15" display="https://iwasecosfa-eu.covalo.com/"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3167,7 +3196,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId15"/>
+  <drawing r:id="rId16"/>
 </worksheet>
 </file>
 
@@ -3189,10 +3218,10 @@
         <v>1</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3236,7 +3265,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="B5" s="6" t="n">
         <f aca="false">COUNTIF(Контакты!$B$2:$B$17,A5)</f>
@@ -3249,7 +3278,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="B6" s="6" t="n">
         <f aca="false">COUNTIF(Контакты!$B$2:$B$17,A6)</f>
@@ -3262,7 +3291,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="B7" s="7" t="n">
         <f aca="false">SUM(B2:B6)</f>
@@ -3283,7 +3312,7 @@
         <v>2</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="C9" s="6"/>
     </row>
@@ -3309,7 +3338,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="B12" s="6" t="n">
         <f aca="false">COUNTIF(Контакты!$C$2:$C$17,A12)</f>
@@ -3367,585 +3396,585 @@
         <v>4</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>60</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>60</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>60</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="B8" s="9" t="s">
         <v>60</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>60</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
+        <v>271</v>
+      </c>
+      <c r="B13" s="9" t="s">
         <v>265</v>
       </c>
-      <c r="B13" s="9" t="s">
-        <v>259</v>
-      </c>
       <c r="C13" s="9" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="9" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="9" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="9" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="9" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="9" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="9" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="9" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="9" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="9" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="9" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="C38" s="9"/>
       <c r="D38" s="9" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="9" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="9" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="8" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="C40" s="9"/>
       <c r="D40" s="9" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="9" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="9" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="9" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="8" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="9" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
     </row>
   </sheetData>

--- a/exhibition/contacts.xlsx
+++ b/exhibition/contacts.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Стенд INPD (Китай)" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Контакты!$A$1:$W$18</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Контакты!$A$1:$W$19</definedName>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Стенд INPD (Китай)'!$A$1:$D$43</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="337">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="353">
   <si>
     <t xml:space="preserve">№</t>
   </si>
@@ -838,6 +838,54 @@
   </si>
   <si>
     <t xml:space="preserve">photos/009_biotic_phocea.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Лантийи (под Лионом), Франция; также Шатель-Сен-Дени (Швейцария) и Ржичани (под Прагой, Чехия)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MS BEAUTiLAB (группа Marvinpac)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cosmetic 360, стенд DC23 (Innovation Route — Formulation)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.msbeautilab.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Контрактное производство под ключ: декоративная косметика (цветные продукты, пудры, ПОМАДЫ/продукты для губ) и уход (эмульсии). Готовые формулы (ready-to-go) и разработка на заказ; формула, упаковка, производство, поддержка в маркетинге и дизайне. Новинка на стенде: веганский плампер для губ со спикулами (мгновенное увеличение объёма, 5-в-1 подготовка губ); шёлковые патчи для глаз</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tatyana DUBUQUOY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Business Manager Senior</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tdubuquoy@msbeautilab.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+33 6 68 93 00 22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">124 rue de Charpenay, 69210 Lentilly, Франция</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Визитка «Every bestseller has a beginning»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Производство декоративной косметики</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Основана в 1964 г. Группа Marvinpac: 2 направления — Marvinpac (еда/напитки) и MS Beautilab (макияж и уход). Оборот группы &gt; 100 млн €, мощность &gt; 6 000 т. Работали с LVMH и L'Oréal. С 2024 г. фокус на эмульсиях, пудрах и помадах. Есть офис на восточном побережье США, США &gt; 20% выручки. Имя Tatyana — возможно, говорит по-русски, уточнить.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://bioalps.org/organizations/ms-beautilab-sa ; https://www.premiumbeautynews.com/fr/la-k-beauty-nous-inspire-nous-la,26511 ; https://www.premiumbeautynews.com/fr/ms-beautilab-engage-sa,18742 ; https://www.industries-cosmetiques.fr/en/?p=10828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Написать Tatyana Dubuquoy: продукты для губ (помады, плампер), пудры, готовые формулы, MOQ, сроки, цены, возможность поставок в Россию</t>
+  </si>
+  <si>
+    <t xml:space="preserve">photos/018_ms_beautilab_card.jpg ; photos/018b_ms_beautilab_stand.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">Мейссак (Коррез), Новая Аквитания; второй сайт — Юссак</t>
@@ -2167,7 +2215,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:W18"/>
+  <dimension ref="A1:W19"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -3001,7 +3049,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
@@ -3018,42 +3066,54 @@
         <v>196</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>27</v>
+        <v>197</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H14" s="2"/>
       <c r="I14" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="J14" s="2"/>
+        <v>199</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>200</v>
+      </c>
       <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2"/>
+      <c r="L14" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>203</v>
+      </c>
       <c r="O14" s="2" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="Q14" s="2"/>
+        <v>205</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>206</v>
+      </c>
       <c r="R14" s="2" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="U14" s="2"/>
+        <v>209</v>
+      </c>
+      <c r="U14" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="V14" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W14" s="2" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3067,20 +3127,20 @@
         <v>45</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>208</v>
+        <v>27</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>213</v>
       </c>
       <c r="H15" s="2"/>
       <c r="I15" s="2" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
@@ -3088,202 +3148,257 @@
       <c r="M15" s="2"/>
       <c r="N15" s="2"/>
       <c r="O15" s="2" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="Q15" s="2" t="s">
-        <v>212</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="Q15" s="2"/>
       <c r="R15" s="2" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="U15" s="2"/>
       <c r="V15" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W15" s="2" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>217</v>
+        <v>131</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>45</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="G16" s="2"/>
-      <c r="H16" s="4" t="s">
-        <v>221</v>
-      </c>
+        <v>223</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="H16" s="2"/>
       <c r="I16" s="2" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
-      <c r="L16" s="2" t="s">
-        <v>223</v>
-      </c>
+      <c r="L16" s="2"/>
       <c r="M16" s="2"/>
       <c r="N16" s="2"/>
       <c r="O16" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>67</v>
+        <v>227</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="T16" s="2" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="U16" s="2"/>
       <c r="V16" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W16" s="2" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D17" s="2"/>
+      <c r="D17" s="2" t="s">
+        <v>234</v>
+      </c>
       <c r="E17" s="2" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
+      <c r="H17" s="4" t="s">
+        <v>237</v>
+      </c>
       <c r="I17" s="2" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
-      <c r="L17" s="2"/>
+      <c r="L17" s="2" t="s">
+        <v>239</v>
+      </c>
       <c r="M17" s="2"/>
       <c r="N17" s="2"/>
-      <c r="O17" s="2"/>
+      <c r="O17" s="2" t="s">
+        <v>240</v>
+      </c>
       <c r="P17" s="2" t="s">
         <v>67</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="R17" s="2" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="T17" s="2" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="U17" s="2"/>
       <c r="V17" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W17" s="2" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>239</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="D18" s="2"/>
       <c r="E18" s="2" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G18" s="4" t="s">
-        <v>241</v>
-      </c>
-      <c r="H18" s="4" t="s">
-        <v>242</v>
-      </c>
+        <v>247</v>
+      </c>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
       <c r="I18" s="2" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
       <c r="N18" s="2"/>
-      <c r="O18" s="2" t="s">
-        <v>244</v>
-      </c>
+      <c r="O18" s="2"/>
       <c r="P18" s="2" t="s">
-        <v>245</v>
+        <v>67</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="R18" s="2" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="S18" s="2" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="T18" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="U18" s="2"/>
       <c r="V18" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W18" s="2" t="s">
-        <v>250</v>
+        <v>253</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="R19" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="S19" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="T19" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="U19" s="2"/>
+      <c r="V19" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="W19" s="2" t="s">
+        <v>266</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W18"/>
+  <autoFilter ref="A1:W19"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1" display="https://www.dachser.fr"/>
     <hyperlink ref="H2" r:id="rId2" display="https://www.dachser.com/en/cosmetic-logistics"/>
@@ -3297,10 +3412,11 @@
     <hyperlink ref="G10" r:id="rId10" display="https://www.desjardin.fr"/>
     <hyperlink ref="H10" r:id="rId11" display="https://www.desjardin.fr/en/categories/cosmetic-packaging"/>
     <hyperlink ref="G11" r:id="rId12" display="www.effervescence-lab.com"/>
-    <hyperlink ref="G14" r:id="rId13" display="https://simah-cosmetiques.fr"/>
-    <hyperlink ref="H16" r:id="rId14" display="https://welcon.kocca.kr/en/directory/company/cosplan-inc--5601"/>
-    <hyperlink ref="G18" r:id="rId15" display="https://iwasecosfa.eu"/>
-    <hyperlink ref="H18" r:id="rId16" display="https://iwasecosfa-eu.covalo.com/"/>
+    <hyperlink ref="G14" r:id="rId13" display="https://www.msbeautilab.com"/>
+    <hyperlink ref="G15" r:id="rId14" display="https://simah-cosmetiques.fr"/>
+    <hyperlink ref="H17" r:id="rId15" display="https://welcon.kocca.kr/en/directory/company/cosplan-inc--5601"/>
+    <hyperlink ref="G19" r:id="rId16" display="https://iwasecosfa.eu"/>
+    <hyperlink ref="H19" r:id="rId17" display="https://iwasecosfa-eu.covalo.com/"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3309,7 +3425,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId17"/>
+  <drawing r:id="rId18"/>
 </worksheet>
 </file>
 
@@ -3331,10 +3447,10 @@
         <v>1</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>251</v>
+        <v>267</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>252</v>
+        <v>268</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3342,11 +3458,11 @@
         <v>23</v>
       </c>
       <c r="B2" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$18,A2)</f>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$19,A2)</f>
         <v>1</v>
       </c>
       <c r="C2" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$18,A2,Контакты!$U$2:$U$18,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$19,A2,Контакты!$U$2:$U$19,"Высокий")</f>
         <v>0</v>
       </c>
     </row>
@@ -3355,11 +3471,11 @@
         <v>44</v>
       </c>
       <c r="B3" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$18,A3)</f>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$19,A3)</f>
         <v>6</v>
       </c>
       <c r="C3" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$18,A3,Контакты!$U$2:$U$18,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$19,A3,Контакты!$U$2:$U$19,"Высокий")</f>
         <v>4</v>
       </c>
     </row>
@@ -3368,51 +3484,51 @@
         <v>131</v>
       </c>
       <c r="B4" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$18,A4)</f>
-        <v>7</v>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$19,A4)</f>
+        <v>8</v>
       </c>
       <c r="C4" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$18,A4,Контакты!$U$2:$U$18,"Высокий")</f>
-        <v>1</v>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$19,A4,Контакты!$U$2:$U$19,"Высокий")</f>
+        <v>2</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="B5" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$18,A5)</f>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$19,A5)</f>
         <v>2</v>
       </c>
       <c r="C5" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$18,A5,Контакты!$U$2:$U$18,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$19,A5,Контакты!$U$2:$U$19,"Высокий")</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>238</v>
+        <v>254</v>
       </c>
       <c r="B6" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$18,A6)</f>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$19,A6)</f>
         <v>1</v>
       </c>
       <c r="C6" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$18,A6,Контакты!$U$2:$U$18,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$19,A6,Контакты!$U$2:$U$19,"Высокий")</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>253</v>
+        <v>269</v>
       </c>
       <c r="B7" s="7" t="n">
         <f aca="false">SUM(B2:B6)</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" s="7" t="n">
         <f aca="false">SUM(C2:C6)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3425,7 +3541,7 @@
         <v>2</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>251</v>
+        <v>267</v>
       </c>
       <c r="C9" s="6"/>
     </row>
@@ -3434,8 +3550,8 @@
         <v>45</v>
       </c>
       <c r="B10" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$18,A10)</f>
-        <v>8</v>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$19,A10)</f>
+        <v>9</v>
       </c>
       <c r="C10" s="6"/>
     </row>
@@ -3444,7 +3560,7 @@
         <v>24</v>
       </c>
       <c r="B11" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$18,A11)</f>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$19,A11)</f>
         <v>1</v>
       </c>
       <c r="C11" s="6"/>
@@ -3454,7 +3570,7 @@
         <v>159</v>
       </c>
       <c r="B12" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$18,A12)</f>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$19,A12)</f>
         <v>1</v>
       </c>
       <c r="C12" s="6"/>
@@ -3464,7 +3580,7 @@
         <v>60</v>
       </c>
       <c r="B13" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$18,A13)</f>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$19,A13)</f>
         <v>3</v>
       </c>
       <c r="C13" s="6"/>
@@ -3474,7 +3590,7 @@
         <v>72</v>
       </c>
       <c r="B14" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$18,A14)</f>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$19,A14)</f>
         <v>4</v>
       </c>
       <c r="C14" s="6"/>
@@ -3509,585 +3625,585 @@
         <v>4</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>254</v>
+        <v>270</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>255</v>
+        <v>271</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>256</v>
+        <v>272</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>257</v>
+        <v>273</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>258</v>
+        <v>274</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>259</v>
+        <v>275</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>260</v>
+        <v>276</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>261</v>
+        <v>277</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>258</v>
+        <v>274</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>262</v>
+        <v>278</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>260</v>
+        <v>276</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>263</v>
+        <v>279</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>60</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>264</v>
+        <v>280</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>265</v>
+        <v>281</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>266</v>
+        <v>282</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>267</v>
+        <v>283</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>268</v>
+        <v>284</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>269</v>
+        <v>285</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>270</v>
+        <v>286</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>60</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>271</v>
+        <v>287</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>272</v>
+        <v>288</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>273</v>
+        <v>289</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>60</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>274</v>
+        <v>290</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>272</v>
+        <v>288</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>275</v>
+        <v>291</v>
       </c>
       <c r="B8" s="9" t="s">
         <v>60</v>
       </c>
       <c r="C8" s="9" t="s">
+        <v>292</v>
+      </c>
+      <c r="D8" s="9" t="s">
         <v>276</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>260</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>277</v>
+        <v>293</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>60</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>278</v>
+        <v>294</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>260</v>
+        <v>276</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>279</v>
+        <v>295</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>280</v>
+        <v>296</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>281</v>
+        <v>297</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>272</v>
+        <v>288</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>282</v>
+        <v>298</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>280</v>
+        <v>296</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>283</v>
+        <v>299</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>272</v>
+        <v>288</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>284</v>
+        <v>300</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>280</v>
+        <v>296</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>285</v>
+        <v>301</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>272</v>
+        <v>288</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>280</v>
+        <v>296</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>272</v>
+        <v>288</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
+        <v>304</v>
+      </c>
+      <c r="B14" s="9" t="s">
+        <v>296</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>305</v>
+      </c>
+      <c r="D14" s="9" t="s">
         <v>288</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>280</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>289</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>272</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>290</v>
+        <v>306</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>280</v>
+        <v>296</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>291</v>
+        <v>307</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>272</v>
+        <v>288</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>292</v>
+        <v>308</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>280</v>
+        <v>296</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>293</v>
+        <v>309</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>272</v>
+        <v>288</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>294</v>
+        <v>310</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>280</v>
+        <v>296</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>295</v>
+        <v>311</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>260</v>
+        <v>276</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
+        <v>312</v>
+      </c>
+      <c r="B18" s="9" t="s">
         <v>296</v>
       </c>
-      <c r="B18" s="9" t="s">
-        <v>280</v>
-      </c>
       <c r="C18" s="9" t="s">
-        <v>297</v>
+        <v>313</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>272</v>
+        <v>288</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>298</v>
+        <v>314</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>280</v>
+        <v>296</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>299</v>
+        <v>315</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>272</v>
+        <v>288</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>300</v>
+        <v>316</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>280</v>
+        <v>296</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>299</v>
+        <v>315</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>272</v>
+        <v>288</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>301</v>
+        <v>317</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>280</v>
+        <v>296</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>302</v>
+        <v>318</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>260</v>
+        <v>276</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>303</v>
+        <v>319</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>280</v>
+        <v>296</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>304</v>
+        <v>320</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>272</v>
+        <v>288</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>305</v>
+        <v>321</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>280</v>
+        <v>296</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>306</v>
+        <v>322</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>260</v>
+        <v>276</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>307</v>
+        <v>323</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>280</v>
+        <v>296</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>297</v>
+        <v>313</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>272</v>
+        <v>288</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>308</v>
+        <v>324</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>280</v>
+        <v>296</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>309</v>
+        <v>325</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>272</v>
+        <v>288</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="9" t="s">
-        <v>310</v>
+        <v>326</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>280</v>
+        <v>296</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>299</v>
+        <v>315</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>272</v>
+        <v>288</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="9" t="s">
-        <v>311</v>
+        <v>327</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>280</v>
+        <v>296</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>312</v>
+        <v>328</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>272</v>
+        <v>288</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="s">
-        <v>313</v>
+        <v>329</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>280</v>
+        <v>296</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>314</v>
+        <v>330</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>272</v>
+        <v>288</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="s">
-        <v>315</v>
+        <v>331</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>280</v>
+        <v>296</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>316</v>
+        <v>332</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>272</v>
+        <v>288</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="s">
-        <v>317</v>
+        <v>333</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>280</v>
+        <v>296</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>318</v>
+        <v>334</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>260</v>
+        <v>276</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="s">
-        <v>319</v>
+        <v>335</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>280</v>
+        <v>296</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>320</v>
+        <v>336</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>260</v>
+        <v>276</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="9" t="s">
-        <v>321</v>
+        <v>337</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>280</v>
+        <v>296</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>322</v>
+        <v>338</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>272</v>
+        <v>288</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="9" t="s">
-        <v>323</v>
+        <v>339</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>280</v>
+        <v>296</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>299</v>
+        <v>315</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>272</v>
+        <v>288</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="9" t="s">
-        <v>324</v>
+        <v>340</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>280</v>
+        <v>296</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>325</v>
+        <v>341</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>272</v>
+        <v>288</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="9" t="s">
-        <v>326</v>
+        <v>342</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>267</v>
+        <v>283</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="9" t="s">
-        <v>327</v>
+        <v>343</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="s">
-        <v>328</v>
+        <v>344</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>267</v>
+        <v>283</v>
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="9" t="s">
-        <v>327</v>
+        <v>343</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="s">
-        <v>329</v>
+        <v>345</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>267</v>
+        <v>283</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="9" t="s">
-        <v>327</v>
+        <v>343</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="9" t="s">
-        <v>330</v>
+        <v>346</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>267</v>
+        <v>283</v>
       </c>
       <c r="C38" s="9"/>
       <c r="D38" s="9" t="s">
-        <v>327</v>
+        <v>343</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="9" t="s">
-        <v>331</v>
+        <v>347</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>267</v>
+        <v>283</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="9" t="s">
-        <v>327</v>
+        <v>343</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="8" t="s">
-        <v>332</v>
+        <v>348</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>267</v>
+        <v>283</v>
       </c>
       <c r="C40" s="9"/>
       <c r="D40" s="9" t="s">
-        <v>327</v>
+        <v>343</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="9" t="s">
-        <v>333</v>
+        <v>349</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>267</v>
+        <v>283</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="9" t="s">
-        <v>327</v>
+        <v>343</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="9" t="s">
-        <v>334</v>
+        <v>350</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>267</v>
+        <v>283</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>335</v>
+        <v>351</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>327</v>
+        <v>343</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="8" t="s">
-        <v>336</v>
+        <v>352</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>267</v>
+        <v>283</v>
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="9" t="s">
-        <v>327</v>
+        <v>343</v>
       </c>
     </row>
   </sheetData>

--- a/exhibition/contacts.xlsx
+++ b/exhibition/contacts.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Стенд INPD (Китай)" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Контакты!$A$1:$W$19</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Контакты!$A$1:$W$20</definedName>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Стенд INPD (Китай)'!$A$1:$D$43</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="353">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="368">
   <si>
     <t xml:space="preserve">№</t>
   </si>
@@ -805,6 +805,51 @@
   </si>
   <si>
     <t xml:space="preserve">photos/010_formulance.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Форкалькье (Альпы Верхнего Прованса), Прованс; второй сайт — Валансоль</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Laboratoires BEA (группа Condat)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.laboratoiresbea.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Контрактное производство (façonnier) под ключ или по этапам — от концепции до производства: ПАРФЮМЕРИЯ, мыло, жидкая и твёрдая косметика, органическая и обычная. На стенде — линейка ухода за волосами (маски, кондиционеры, сыворотки)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anouck HIVER (вписана от руки на визитке Laurine Guillaume)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">По визитке: Laurine GUILLAUME — Area Sales Manager (зачёркнуто, заменено на Anouck Hiver)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ahiver@laboratoiresbea.com ; lguillaume@laboratoiresbea.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Офис: +33 4 92 75 37 69 ; мобильный Laurine Guillaume: +33 6 62 17 58 71</t>
+  </si>
+  <si>
+    <t xml:space="preserve">265 Av. des Châlus, 04300 Forcalquier, Франция</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Визитка Laurine Guillaume, от руки вписано: Anouck HIVER, ahiver@laboratoiresbea.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Лаборатория во Франции по производству парфюма. ВНИМАНИЕ: очень долгие сроки производства</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Оборот ~22 млн € (2024), 100–199 сотрудников. С 2008 г. в группе Condat. В 2012 купили Laboratoires SCV (сайт в Валансоли). Сертификаты ISO 9001 и ISO 22716 (GMP). Раньше ~65% продаж шло на экспорт (данные старые).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://madeinmarseille.net/environnement/25019-filiere-cosmetique-provence/ ; https://www.xerfi.com/etudes-par-entreprise/laboratoires-bea_383819836 ; https://exhibitor.beautyworldme.com/exhibitor-search-en/exhibitor-search.detail.html/laboratoires-bea.html ; https://www.premiumbeautynews.com/en/laboratoires-bea-focus-on-growth,5593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Написать Anouck Hiver: точные сроки производства парфюма, MOQ, цены. Сроки — главный минус, сравнить с другими вариантами</t>
+  </si>
+  <si>
+    <t xml:space="preserve">photos/019_laboratoires_bea.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">Марсель</t>
@@ -2215,7 +2260,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:W19"/>
+  <dimension ref="A1:W20"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -2994,7 +3039,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
@@ -3011,45 +3056,55 @@
         <v>185</v>
       </c>
       <c r="F13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G13" s="4" t="s">
         <v>186</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>187</v>
       </c>
       <c r="H13" s="2"/>
       <c r="I13" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="J13" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="J13" s="2"/>
       <c r="K13" s="2"/>
-      <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2"/>
+      <c r="L13" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>191</v>
+      </c>
       <c r="O13" s="2" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="Q13" s="2"/>
+        <v>193</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>194</v>
+      </c>
       <c r="R13" s="2" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="U13" s="2"/>
       <c r="V13" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W13" s="2" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
@@ -3060,63 +3115,51 @@
         <v>45</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>198</v>
+        <v>201</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>202</v>
       </c>
       <c r="H14" s="2"/>
       <c r="I14" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>200</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="J14" s="2"/>
       <c r="K14" s="2"/>
-      <c r="L14" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="M14" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="N14" s="2" t="s">
-        <v>203</v>
-      </c>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="2"/>
       <c r="O14" s="2" t="s">
         <v>204</v>
       </c>
       <c r="P14" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="Q14" s="2" t="s">
+      <c r="Q14" s="2"/>
+      <c r="R14" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="R14" s="2" t="s">
+      <c r="S14" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="S14" s="2" t="s">
+      <c r="T14" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="T14" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="U14" s="2" t="s">
-        <v>58</v>
-      </c>
+      <c r="U14" s="2"/>
       <c r="V14" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W14" s="2" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
@@ -3127,13 +3170,13 @@
         <v>45</v>
       </c>
       <c r="D15" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="F15" s="2" t="s">
         <v>212</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="G15" s="4" t="s">
         <v>213</v>
@@ -3142,33 +3185,45 @@
       <c r="I15" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="J15" s="2"/>
+      <c r="J15" s="2" t="s">
+        <v>215</v>
+      </c>
       <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
-      <c r="N15" s="2"/>
+      <c r="L15" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>218</v>
+      </c>
       <c r="O15" s="2" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="Q15" s="2"/>
+        <v>220</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>221</v>
+      </c>
       <c r="R15" s="2" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="U15" s="2"/>
+        <v>224</v>
+      </c>
+      <c r="U15" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="V15" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W15" s="2" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3182,20 +3237,20 @@
         <v>45</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>224</v>
+        <v>27</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>228</v>
       </c>
       <c r="H16" s="2"/>
       <c r="I16" s="2" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
@@ -3203,202 +3258,257 @@
       <c r="M16" s="2"/>
       <c r="N16" s="2"/>
       <c r="O16" s="2" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="Q16" s="2" t="s">
-        <v>228</v>
-      </c>
+        <v>231</v>
+      </c>
+      <c r="Q16" s="2"/>
       <c r="R16" s="2" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="T16" s="2" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="U16" s="2"/>
       <c r="V16" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W16" s="2" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>233</v>
+        <v>131</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>45</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="G17" s="2"/>
-      <c r="H17" s="4" t="s">
-        <v>237</v>
-      </c>
+        <v>238</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="H17" s="2"/>
       <c r="I17" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
-      <c r="L17" s="2" t="s">
-        <v>239</v>
-      </c>
+      <c r="L17" s="2"/>
       <c r="M17" s="2"/>
       <c r="N17" s="2"/>
       <c r="O17" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>67</v>
+        <v>242</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="R17" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="T17" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="U17" s="2"/>
       <c r="V17" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W17" s="2" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>233</v>
+        <v>248</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D18" s="2"/>
+      <c r="D18" s="2" t="s">
+        <v>249</v>
+      </c>
       <c r="E18" s="2" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
+      <c r="H18" s="4" t="s">
+        <v>252</v>
+      </c>
       <c r="I18" s="2" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
-      <c r="L18" s="2"/>
+      <c r="L18" s="2" t="s">
+        <v>254</v>
+      </c>
       <c r="M18" s="2"/>
       <c r="N18" s="2"/>
-      <c r="O18" s="2"/>
+      <c r="O18" s="2" t="s">
+        <v>255</v>
+      </c>
       <c r="P18" s="2" t="s">
         <v>67</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>249</v>
+        <v>256</v>
       </c>
       <c r="R18" s="2" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="S18" s="2" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="T18" s="2" t="s">
-        <v>252</v>
+        <v>259</v>
       </c>
       <c r="U18" s="2"/>
       <c r="V18" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W18" s="2" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>255</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="D19" s="2"/>
       <c r="E19" s="2" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>257</v>
-      </c>
-      <c r="H19" s="4" t="s">
-        <v>258</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
       <c r="I19" s="2" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
       <c r="N19" s="2"/>
-      <c r="O19" s="2" t="s">
-        <v>260</v>
-      </c>
+      <c r="O19" s="2"/>
       <c r="P19" s="2" t="s">
-        <v>261</v>
+        <v>67</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="R19" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="T19" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="U19" s="2"/>
       <c r="V19" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W19" s="2" t="s">
-        <v>266</v>
+        <v>268</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="2" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="Q20" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="R20" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="S20" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="T20" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="U20" s="2"/>
+      <c r="V20" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="W20" s="2" t="s">
+        <v>281</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W19"/>
+  <autoFilter ref="A1:W20"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1" display="https://www.dachser.fr"/>
     <hyperlink ref="H2" r:id="rId2" display="https://www.dachser.com/en/cosmetic-logistics"/>
@@ -3412,11 +3522,12 @@
     <hyperlink ref="G10" r:id="rId10" display="https://www.desjardin.fr"/>
     <hyperlink ref="H10" r:id="rId11" display="https://www.desjardin.fr/en/categories/cosmetic-packaging"/>
     <hyperlink ref="G11" r:id="rId12" display="www.effervescence-lab.com"/>
-    <hyperlink ref="G14" r:id="rId13" display="https://www.msbeautilab.com"/>
-    <hyperlink ref="G15" r:id="rId14" display="https://simah-cosmetiques.fr"/>
-    <hyperlink ref="H17" r:id="rId15" display="https://welcon.kocca.kr/en/directory/company/cosplan-inc--5601"/>
-    <hyperlink ref="G19" r:id="rId16" display="https://iwasecosfa.eu"/>
-    <hyperlink ref="H19" r:id="rId17" display="https://iwasecosfa-eu.covalo.com/"/>
+    <hyperlink ref="G13" r:id="rId13" display="https://www.laboratoiresbea.com"/>
+    <hyperlink ref="G15" r:id="rId14" display="https://www.msbeautilab.com"/>
+    <hyperlink ref="G16" r:id="rId15" display="https://simah-cosmetiques.fr"/>
+    <hyperlink ref="H18" r:id="rId16" display="https://welcon.kocca.kr/en/directory/company/cosplan-inc--5601"/>
+    <hyperlink ref="G20" r:id="rId17" display="https://iwasecosfa.eu"/>
+    <hyperlink ref="H20" r:id="rId18" display="https://iwasecosfa-eu.covalo.com/"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3425,7 +3536,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId18"/>
+  <drawing r:id="rId19"/>
 </worksheet>
 </file>
 
@@ -3447,10 +3558,10 @@
         <v>1</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>267</v>
+        <v>282</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>268</v>
+        <v>283</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3458,11 +3569,11 @@
         <v>23</v>
       </c>
       <c r="B2" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$19,A2)</f>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$20,A2)</f>
         <v>1</v>
       </c>
       <c r="C2" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$19,A2,Контакты!$U$2:$U$19,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$20,A2,Контакты!$U$2:$U$20,"Высокий")</f>
         <v>0</v>
       </c>
     </row>
@@ -3471,11 +3582,11 @@
         <v>44</v>
       </c>
       <c r="B3" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$19,A3)</f>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$20,A3)</f>
         <v>6</v>
       </c>
       <c r="C3" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$19,A3,Контакты!$U$2:$U$19,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$20,A3,Контакты!$U$2:$U$20,"Высокий")</f>
         <v>4</v>
       </c>
     </row>
@@ -3484,47 +3595,47 @@
         <v>131</v>
       </c>
       <c r="B4" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$19,A4)</f>
-        <v>8</v>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$20,A4)</f>
+        <v>9</v>
       </c>
       <c r="C4" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$19,A4,Контакты!$U$2:$U$19,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$20,A4,Контакты!$U$2:$U$20,"Высокий")</f>
         <v>2</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>233</v>
+        <v>248</v>
       </c>
       <c r="B5" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$19,A5)</f>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$20,A5)</f>
         <v>2</v>
       </c>
       <c r="C5" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$19,A5,Контакты!$U$2:$U$19,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$20,A5,Контакты!$U$2:$U$20,"Высокий")</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>254</v>
+        <v>269</v>
       </c>
       <c r="B6" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$19,A6)</f>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$20,A6)</f>
         <v>1</v>
       </c>
       <c r="C6" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$19,A6,Контакты!$U$2:$U$19,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$20,A6,Контакты!$U$2:$U$20,"Высокий")</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="7" t="s">
-        <v>269</v>
+        <v>284</v>
       </c>
       <c r="B7" s="7" t="n">
         <f aca="false">SUM(B2:B6)</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" s="7" t="n">
         <f aca="false">SUM(C2:C6)</f>
@@ -3541,7 +3652,7 @@
         <v>2</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>267</v>
+        <v>282</v>
       </c>
       <c r="C9" s="6"/>
     </row>
@@ -3550,8 +3661,8 @@
         <v>45</v>
       </c>
       <c r="B10" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$19,A10)</f>
-        <v>9</v>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$20,A10)</f>
+        <v>10</v>
       </c>
       <c r="C10" s="6"/>
     </row>
@@ -3560,7 +3671,7 @@
         <v>24</v>
       </c>
       <c r="B11" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$19,A11)</f>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$20,A11)</f>
         <v>1</v>
       </c>
       <c r="C11" s="6"/>
@@ -3570,7 +3681,7 @@
         <v>159</v>
       </c>
       <c r="B12" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$19,A12)</f>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$20,A12)</f>
         <v>1</v>
       </c>
       <c r="C12" s="6"/>
@@ -3580,7 +3691,7 @@
         <v>60</v>
       </c>
       <c r="B13" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$19,A13)</f>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$20,A13)</f>
         <v>3</v>
       </c>
       <c r="C13" s="6"/>
@@ -3590,7 +3701,7 @@
         <v>72</v>
       </c>
       <c r="B14" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$19,A14)</f>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$20,A14)</f>
         <v>4</v>
       </c>
       <c r="C14" s="6"/>
@@ -3625,585 +3736,585 @@
         <v>4</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>270</v>
+        <v>285</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>271</v>
+        <v>286</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>272</v>
+        <v>287</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>273</v>
+        <v>288</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>274</v>
+        <v>289</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>275</v>
+        <v>290</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>276</v>
+        <v>291</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>277</v>
+        <v>292</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>274</v>
+        <v>289</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>278</v>
+        <v>293</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>276</v>
+        <v>291</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>279</v>
+        <v>294</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>60</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>280</v>
+        <v>295</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>281</v>
+        <v>296</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>282</v>
+        <v>297</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>283</v>
+        <v>298</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>284</v>
+        <v>299</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>285</v>
+        <v>300</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>286</v>
+        <v>301</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>60</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>287</v>
+        <v>302</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>289</v>
+        <v>304</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>60</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>290</v>
+        <v>305</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>291</v>
+        <v>306</v>
       </c>
       <c r="B8" s="9" t="s">
         <v>60</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>292</v>
+        <v>307</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>276</v>
+        <v>291</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>293</v>
+        <v>308</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>60</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>294</v>
+        <v>309</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>276</v>
+        <v>291</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>295</v>
+        <v>310</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>297</v>
+        <v>312</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>298</v>
+        <v>313</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>299</v>
+        <v>314</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>300</v>
+        <v>315</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>301</v>
+        <v>316</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>302</v>
+        <v>317</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="C13" s="9" t="s">
+        <v>318</v>
+      </c>
+      <c r="D13" s="9" t="s">
         <v>303</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>304</v>
+        <v>319</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>305</v>
+        <v>320</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>306</v>
+        <v>321</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>307</v>
+        <v>322</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>308</v>
+        <v>323</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>309</v>
+        <v>324</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>310</v>
+        <v>325</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>311</v>
+        <v>326</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>276</v>
+        <v>291</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>312</v>
+        <v>327</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>313</v>
+        <v>328</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>314</v>
+        <v>329</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>315</v>
+        <v>330</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>316</v>
+        <v>331</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>315</v>
+        <v>330</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>317</v>
+        <v>332</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>318</v>
+        <v>333</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>276</v>
+        <v>291</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>319</v>
+        <v>334</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>320</v>
+        <v>335</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>321</v>
+        <v>336</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>322</v>
+        <v>337</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>276</v>
+        <v>291</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>313</v>
+        <v>328</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>324</v>
+        <v>339</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>325</v>
+        <v>340</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="9" t="s">
-        <v>326</v>
+        <v>341</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>315</v>
+        <v>330</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="9" t="s">
-        <v>327</v>
+        <v>342</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>328</v>
+        <v>343</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="s">
-        <v>329</v>
+        <v>344</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>330</v>
+        <v>345</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="s">
-        <v>331</v>
+        <v>346</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>332</v>
+        <v>347</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="s">
-        <v>333</v>
+        <v>348</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>334</v>
+        <v>349</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>276</v>
+        <v>291</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="s">
-        <v>335</v>
+        <v>350</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>276</v>
+        <v>291</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="9" t="s">
-        <v>337</v>
+        <v>352</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>338</v>
+        <v>353</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="9" t="s">
-        <v>339</v>
+        <v>354</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>315</v>
+        <v>330</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="9" t="s">
-        <v>340</v>
+        <v>355</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>341</v>
+        <v>356</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>288</v>
+        <v>303</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="9" t="s">
-        <v>342</v>
+        <v>357</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>283</v>
+        <v>298</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="9" t="s">
-        <v>343</v>
+        <v>358</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="s">
-        <v>344</v>
+        <v>359</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>283</v>
+        <v>298</v>
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="9" t="s">
-        <v>343</v>
+        <v>358</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="s">
-        <v>345</v>
+        <v>360</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>283</v>
+        <v>298</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="9" t="s">
-        <v>343</v>
+        <v>358</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="9" t="s">
-        <v>346</v>
+        <v>361</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>283</v>
+        <v>298</v>
       </c>
       <c r="C38" s="9"/>
       <c r="D38" s="9" t="s">
-        <v>343</v>
+        <v>358</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="9" t="s">
-        <v>347</v>
+        <v>362</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>283</v>
+        <v>298</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="9" t="s">
-        <v>343</v>
+        <v>358</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="8" t="s">
-        <v>348</v>
+        <v>363</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>283</v>
+        <v>298</v>
       </c>
       <c r="C40" s="9"/>
       <c r="D40" s="9" t="s">
-        <v>343</v>
+        <v>358</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="9" t="s">
-        <v>349</v>
+        <v>364</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>283</v>
+        <v>298</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="9" t="s">
-        <v>343</v>
+        <v>358</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="9" t="s">
-        <v>350</v>
+        <v>365</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>283</v>
+        <v>298</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>351</v>
+        <v>366</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>343</v>
+        <v>358</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="8" t="s">
-        <v>352</v>
+        <v>367</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>283</v>
+        <v>298</v>
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="9" t="s">
-        <v>343</v>
+        <v>358</v>
       </c>
     </row>
   </sheetData>

--- a/exhibition/contacts.xlsx
+++ b/exhibition/contacts.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Стенд INPD (Китай)" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Контакты!$A$1:$W$20</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Контакты!$A$1:$W$21</definedName>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Стенд INPD (Китай)'!$A$1:$D$43</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="380">
   <si>
     <t xml:space="preserve">№</t>
   </si>
@@ -646,6 +646,42 @@
   </si>
   <si>
     <t xml:space="preserve">photos/006_lamer_beauty.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Тайвань</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Бренд со своим заводом (OEM — уточнить)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Тайвань (Таоюань)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">O'RIGHT Inc. (O'right — Sustainable Beauty)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cosmetic 360, тайваньский павильон (Taiwan Beauty Valley), рядом со стендом DC43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.oright.com.tw</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Производство зубной пасты: 100% натуральная, 100% биооснова, вместо абразивов — древесная целлюлоза (бук, ель, FSC). Линейка Toothpaste Nº Zero и др. (подарочный набор из 3 паст). Основной профиль бренда — экологичный уход за волосами и кожей</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Производство зубной пасты</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Тайваньский «зелёный» бренд со своим заводом — по их данным, первый в Азии GMP-сертифицированный завод «зелёной» косметики, 10 международных сертификатов; углеродная нейтральность (продукты, завод, компания), подтверждено SGS с 2020 г. Награды: Green Product Award, Taiwan Excellence. Делают ли производство под чужую марку (OEM/ODM) — в источниках не найдено, уточнить.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://en.wikipedia.org/wiki/O%27right ; https://www.gp-award.com/en/products/toothpaste-n-zero ; https://www.taiwanexcellence.org/en/award/product/1100126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Уточнить, производят ли пасту под нашу марку (OEM), MOQ, сроки, цены; контакт — через форму на oright.com.tw или на стенде</t>
+  </si>
+  <si>
+    <t xml:space="preserve">photos/020_oright.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">Франция</t>
@@ -2260,7 +2296,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:W20"/>
+  <dimension ref="A1:W21"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -2799,7 +2835,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="202.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="91" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
@@ -2807,122 +2843,120 @@
         <v>131</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>45</v>
+        <v>132</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G9" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H9" s="2"/>
       <c r="I9" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="J9" s="2" t="s">
         <v>137</v>
       </c>
+      <c r="J9" s="2"/>
       <c r="K9" s="2"/>
-      <c r="L9" s="2" t="s">
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
+      <c r="N9" s="2"/>
+      <c r="O9" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q9" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="M9" s="2" t="s">
+      <c r="R9" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="N9" s="2" t="s">
+      <c r="S9" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="O9" s="2" t="s">
+      <c r="T9" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="P9" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="R9" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="S9" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="T9" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="U9" s="2" t="s">
-        <v>58</v>
-      </c>
+      <c r="U9" s="2"/>
       <c r="V9" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W9" s="2" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="202.95" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="D10" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="G10" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="J10" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G10" s="4" t="s">
+      <c r="K10" s="2"/>
+      <c r="L10" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="M10" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="I10" s="2" t="s">
+      <c r="N10" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2" t="s">
+      <c r="O10" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="N10" s="2"/>
-      <c r="O10" s="2" t="s">
+      <c r="P10" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="P10" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q10" s="2"/>
+      <c r="Q10" s="2" t="s">
+        <v>155</v>
+      </c>
       <c r="R10" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="S10" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="U10" s="2"/>
+        <v>158</v>
+      </c>
+      <c r="U10" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="V10" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W10" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2930,10 +2964,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>159</v>
+        <v>72</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>160</v>
@@ -2942,12 +2976,14 @@
         <v>161</v>
       </c>
       <c r="F11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G11" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="G11" s="4" t="s">
+      <c r="H11" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="H11" s="2"/>
       <c r="I11" s="2" t="s">
         <v>164</v>
       </c>
@@ -2957,328 +2993,330 @@
       <c r="M11" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="N11" s="2" t="s">
+      <c r="N11" s="2"/>
+      <c r="O11" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="O11" s="2" t="s">
+      <c r="P11" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q11" s="2"/>
+      <c r="R11" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="P11" s="2" t="s">
+      <c r="S11" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="Q11" s="2" t="s">
+      <c r="T11" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="R11" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="S11" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="T11" s="2" t="s">
-        <v>172</v>
       </c>
       <c r="U11" s="2"/>
       <c r="V11" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W11" s="2" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="180.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>60</v>
+        <v>171</v>
       </c>
       <c r="D12" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="G12" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="G12" s="2"/>
       <c r="H12" s="2"/>
       <c r="I12" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
-      <c r="N12" s="2"/>
+      <c r="M12" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>178</v>
+      </c>
       <c r="O12" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="Q12" s="2"/>
+        <v>180</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>181</v>
+      </c>
       <c r="R12" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="U12" s="2"/>
       <c r="V12" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W12" s="2" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="180.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>186</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="G13" s="2"/>
       <c r="H13" s="2"/>
       <c r="I13" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>188</v>
-      </c>
+        <v>189</v>
+      </c>
+      <c r="J13" s="2"/>
       <c r="K13" s="2"/>
-      <c r="L13" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="M13" s="2" t="s">
+      <c r="L13" s="2"/>
+      <c r="M13" s="2"/>
+      <c r="N13" s="2"/>
+      <c r="O13" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="N13" s="2" t="s">
+      <c r="P13" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="O13" s="2" t="s">
+      <c r="Q13" s="2"/>
+      <c r="R13" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="P13" s="2" t="s">
+      <c r="S13" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="Q13" s="2" t="s">
+      <c r="T13" s="2" t="s">
         <v>194</v>
-      </c>
-      <c r="R13" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="S13" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="T13" s="2" t="s">
-        <v>197</v>
       </c>
       <c r="U13" s="2"/>
       <c r="V13" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W13" s="2" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>45</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>202</v>
+        <v>27</v>
+      </c>
+      <c r="G14" s="4" t="s">
+        <v>198</v>
       </c>
       <c r="H14" s="2"/>
       <c r="I14" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="K14" s="2"/>
+      <c r="L14" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="N14" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
-      <c r="N14" s="2"/>
       <c r="O14" s="2" t="s">
         <v>204</v>
       </c>
       <c r="P14" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="Q14" s="2"/>
+      <c r="Q14" s="2" t="s">
+        <v>206</v>
+      </c>
       <c r="R14" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="U14" s="2"/>
       <c r="V14" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W14" s="2" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>45</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="G15" s="4" t="s">
         <v>213</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>214</v>
       </c>
       <c r="H15" s="2"/>
       <c r="I15" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="J15" s="2" t="s">
         <v>215</v>
       </c>
+      <c r="J15" s="2"/>
       <c r="K15" s="2"/>
-      <c r="L15" s="2" t="s">
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="M15" s="2" t="s">
+      <c r="P15" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="N15" s="2" t="s">
+      <c r="Q15" s="2"/>
+      <c r="R15" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="O15" s="2" t="s">
+      <c r="S15" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="P15" s="2" t="s">
+      <c r="T15" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="Q15" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="R15" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="S15" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="T15" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="U15" s="2" t="s">
-        <v>58</v>
-      </c>
+      <c r="U15" s="2"/>
       <c r="V15" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W15" s="2" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>45</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>27</v>
+        <v>224</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="H16" s="2"/>
       <c r="I16" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="M16" s="2" t="s">
         <v>229</v>
       </c>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
-      <c r="M16" s="2"/>
-      <c r="N16" s="2"/>
+      <c r="N16" s="2" t="s">
+        <v>230</v>
+      </c>
       <c r="O16" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="Q16" s="2"/>
+        <v>232</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>233</v>
+      </c>
       <c r="R16" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="T16" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="U16" s="2"/>
+        <v>236</v>
+      </c>
+      <c r="U16" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="V16" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W16" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3286,26 +3324,26 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>131</v>
+        <v>143</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>45</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>239</v>
+        <v>27</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>240</v>
       </c>
       <c r="H17" s="2"/>
       <c r="I17" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
@@ -3313,14 +3351,12 @@
       <c r="M17" s="2"/>
       <c r="N17" s="2"/>
       <c r="O17" s="2" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="Q17" s="2" t="s">
         <v>243</v>
       </c>
+      <c r="Q17" s="2"/>
       <c r="R17" s="2" t="s">
         <v>244</v>
       </c>
@@ -3338,177 +3374,234 @@
         <v>247</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>248</v>
+        <v>143</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>45</v>
       </c>
       <c r="D18" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>249</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="G18" s="2" t="s">
         <v>251</v>
       </c>
-      <c r="G18" s="2"/>
-      <c r="H18" s="4" t="s">
+      <c r="H18" s="2"/>
+      <c r="I18" s="2" t="s">
         <v>252</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>253</v>
       </c>
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
-      <c r="L18" s="2" t="s">
-        <v>254</v>
-      </c>
+      <c r="L18" s="2"/>
       <c r="M18" s="2"/>
       <c r="N18" s="2"/>
       <c r="O18" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="Q18" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="P18" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q18" s="2" t="s">
+      <c r="R18" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="R18" s="2" t="s">
+      <c r="S18" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="S18" s="2" t="s">
+      <c r="T18" s="2" t="s">
         <v>258</v>
-      </c>
-      <c r="T18" s="2" t="s">
-        <v>259</v>
       </c>
       <c r="U18" s="2"/>
       <c r="V18" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W18" s="2" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>248</v>
+        <v>260</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D19" s="2"/>
+      <c r="D19" s="2" t="s">
+        <v>261</v>
+      </c>
       <c r="E19" s="2" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
+      <c r="H19" s="4" t="s">
+        <v>264</v>
+      </c>
       <c r="I19" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
-      <c r="L19" s="2"/>
+      <c r="L19" s="2" t="s">
+        <v>266</v>
+      </c>
       <c r="M19" s="2"/>
       <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
+      <c r="O19" s="2" t="s">
+        <v>267</v>
+      </c>
       <c r="P19" s="2" t="s">
         <v>67</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="R19" s="2" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="T19" s="2" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="U19" s="2"/>
       <c r="V19" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W19" s="2" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>270</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="D20" s="2"/>
       <c r="E20" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G20" s="4" t="s">
-        <v>272</v>
-      </c>
-      <c r="H20" s="4" t="s">
-        <v>273</v>
-      </c>
+        <v>274</v>
+      </c>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
       <c r="I20" s="2" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
       <c r="M20" s="2"/>
       <c r="N20" s="2"/>
-      <c r="O20" s="2" t="s">
-        <v>275</v>
-      </c>
+      <c r="O20" s="2"/>
       <c r="P20" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q20" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="Q20" s="2" t="s">
+      <c r="R20" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="R20" s="2" t="s">
+      <c r="S20" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="S20" s="2" t="s">
+      <c r="T20" s="2" t="s">
         <v>279</v>
-      </c>
-      <c r="T20" s="2" t="s">
-        <v>280</v>
       </c>
       <c r="U20" s="2"/>
       <c r="V20" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W20" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="3" t="s">
         <v>281</v>
       </c>
+      <c r="C21" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>284</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>285</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
+      <c r="M21" s="2"/>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="P21" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="Q21" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="R21" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="S21" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="T21" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="U21" s="2"/>
+      <c r="V21" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="W21" s="2" t="s">
+        <v>293</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W20"/>
+  <autoFilter ref="A1:W21"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1" display="https://www.dachser.fr"/>
     <hyperlink ref="H2" r:id="rId2" display="https://www.dachser.com/en/cosmetic-logistics"/>
@@ -3518,16 +3611,17 @@
     <hyperlink ref="G6" r:id="rId6" display="https://www.eury-packaging.com"/>
     <hyperlink ref="G7" r:id="rId7" display="www.kava.cn"/>
     <hyperlink ref="G8" r:id="rId8" display="www.lamerbeauty.uk ; www.rsgroup.cn"/>
-    <hyperlink ref="G9" r:id="rId9" display="https://www.aircospascual-anjac.com"/>
-    <hyperlink ref="G10" r:id="rId10" display="https://www.desjardin.fr"/>
-    <hyperlink ref="H10" r:id="rId11" display="https://www.desjardin.fr/en/categories/cosmetic-packaging"/>
-    <hyperlink ref="G11" r:id="rId12" display="www.effervescence-lab.com"/>
-    <hyperlink ref="G13" r:id="rId13" display="https://www.laboratoiresbea.com"/>
-    <hyperlink ref="G15" r:id="rId14" display="https://www.msbeautilab.com"/>
-    <hyperlink ref="G16" r:id="rId15" display="https://simah-cosmetiques.fr"/>
-    <hyperlink ref="H18" r:id="rId16" display="https://welcon.kocca.kr/en/directory/company/cosplan-inc--5601"/>
-    <hyperlink ref="G20" r:id="rId17" display="https://iwasecosfa.eu"/>
-    <hyperlink ref="H20" r:id="rId18" display="https://iwasecosfa-eu.covalo.com/"/>
+    <hyperlink ref="G9" r:id="rId9" display="https://www.oright.com.tw"/>
+    <hyperlink ref="G10" r:id="rId10" display="https://www.aircospascual-anjac.com"/>
+    <hyperlink ref="G11" r:id="rId11" display="https://www.desjardin.fr"/>
+    <hyperlink ref="H11" r:id="rId12" display="https://www.desjardin.fr/en/categories/cosmetic-packaging"/>
+    <hyperlink ref="G12" r:id="rId13" display="www.effervescence-lab.com"/>
+    <hyperlink ref="G14" r:id="rId14" display="https://www.laboratoiresbea.com"/>
+    <hyperlink ref="G16" r:id="rId15" display="https://www.msbeautilab.com"/>
+    <hyperlink ref="G17" r:id="rId16" display="https://simah-cosmetiques.fr"/>
+    <hyperlink ref="H19" r:id="rId17" display="https://welcon.kocca.kr/en/directory/company/cosplan-inc--5601"/>
+    <hyperlink ref="G21" r:id="rId18" display="https://iwasecosfa.eu"/>
+    <hyperlink ref="H21" r:id="rId19" display="https://iwasecosfa-eu.covalo.com/"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3536,7 +3630,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId19"/>
+  <drawing r:id="rId20"/>
 </worksheet>
 </file>
 
@@ -3545,7 +3639,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C14"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="28"/>
@@ -3558,10 +3652,10 @@
         <v>1</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>282</v>
+        <v>294</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>283</v>
+        <v>295</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3569,11 +3663,11 @@
         <v>23</v>
       </c>
       <c r="B2" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$20,A2)</f>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$21,A2)</f>
         <v>1</v>
       </c>
       <c r="C2" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$20,A2,Контакты!$U$2:$U$20,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$21,A2,Контакты!$U$2:$U$21,"Высокий")</f>
         <v>0</v>
       </c>
     </row>
@@ -3582,11 +3676,11 @@
         <v>44</v>
       </c>
       <c r="B3" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$20,A3)</f>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$21,A3)</f>
         <v>6</v>
       </c>
       <c r="C3" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$20,A3,Контакты!$U$2:$U$20,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$21,A3,Контакты!$U$2:$U$21,"Высокий")</f>
         <v>4</v>
       </c>
     </row>
@@ -3595,116 +3689,139 @@
         <v>131</v>
       </c>
       <c r="B4" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$20,A4)</f>
-        <v>9</v>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$21,A4)</f>
+        <v>1</v>
       </c>
       <c r="C4" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$20,A4,Контакты!$U$2:$U$20,"Высокий")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$21,A4,Контакты!$U$2:$U$21,"Высокий")</f>
+        <v>0</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="s">
-        <v>248</v>
+        <v>143</v>
       </c>
       <c r="B5" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$20,A5)</f>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$21,A5)</f>
+        <v>9</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$21,A5,Контакты!$U$2:$U$21,"Высокий")</f>
         <v>2</v>
-      </c>
-      <c r="C5" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$20,A5,Контакты!$U$2:$U$20,"Высокий")</f>
-        <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="B6" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$20,A6)</f>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$21,A6)</f>
+        <v>2</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$21,A6,Контакты!$U$2:$U$21,"Высокий")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="B7" s="6" t="n">
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$21,A7)</f>
         <v>1</v>
       </c>
-      <c r="C6" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$20,A6,Контакты!$U$2:$U$20,"Высокий")</f>
+      <c r="C7" s="6" t="n">
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$21,A7,Контакты!$U$2:$U$21,"Высокий")</f>
         <v>0</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="7" t="s">
-        <v>284</v>
-      </c>
-      <c r="B7" s="7" t="n">
-        <f aca="false">SUM(B2:B6)</f>
-        <v>19</v>
-      </c>
-      <c r="C7" s="7" t="n">
-        <f aca="false">SUM(C2:C6)</f>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="B8" s="7" t="n">
+        <f aca="false">SUM(B2:B7)</f>
+        <v>20</v>
+      </c>
+      <c r="C8" s="7" t="n">
+        <f aca="false">SUM(C2:C7)</f>
         <v>6</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6"/>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-    </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>282</v>
-      </c>
+      <c r="A9" s="6"/>
+      <c r="B9" s="6"/>
       <c r="C9" s="6"/>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B10" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$20,A10)</f>
-        <v>10</v>
+        <v>2</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>294</v>
       </c>
       <c r="C10" s="6"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="s">
-        <v>24</v>
+        <v>132</v>
       </c>
       <c r="B11" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$20,A11)</f>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$21,A11)</f>
         <v>1</v>
       </c>
       <c r="C11" s="6"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="6" t="s">
-        <v>159</v>
+        <v>45</v>
       </c>
       <c r="B12" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$20,A12)</f>
-        <v>1</v>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$21,A12)</f>
+        <v>10</v>
       </c>
       <c r="C12" s="6"/>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="6" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="B13" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$20,A13)</f>
-        <v>3</v>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$21,A13)</f>
+        <v>1</v>
       </c>
       <c r="C13" s="6"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="B14" s="6" t="n">
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$21,A14)</f>
+        <v>1</v>
+      </c>
+      <c r="C14" s="6"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B15" s="6" t="n">
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$21,A15)</f>
+        <v>3</v>
+      </c>
+      <c r="C15" s="6"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="B14" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$20,A14)</f>
+      <c r="B16" s="6" t="n">
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$21,A16)</f>
         <v>4</v>
       </c>
-      <c r="C14" s="6"/>
+      <c r="C16" s="6"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -3736,585 +3853,585 @@
         <v>4</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>285</v>
+        <v>297</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>286</v>
+        <v>298</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>287</v>
+        <v>299</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>288</v>
+        <v>300</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>290</v>
+        <v>302</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>291</v>
+        <v>303</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>292</v>
+        <v>304</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>289</v>
+        <v>301</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>293</v>
+        <v>305</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>291</v>
+        <v>303</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>294</v>
+        <v>306</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>60</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>295</v>
+        <v>307</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>296</v>
+        <v>308</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>297</v>
+        <v>309</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>299</v>
+        <v>311</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>300</v>
+        <v>312</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>301</v>
+        <v>313</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>60</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>302</v>
+        <v>314</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>304</v>
+        <v>316</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>60</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>305</v>
+        <v>317</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>306</v>
+        <v>318</v>
       </c>
       <c r="B8" s="9" t="s">
         <v>60</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>307</v>
+        <v>319</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>291</v>
+        <v>303</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>308</v>
+        <v>320</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>60</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>309</v>
+        <v>321</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>291</v>
+        <v>303</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>310</v>
+        <v>322</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>312</v>
+        <v>324</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>313</v>
+        <v>325</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>314</v>
+        <v>326</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
+        <v>327</v>
+      </c>
+      <c r="B12" s="9" t="s">
+        <v>323</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>328</v>
+      </c>
+      <c r="D12" s="9" t="s">
         <v>315</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>311</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>316</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>303</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>317</v>
+        <v>329</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>318</v>
+        <v>330</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>319</v>
+        <v>331</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>321</v>
+        <v>333</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>322</v>
+        <v>334</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="B16" s="9" t="s">
         <v>323</v>
       </c>
-      <c r="B16" s="9" t="s">
-        <v>311</v>
-      </c>
       <c r="C16" s="9" t="s">
-        <v>324</v>
+        <v>336</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>325</v>
+        <v>337</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>326</v>
+        <v>338</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>291</v>
+        <v>303</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>327</v>
+        <v>339</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>329</v>
+        <v>341</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>331</v>
+        <v>343</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>332</v>
+        <v>344</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>333</v>
+        <v>345</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>291</v>
+        <v>303</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>334</v>
+        <v>346</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>335</v>
+        <v>347</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>336</v>
+        <v>348</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>337</v>
+        <v>349</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>291</v>
+        <v>303</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>338</v>
+        <v>350</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>328</v>
+        <v>340</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>339</v>
+        <v>351</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>340</v>
+        <v>352</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="9" t="s">
-        <v>341</v>
+        <v>353</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="9" t="s">
-        <v>342</v>
+        <v>354</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>343</v>
+        <v>355</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="s">
-        <v>344</v>
+        <v>356</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>345</v>
+        <v>357</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="s">
-        <v>346</v>
+        <v>358</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>347</v>
+        <v>359</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="s">
-        <v>348</v>
+        <v>360</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>349</v>
+        <v>361</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>291</v>
+        <v>303</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="s">
-        <v>350</v>
+        <v>362</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>351</v>
+        <v>363</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>291</v>
+        <v>303</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="9" t="s">
-        <v>352</v>
+        <v>364</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>353</v>
+        <v>365</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="9" t="s">
-        <v>354</v>
+        <v>366</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>330</v>
+        <v>342</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="9" t="s">
-        <v>355</v>
+        <v>367</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>311</v>
+        <v>323</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>356</v>
+        <v>368</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>303</v>
+        <v>315</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="9" t="s">
-        <v>357</v>
+        <v>369</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="9" t="s">
-        <v>358</v>
+        <v>370</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="s">
-        <v>359</v>
+        <v>371</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="9" t="s">
-        <v>358</v>
+        <v>370</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="s">
-        <v>360</v>
+        <v>372</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="9" t="s">
-        <v>358</v>
+        <v>370</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="9" t="s">
-        <v>361</v>
+        <v>373</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="C38" s="9"/>
       <c r="D38" s="9" t="s">
-        <v>358</v>
+        <v>370</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="9" t="s">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="9" t="s">
-        <v>358</v>
+        <v>370</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="8" t="s">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="C40" s="9"/>
       <c r="D40" s="9" t="s">
-        <v>358</v>
+        <v>370</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="9" t="s">
-        <v>364</v>
+        <v>376</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="9" t="s">
-        <v>358</v>
+        <v>370</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="9" t="s">
-        <v>365</v>
+        <v>377</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>366</v>
+        <v>378</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>358</v>
+        <v>370</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="8" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>298</v>
+        <v>310</v>
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="9" t="s">
-        <v>358</v>
+        <v>370</v>
       </c>
     </row>
   </sheetData>

--- a/exhibition/contacts.xlsx
+++ b/exhibition/contacts.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Стенд INPD (Китай)" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Контакты!$A$1:$W$21</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Контакты!$A$1:$W$22</definedName>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Стенд INPD (Китай)'!$A$1:$D$43</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="395">
   <si>
     <t xml:space="preserve">№</t>
   </si>
@@ -733,6 +733,51 @@
   </si>
   <si>
     <t xml:space="preserve">photos/016_anjac.jpg ; photos/016b_anjac_aircos_pascual_card.jpg ; photos/016c_anjac_video.MOV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Дрё (Эр и Луар), ~80 км от Парижа</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cosinus Servicosm (cosmetic lab &amp; packing)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.cosinus-servicosm.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Лаборатория и фасовка косметики (cosmetic lab &amp; packing): производство ПАРФЮМА с маленькими минимальными партиями — от 1 000 флаконов. На стенде также Climastick — охлаждающий стик для кожи (2 зоны применения, апсайкл-ингредиенты)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Christophe MEUNIER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Directeur de Site (директор площадки)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">christophe.meunier@cosinus-servicosm.com</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Моб.: +33 6 76 04 11 61 ; офис: +33 2 37 38 03 30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12 Rue Jean-Louis Chanoine, ZA de la Rabette, 28100 Dreux, Франция</t>
+  </si>
+  <si>
+    <t xml:space="preserve">От руки: «производят духи, 1000 флакончиков»</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Производят парфюм, маленькие минималки — от 1 000 флаконов</t>
+  </si>
+  <si>
+    <t xml:space="preserve">По реестру Франции: SARL Cosinus, Дрё, работает с 1997 г., код деятельности 20.42Z (производство парфюмерии и туалетных средств), 10–19 сотрудников, выручка ~2 млн € (данные 2015–2017). Небольшое производство — отсюда гибкие маленькие партии.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.xerfi.com/etudes-par-entreprise/cosinus_414916825 ; https://api-avis-situation-sirene.insee.fr/identification/pdf/41491682500022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Написать Christophe Meunier: парфюм от 1 000 флаконов — цены, сроки, свои отдушки или наши, флаконы (их или EURY/Cypress), документы</t>
+  </si>
+  <si>
+    <t xml:space="preserve">photos/021_cosinus_servicosm.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">Под Парижем (рядом с аэропортом Руасси — Шарль-де-Голль); есть также производство в Азии</t>
@@ -2296,7 +2341,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:W21"/>
+  <dimension ref="A1:W22"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -2959,7 +3004,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="57.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
@@ -2967,7 +3012,7 @@
         <v>143</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>72</v>
+        <v>45</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>160</v>
@@ -2981,41 +3026,49 @@
       <c r="G11" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="H11" s="4" t="s">
+      <c r="H11" s="2"/>
+      <c r="I11" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="I11" s="2" t="s">
+      <c r="J11" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="J11" s="2"/>
       <c r="K11" s="2"/>
-      <c r="L11" s="2"/>
+      <c r="L11" s="2" t="s">
+        <v>165</v>
+      </c>
       <c r="M11" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="N11" s="2"/>
+        <v>166</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>167</v>
+      </c>
       <c r="O11" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q11" s="2"/>
+        <v>169</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>170</v>
+      </c>
       <c r="R11" s="2" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="U11" s="2"/>
+        <v>173</v>
+      </c>
+      <c r="U11" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="V11" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W11" s="2" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3026,42 +3079,40 @@
         <v>143</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>171</v>
+        <v>72</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>174</v>
+        <v>27</v>
       </c>
       <c r="G12" s="4" t="s">
-        <v>175</v>
-      </c>
-      <c r="H12" s="2"/>
+        <v>177</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>178</v>
+      </c>
       <c r="I12" s="2" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="J12" s="2"/>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
       <c r="M12" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="N12" s="2" t="s">
-        <v>178</v>
-      </c>
+        <v>180</v>
+      </c>
+      <c r="N12" s="2"/>
       <c r="O12" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="Q12" s="2" t="s">
-        <v>181</v>
-      </c>
+        <v>67</v>
+      </c>
+      <c r="Q12" s="2"/>
       <c r="R12" s="2" t="s">
         <v>182</v>
       </c>
@@ -3079,7 +3130,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="180.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
@@ -3087,52 +3138,60 @@
         <v>143</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>60</v>
+        <v>186</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="G13" s="2"/>
+        <v>189</v>
+      </c>
+      <c r="G13" s="4" t="s">
+        <v>190</v>
+      </c>
       <c r="H13" s="2"/>
       <c r="I13" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="J13" s="2"/>
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
-      <c r="M13" s="2"/>
-      <c r="N13" s="2"/>
+      <c r="M13" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>193</v>
+      </c>
       <c r="O13" s="2" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="Q13" s="2"/>
+        <v>195</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>196</v>
+      </c>
       <c r="R13" s="2" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="U13" s="2"/>
       <c r="V13" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W13" s="2" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="180.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
@@ -3140,46 +3199,34 @@
         <v>143</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>198</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="G14" s="2"/>
       <c r="H14" s="2"/>
       <c r="I14" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>200</v>
-      </c>
+        <v>204</v>
+      </c>
+      <c r="J14" s="2"/>
       <c r="K14" s="2"/>
-      <c r="L14" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="M14" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="N14" s="2" t="s">
-        <v>203</v>
-      </c>
+      <c r="L14" s="2"/>
+      <c r="M14" s="2"/>
+      <c r="N14" s="2"/>
       <c r="O14" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="Q14" s="2" t="s">
         <v>206</v>
       </c>
+      <c r="Q14" s="2"/>
       <c r="R14" s="2" t="s">
         <v>207</v>
       </c>
@@ -3197,7 +3244,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
@@ -3214,45 +3261,55 @@
         <v>212</v>
       </c>
       <c r="F15" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G15" s="4" t="s">
         <v>213</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>214</v>
       </c>
       <c r="H15" s="2"/>
       <c r="I15" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="J15" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="J15" s="2"/>
       <c r="K15" s="2"/>
-      <c r="L15" s="2"/>
-      <c r="M15" s="2"/>
-      <c r="N15" s="2"/>
+      <c r="L15" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>218</v>
+      </c>
       <c r="O15" s="2" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="Q15" s="2"/>
+        <v>220</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>221</v>
+      </c>
       <c r="R15" s="2" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="U15" s="2"/>
       <c r="V15" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W15" s="2" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
@@ -3263,63 +3320,51 @@
         <v>45</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="G16" s="4" t="s">
-        <v>225</v>
+        <v>228</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>229</v>
       </c>
       <c r="H16" s="2"/>
       <c r="I16" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>227</v>
-      </c>
+        <v>230</v>
+      </c>
+      <c r="J16" s="2"/>
       <c r="K16" s="2"/>
-      <c r="L16" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="N16" s="2" t="s">
-        <v>230</v>
-      </c>
+      <c r="L16" s="2"/>
+      <c r="M16" s="2"/>
+      <c r="N16" s="2"/>
       <c r="O16" s="2" t="s">
         <v>231</v>
       </c>
       <c r="P16" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="Q16" s="2" t="s">
+      <c r="Q16" s="2"/>
+      <c r="R16" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="R16" s="2" t="s">
+      <c r="S16" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="S16" s="2" t="s">
+      <c r="T16" s="2" t="s">
         <v>235</v>
       </c>
-      <c r="T16" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="U16" s="2" t="s">
-        <v>58</v>
-      </c>
+      <c r="U16" s="2"/>
       <c r="V16" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W16" s="2" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
@@ -3330,13 +3375,13 @@
         <v>45</v>
       </c>
       <c r="D17" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="F17" s="2" t="s">
         <v>239</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>27</v>
       </c>
       <c r="G17" s="4" t="s">
         <v>240</v>
@@ -3345,33 +3390,45 @@
       <c r="I17" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="J17" s="2"/>
+      <c r="J17" s="2" t="s">
+        <v>242</v>
+      </c>
       <c r="K17" s="2"/>
-      <c r="L17" s="2"/>
-      <c r="M17" s="2"/>
-      <c r="N17" s="2"/>
+      <c r="L17" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="M17" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="N17" s="2" t="s">
+        <v>245</v>
+      </c>
       <c r="O17" s="2" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="Q17" s="2"/>
+        <v>247</v>
+      </c>
+      <c r="Q17" s="2" t="s">
+        <v>248</v>
+      </c>
       <c r="R17" s="2" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="T17" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="U17" s="2"/>
+        <v>251</v>
+      </c>
+      <c r="U17" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="V17" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W17" s="2" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3385,20 +3442,20 @@
         <v>45</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>251</v>
+        <v>27</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>255</v>
       </c>
       <c r="H18" s="2"/>
       <c r="I18" s="2" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
@@ -3406,202 +3463,257 @@
       <c r="M18" s="2"/>
       <c r="N18" s="2"/>
       <c r="O18" s="2" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="Q18" s="2" t="s">
-        <v>255</v>
-      </c>
+        <v>258</v>
+      </c>
+      <c r="Q18" s="2"/>
       <c r="R18" s="2" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="S18" s="2" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="T18" s="2" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="U18" s="2"/>
       <c r="V18" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W18" s="2" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>260</v>
+        <v>143</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>45</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>263</v>
-      </c>
-      <c r="G19" s="2"/>
-      <c r="H19" s="4" t="s">
-        <v>264</v>
-      </c>
+        <v>265</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="H19" s="2"/>
       <c r="I19" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
-      <c r="L19" s="2" t="s">
-        <v>266</v>
-      </c>
+      <c r="L19" s="2"/>
       <c r="M19" s="2"/>
       <c r="N19" s="2"/>
       <c r="O19" s="2" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>67</v>
+        <v>269</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="R19" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="T19" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="U19" s="2"/>
       <c r="V19" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W19" s="2" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>260</v>
+        <v>275</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D20" s="2"/>
+      <c r="D20" s="2" t="s">
+        <v>276</v>
+      </c>
       <c r="E20" s="2" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
+      <c r="H20" s="4" t="s">
+        <v>279</v>
+      </c>
       <c r="I20" s="2" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
-      <c r="L20" s="2"/>
+      <c r="L20" s="2" t="s">
+        <v>281</v>
+      </c>
       <c r="M20" s="2"/>
       <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
+      <c r="O20" s="2" t="s">
+        <v>282</v>
+      </c>
       <c r="P20" s="2" t="s">
         <v>67</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>276</v>
+        <v>283</v>
       </c>
       <c r="R20" s="2" t="s">
-        <v>277</v>
+        <v>284</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>278</v>
+        <v>285</v>
       </c>
       <c r="T20" s="2" t="s">
-        <v>279</v>
+        <v>286</v>
       </c>
       <c r="U20" s="2"/>
       <c r="V20" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W20" s="2" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="n">
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>282</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="D21" s="2"/>
       <c r="E21" s="2" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G21" s="4" t="s">
-        <v>284</v>
-      </c>
-      <c r="H21" s="4" t="s">
-        <v>285</v>
-      </c>
+        <v>289</v>
+      </c>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
       <c r="I21" s="2" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
       <c r="L21" s="2"/>
       <c r="M21" s="2"/>
       <c r="N21" s="2"/>
-      <c r="O21" s="2" t="s">
-        <v>287</v>
-      </c>
+      <c r="O21" s="2"/>
       <c r="P21" s="2" t="s">
-        <v>288</v>
+        <v>67</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="R21" s="2" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="S21" s="2" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="T21" s="2" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="U21" s="2"/>
       <c r="V21" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W21" s="2" t="s">
-        <v>293</v>
+        <v>295</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="2" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G22" s="4" t="s">
+        <v>299</v>
+      </c>
+      <c r="H22" s="4" t="s">
+        <v>300</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
+      <c r="M22" s="2"/>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="Q22" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="R22" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="S22" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="T22" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="U22" s="2"/>
+      <c r="V22" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="W22" s="2" t="s">
+        <v>308</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W21"/>
+  <autoFilter ref="A1:W22"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1" display="https://www.dachser.fr"/>
     <hyperlink ref="H2" r:id="rId2" display="https://www.dachser.com/en/cosmetic-logistics"/>
@@ -3613,15 +3725,16 @@
     <hyperlink ref="G8" r:id="rId8" display="www.lamerbeauty.uk ; www.rsgroup.cn"/>
     <hyperlink ref="G9" r:id="rId9" display="https://www.oright.com.tw"/>
     <hyperlink ref="G10" r:id="rId10" display="https://www.aircospascual-anjac.com"/>
-    <hyperlink ref="G11" r:id="rId11" display="https://www.desjardin.fr"/>
-    <hyperlink ref="H11" r:id="rId12" display="https://www.desjardin.fr/en/categories/cosmetic-packaging"/>
-    <hyperlink ref="G12" r:id="rId13" display="www.effervescence-lab.com"/>
-    <hyperlink ref="G14" r:id="rId14" display="https://www.laboratoiresbea.com"/>
-    <hyperlink ref="G16" r:id="rId15" display="https://www.msbeautilab.com"/>
-    <hyperlink ref="G17" r:id="rId16" display="https://simah-cosmetiques.fr"/>
-    <hyperlink ref="H19" r:id="rId17" display="https://welcon.kocca.kr/en/directory/company/cosplan-inc--5601"/>
-    <hyperlink ref="G21" r:id="rId18" display="https://iwasecosfa.eu"/>
-    <hyperlink ref="H21" r:id="rId19" display="https://iwasecosfa-eu.covalo.com/"/>
+    <hyperlink ref="G11" r:id="rId11" display="https://www.cosinus-servicosm.com"/>
+    <hyperlink ref="G12" r:id="rId12" display="https://www.desjardin.fr"/>
+    <hyperlink ref="H12" r:id="rId13" display="https://www.desjardin.fr/en/categories/cosmetic-packaging"/>
+    <hyperlink ref="G13" r:id="rId14" display="www.effervescence-lab.com"/>
+    <hyperlink ref="G15" r:id="rId15" display="https://www.laboratoiresbea.com"/>
+    <hyperlink ref="G17" r:id="rId16" display="https://www.msbeautilab.com"/>
+    <hyperlink ref="G18" r:id="rId17" display="https://simah-cosmetiques.fr"/>
+    <hyperlink ref="H20" r:id="rId18" display="https://welcon.kocca.kr/en/directory/company/cosplan-inc--5601"/>
+    <hyperlink ref="G22" r:id="rId19" display="https://iwasecosfa.eu"/>
+    <hyperlink ref="H22" r:id="rId20" display="https://iwasecosfa-eu.covalo.com/"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3630,7 +3743,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId20"/>
+  <drawing r:id="rId21"/>
 </worksheet>
 </file>
 
@@ -3652,10 +3765,10 @@
         <v>1</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>294</v>
+        <v>309</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>295</v>
+        <v>310</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3663,11 +3776,11 @@
         <v>23</v>
       </c>
       <c r="B2" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$21,A2)</f>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$22,A2)</f>
         <v>1</v>
       </c>
       <c r="C2" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$21,A2,Контакты!$U$2:$U$21,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$22,A2,Контакты!$U$2:$U$22,"Высокий")</f>
         <v>0</v>
       </c>
     </row>
@@ -3676,11 +3789,11 @@
         <v>44</v>
       </c>
       <c r="B3" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$21,A3)</f>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$22,A3)</f>
         <v>6</v>
       </c>
       <c r="C3" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$21,A3,Контакты!$U$2:$U$21,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$22,A3,Контакты!$U$2:$U$22,"Высокий")</f>
         <v>4</v>
       </c>
     </row>
@@ -3689,11 +3802,11 @@
         <v>131</v>
       </c>
       <c r="B4" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$21,A4)</f>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$22,A4)</f>
         <v>1</v>
       </c>
       <c r="C4" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$21,A4,Контакты!$U$2:$U$21,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$22,A4,Контакты!$U$2:$U$22,"Высокий")</f>
         <v>0</v>
       </c>
     </row>
@@ -3702,51 +3815,51 @@
         <v>143</v>
       </c>
       <c r="B5" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$21,A5)</f>
-        <v>9</v>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$22,A5)</f>
+        <v>10</v>
       </c>
       <c r="C5" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$21,A5,Контакты!$U$2:$U$21,"Высокий")</f>
-        <v>2</v>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$22,A5,Контакты!$U$2:$U$22,"Высокий")</f>
+        <v>3</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>260</v>
+        <v>275</v>
       </c>
       <c r="B6" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$21,A6)</f>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$22,A6)</f>
         <v>2</v>
       </c>
       <c r="C6" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$21,A6,Контакты!$U$2:$U$21,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$22,A6,Контакты!$U$2:$U$22,"Высокий")</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>281</v>
+        <v>296</v>
       </c>
       <c r="B7" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$21,A7)</f>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$22,A7)</f>
         <v>1</v>
       </c>
       <c r="C7" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$21,A7,Контакты!$U$2:$U$21,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$22,A7,Контакты!$U$2:$U$22,"Высокий")</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>296</v>
+        <v>311</v>
       </c>
       <c r="B8" s="7" t="n">
         <f aca="false">SUM(B2:B7)</f>
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C8" s="7" t="n">
         <f aca="false">SUM(C2:C7)</f>
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3759,7 +3872,7 @@
         <v>2</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>294</v>
+        <v>309</v>
       </c>
       <c r="C10" s="6"/>
     </row>
@@ -3768,7 +3881,7 @@
         <v>132</v>
       </c>
       <c r="B11" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$21,A11)</f>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$22,A11)</f>
         <v>1</v>
       </c>
       <c r="C11" s="6"/>
@@ -3778,8 +3891,8 @@
         <v>45</v>
       </c>
       <c r="B12" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$21,A12)</f>
-        <v>10</v>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$22,A12)</f>
+        <v>11</v>
       </c>
       <c r="C12" s="6"/>
     </row>
@@ -3788,17 +3901,17 @@
         <v>24</v>
       </c>
       <c r="B13" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$21,A13)</f>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$22,A13)</f>
         <v>1</v>
       </c>
       <c r="C13" s="6"/>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="6" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="B14" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$21,A14)</f>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$22,A14)</f>
         <v>1</v>
       </c>
       <c r="C14" s="6"/>
@@ -3808,7 +3921,7 @@
         <v>60</v>
       </c>
       <c r="B15" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$21,A15)</f>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$22,A15)</f>
         <v>3</v>
       </c>
       <c r="C15" s="6"/>
@@ -3818,7 +3931,7 @@
         <v>72</v>
       </c>
       <c r="B16" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$21,A16)</f>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$22,A16)</f>
         <v>4</v>
       </c>
       <c r="C16" s="6"/>
@@ -3853,585 +3966,585 @@
         <v>4</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>297</v>
+        <v>312</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>298</v>
+        <v>313</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>299</v>
+        <v>314</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>300</v>
+        <v>315</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>301</v>
+        <v>316</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>302</v>
+        <v>317</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>303</v>
+        <v>318</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>304</v>
+        <v>319</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>301</v>
+        <v>316</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>305</v>
+        <v>320</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>303</v>
+        <v>318</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>306</v>
+        <v>321</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>60</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>307</v>
+        <v>322</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>308</v>
+        <v>323</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>309</v>
+        <v>324</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>310</v>
+        <v>325</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>311</v>
+        <v>326</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>312</v>
+        <v>327</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>313</v>
+        <v>328</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>60</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>314</v>
+        <v>329</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>315</v>
+        <v>330</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>316</v>
+        <v>331</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>60</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>317</v>
+        <v>332</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>315</v>
+        <v>330</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>318</v>
+        <v>333</v>
       </c>
       <c r="B8" s="9" t="s">
         <v>60</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>319</v>
+        <v>334</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>303</v>
+        <v>318</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>320</v>
+        <v>335</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>60</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>321</v>
+        <v>336</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>303</v>
+        <v>318</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>322</v>
+        <v>337</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>324</v>
+        <v>339</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>315</v>
+        <v>330</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>325</v>
+        <v>340</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>326</v>
+        <v>341</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>315</v>
+        <v>330</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>327</v>
+        <v>342</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>328</v>
+        <v>343</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>315</v>
+        <v>330</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>329</v>
+        <v>344</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="C13" s="9" t="s">
+        <v>345</v>
+      </c>
+      <c r="D13" s="9" t="s">
         <v>330</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>315</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>331</v>
+        <v>346</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>332</v>
+        <v>347</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>315</v>
+        <v>330</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>333</v>
+        <v>348</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>334</v>
+        <v>349</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>315</v>
+        <v>330</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>335</v>
+        <v>350</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>336</v>
+        <v>351</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>315</v>
+        <v>330</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>337</v>
+        <v>352</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>338</v>
+        <v>353</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>303</v>
+        <v>318</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>339</v>
+        <v>354</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>340</v>
+        <v>355</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>315</v>
+        <v>330</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>341</v>
+        <v>356</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>342</v>
+        <v>357</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>315</v>
+        <v>330</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>343</v>
+        <v>358</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>342</v>
+        <v>357</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>315</v>
+        <v>330</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>344</v>
+        <v>359</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>345</v>
+        <v>360</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>303</v>
+        <v>318</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>346</v>
+        <v>361</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>347</v>
+        <v>362</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>315</v>
+        <v>330</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>348</v>
+        <v>363</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>349</v>
+        <v>364</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>303</v>
+        <v>318</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>350</v>
+        <v>365</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>340</v>
+        <v>355</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>315</v>
+        <v>330</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>351</v>
+        <v>366</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>352</v>
+        <v>367</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>315</v>
+        <v>330</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="9" t="s">
-        <v>353</v>
+        <v>368</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>342</v>
+        <v>357</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>315</v>
+        <v>330</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="9" t="s">
-        <v>354</v>
+        <v>369</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>355</v>
+        <v>370</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>315</v>
+        <v>330</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="s">
-        <v>356</v>
+        <v>371</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>357</v>
+        <v>372</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>315</v>
+        <v>330</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="s">
-        <v>358</v>
+        <v>373</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>359</v>
+        <v>374</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>315</v>
+        <v>330</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="s">
-        <v>360</v>
+        <v>375</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>361</v>
+        <v>376</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>303</v>
+        <v>318</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="s">
-        <v>362</v>
+        <v>377</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>363</v>
+        <v>378</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>303</v>
+        <v>318</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="9" t="s">
-        <v>364</v>
+        <v>379</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>365</v>
+        <v>380</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>315</v>
+        <v>330</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="9" t="s">
-        <v>366</v>
+        <v>381</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>342</v>
+        <v>357</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>315</v>
+        <v>330</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="9" t="s">
-        <v>367</v>
+        <v>382</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>323</v>
+        <v>338</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>368</v>
+        <v>383</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>315</v>
+        <v>330</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="9" t="s">
-        <v>369</v>
+        <v>384</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>310</v>
+        <v>325</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="9" t="s">
-        <v>370</v>
+        <v>385</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="s">
-        <v>371</v>
+        <v>386</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>310</v>
+        <v>325</v>
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="9" t="s">
-        <v>370</v>
+        <v>385</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="s">
-        <v>372</v>
+        <v>387</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>310</v>
+        <v>325</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="9" t="s">
-        <v>370</v>
+        <v>385</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="9" t="s">
-        <v>373</v>
+        <v>388</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>310</v>
+        <v>325</v>
       </c>
       <c r="C38" s="9"/>
       <c r="D38" s="9" t="s">
-        <v>370</v>
+        <v>385</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="9" t="s">
-        <v>374</v>
+        <v>389</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>310</v>
+        <v>325</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="9" t="s">
-        <v>370</v>
+        <v>385</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="8" t="s">
-        <v>375</v>
+        <v>390</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>310</v>
+        <v>325</v>
       </c>
       <c r="C40" s="9"/>
       <c r="D40" s="9" t="s">
-        <v>370</v>
+        <v>385</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="9" t="s">
-        <v>376</v>
+        <v>391</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>310</v>
+        <v>325</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="9" t="s">
-        <v>370</v>
+        <v>385</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="9" t="s">
-        <v>377</v>
+        <v>392</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>310</v>
+        <v>325</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>378</v>
+        <v>393</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>370</v>
+        <v>385</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="8" t="s">
-        <v>379</v>
+        <v>394</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>310</v>
+        <v>325</v>
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="9" t="s">
-        <v>370</v>
+        <v>385</v>
       </c>
     </row>
   </sheetData>

--- a/exhibition/contacts.xlsx
+++ b/exhibition/contacts.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Стенд INPD (Китай)" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Контакты!$A$1:$W$22</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Контакты!$A$1:$W$23</definedName>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Стенд INPD (Китай)'!$A$1:$D$43</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="404">
   <si>
     <t xml:space="preserve">№</t>
   </si>
@@ -1012,6 +1012,33 @@
   </si>
   <si>
     <t xml:space="preserve">photos/018_ms_beautilab_card.jpg ; photos/018b_ms_beautilab_stand.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Регион Иль-де-Франс (запад от Парижа: Гервиль / Мант-ля-Жоли — ABO); France Lab — Париж, хаб в Нью-Йорке</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marie Claire Beauty Group: CEGEDIS (парфюм) + ABO Cosmétiques (косметика) + France Lab (разработка) + Decortiat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cosmetic 360, стенд DB28 (Innovation Route — Formulation)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Полный цикл от создания бренда до производства, под ключ или по этапам: ПАРФЮМ (CEGEDIS — производство парфюмерии), уход, макияж, уход за волосами, ароматы для дома (ABO — производство и фасовка селективной, органической и натуральной косметики, в т.ч. парфюмерной воды). France Lab — разработка ароматов и косметики на заказ, дизайн упаковки, регуляторика. Новинка на стенде: парфюм нового поколения — без спирта, на водной основе, стойкий. На витрине: парфюмы, кремы, палетки теней, румяна, помады</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Производитель парфюма</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Группа принадлежит медиагруппе Marie Claire. France Lab куплена в 2015 г., ABO Cosmétiques и Cegedis — в 2018 г., дизайн-агентство Desdoigts &amp; Associés — в 2020 г. Вместе закрывают цепочку от создания бренда до производства. Decortiat — в источниках не найден (возможно, партнёр/подразделение).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.premiumbeautynews.com/en/marie-claire-group-to-speed-up,14015 ; https://beautymatter.com/articles/marie-claire-group-continues-diversification-in-beauty-sector ; https://www.cosmetic-valley.com/en/annuaire-entreprises/abo-cosmetiques ; https://www.premiumbeautynews.com/en/france-lab-sets-up-offices-and-an,9839 ; https://www.cbnews.fr/medias/groupe-marie-claire-rachete-agence-desdoigts-associes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Взять контакт на стенде DB28; запросить: парфюм (в т.ч. безспиртовой на водной основе), MOQ, сроки, цены; продукты для губ и макияж</t>
+  </si>
+  <si>
+    <t xml:space="preserve">photos/022_marie_claire_beauty_group.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">Мейссак (Коррез), Новая Аквитания; второй сайт — Юссак</t>
@@ -2341,7 +2368,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:W22"/>
+  <dimension ref="A1:W23"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -3431,7 +3458,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="18" customFormat="false" ht="180.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
@@ -3448,11 +3475,9 @@
         <v>254</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G18" s="4" t="s">
         <v>255</v>
       </c>
+      <c r="G18" s="2"/>
       <c r="H18" s="2"/>
       <c r="I18" s="2" t="s">
         <v>256</v>
@@ -3463,27 +3488,31 @@
       <c r="M18" s="2"/>
       <c r="N18" s="2"/>
       <c r="O18" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q18" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="P18" s="2" t="s">
+      <c r="R18" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="Q18" s="2"/>
-      <c r="R18" s="2" t="s">
+      <c r="S18" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="S18" s="2" t="s">
+      <c r="T18" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="T18" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="U18" s="2"/>
+      <c r="U18" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="V18" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W18" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3497,20 +3526,20 @@
         <v>45</v>
       </c>
       <c r="D19" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="F19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G19" s="4" t="s">
         <v>264</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>266</v>
       </c>
       <c r="H19" s="2"/>
       <c r="I19" s="2" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
@@ -3518,202 +3547,257 @@
       <c r="M19" s="2"/>
       <c r="N19" s="2"/>
       <c r="O19" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="Q19" s="2"/>
+      <c r="R19" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="P19" s="2" t="s">
+      <c r="S19" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="Q19" s="2" t="s">
+      <c r="T19" s="2" t="s">
         <v>270</v>
-      </c>
-      <c r="R19" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="S19" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="T19" s="2" t="s">
-        <v>273</v>
       </c>
       <c r="U19" s="2"/>
       <c r="V19" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W19" s="2" t="s">
-        <v>274</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>275</v>
+        <v>143</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>45</v>
       </c>
       <c r="D20" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2" t="s">
         <v>276</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="G20" s="2"/>
-      <c r="H20" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>280</v>
       </c>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
-      <c r="L20" s="2" t="s">
-        <v>281</v>
-      </c>
+      <c r="L20" s="2"/>
       <c r="M20" s="2"/>
       <c r="N20" s="2"/>
       <c r="O20" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="Q20" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="R20" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="S20" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="T20" s="2" t="s">
         <v>282</v>
-      </c>
-      <c r="P20" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q20" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="R20" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="S20" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="T20" s="2" t="s">
-        <v>286</v>
       </c>
       <c r="U20" s="2"/>
       <c r="V20" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W20" s="2" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="n">
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D21" s="2"/>
+      <c r="D21" s="2" t="s">
+        <v>285</v>
+      </c>
       <c r="E21" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="G21" s="2"/>
+      <c r="H21" s="4" t="s">
         <v>288</v>
       </c>
-      <c r="F21" s="2" t="s">
+      <c r="I21" s="2" t="s">
         <v>289</v>
-      </c>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2" t="s">
-        <v>290</v>
       </c>
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
-      <c r="L21" s="2"/>
+      <c r="L21" s="2" t="s">
+        <v>290</v>
+      </c>
       <c r="M21" s="2"/>
       <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
+      <c r="O21" s="2" t="s">
+        <v>291</v>
+      </c>
       <c r="P21" s="2" t="s">
         <v>67</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="R21" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="S21" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="T21" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="U21" s="2"/>
       <c r="V21" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W21" s="2" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="n">
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>296</v>
+        <v>284</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D22" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="F22" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="F22" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G22" s="4" t="s">
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2" t="s">
         <v>299</v>
-      </c>
-      <c r="H22" s="4" t="s">
-        <v>300</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>301</v>
       </c>
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>
       <c r="M22" s="2"/>
       <c r="N22" s="2"/>
-      <c r="O22" s="2" t="s">
+      <c r="O22" s="2"/>
+      <c r="P22" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q22" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="R22" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="S22" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="P22" s="2" t="s">
+      <c r="T22" s="2" t="s">
         <v>303</v>
-      </c>
-      <c r="Q22" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="R22" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="S22" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="T22" s="2" t="s">
-        <v>307</v>
       </c>
       <c r="U22" s="2"/>
       <c r="V22" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W22" s="2" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="2" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G23" s="4" t="s">
         <v>308</v>
       </c>
+      <c r="H23" s="4" t="s">
+        <v>309</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
+      <c r="M23" s="2"/>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="P23" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="Q23" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="R23" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="S23" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="T23" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="U23" s="2"/>
+      <c r="V23" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="W23" s="2" t="s">
+        <v>317</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W22"/>
+  <autoFilter ref="A1:W23"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1" display="https://www.dachser.fr"/>
     <hyperlink ref="H2" r:id="rId2" display="https://www.dachser.com/en/cosmetic-logistics"/>
@@ -3731,10 +3815,10 @@
     <hyperlink ref="G13" r:id="rId14" display="www.effervescence-lab.com"/>
     <hyperlink ref="G15" r:id="rId15" display="https://www.laboratoiresbea.com"/>
     <hyperlink ref="G17" r:id="rId16" display="https://www.msbeautilab.com"/>
-    <hyperlink ref="G18" r:id="rId17" display="https://simah-cosmetiques.fr"/>
-    <hyperlink ref="H20" r:id="rId18" display="https://welcon.kocca.kr/en/directory/company/cosplan-inc--5601"/>
-    <hyperlink ref="G22" r:id="rId19" display="https://iwasecosfa.eu"/>
-    <hyperlink ref="H22" r:id="rId20" display="https://iwasecosfa-eu.covalo.com/"/>
+    <hyperlink ref="G19" r:id="rId17" display="https://simah-cosmetiques.fr"/>
+    <hyperlink ref="H21" r:id="rId18" display="https://welcon.kocca.kr/en/directory/company/cosplan-inc--5601"/>
+    <hyperlink ref="G23" r:id="rId19" display="https://iwasecosfa.eu"/>
+    <hyperlink ref="H23" r:id="rId20" display="https://iwasecosfa-eu.covalo.com/"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3765,10 +3849,10 @@
         <v>1</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>310</v>
+        <v>319</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3776,11 +3860,11 @@
         <v>23</v>
       </c>
       <c r="B2" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$22,A2)</f>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$23,A2)</f>
         <v>1</v>
       </c>
       <c r="C2" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$22,A2,Контакты!$U$2:$U$22,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$23,A2,Контакты!$U$2:$U$23,"Высокий")</f>
         <v>0</v>
       </c>
     </row>
@@ -3789,11 +3873,11 @@
         <v>44</v>
       </c>
       <c r="B3" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$22,A3)</f>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$23,A3)</f>
         <v>6</v>
       </c>
       <c r="C3" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$22,A3,Контакты!$U$2:$U$22,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$23,A3,Контакты!$U$2:$U$23,"Высокий")</f>
         <v>4</v>
       </c>
     </row>
@@ -3802,11 +3886,11 @@
         <v>131</v>
       </c>
       <c r="B4" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$22,A4)</f>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$23,A4)</f>
         <v>1</v>
       </c>
       <c r="C4" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$22,A4,Контакты!$U$2:$U$22,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$23,A4,Контакты!$U$2:$U$23,"Высокий")</f>
         <v>0</v>
       </c>
     </row>
@@ -3815,51 +3899,51 @@
         <v>143</v>
       </c>
       <c r="B5" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$22,A5)</f>
-        <v>10</v>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$23,A5)</f>
+        <v>11</v>
       </c>
       <c r="C5" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$22,A5,Контакты!$U$2:$U$22,"Высокий")</f>
-        <v>3</v>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$23,A5,Контакты!$U$2:$U$23,"Высокий")</f>
+        <v>4</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="B6" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$22,A6)</f>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$23,A6)</f>
         <v>2</v>
       </c>
       <c r="C6" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$22,A6,Контакты!$U$2:$U$22,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$23,A6,Контакты!$U$2:$U$23,"Высокий")</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="B7" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$22,A7)</f>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$23,A7)</f>
         <v>1</v>
       </c>
       <c r="C7" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$22,A7,Контакты!$U$2:$U$22,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$23,A7,Контакты!$U$2:$U$23,"Высокий")</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="B8" s="7" t="n">
         <f aca="false">SUM(B2:B7)</f>
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" s="7" t="n">
         <f aca="false">SUM(C2:C7)</f>
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3872,7 +3956,7 @@
         <v>2</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="C10" s="6"/>
     </row>
@@ -3881,7 +3965,7 @@
         <v>132</v>
       </c>
       <c r="B11" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$22,A11)</f>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$23,A11)</f>
         <v>1</v>
       </c>
       <c r="C11" s="6"/>
@@ -3891,8 +3975,8 @@
         <v>45</v>
       </c>
       <c r="B12" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$22,A12)</f>
-        <v>11</v>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$23,A12)</f>
+        <v>12</v>
       </c>
       <c r="C12" s="6"/>
     </row>
@@ -3901,7 +3985,7 @@
         <v>24</v>
       </c>
       <c r="B13" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$22,A13)</f>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$23,A13)</f>
         <v>1</v>
       </c>
       <c r="C13" s="6"/>
@@ -3911,7 +3995,7 @@
         <v>186</v>
       </c>
       <c r="B14" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$22,A14)</f>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$23,A14)</f>
         <v>1</v>
       </c>
       <c r="C14" s="6"/>
@@ -3921,7 +4005,7 @@
         <v>60</v>
       </c>
       <c r="B15" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$22,A15)</f>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$23,A15)</f>
         <v>3</v>
       </c>
       <c r="C15" s="6"/>
@@ -3931,7 +4015,7 @@
         <v>72</v>
       </c>
       <c r="B16" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$22,A16)</f>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$23,A16)</f>
         <v>4</v>
       </c>
       <c r="C16" s="6"/>
@@ -3966,585 +4050,585 @@
         <v>4</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>60</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>327</v>
+        <v>336</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>60</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>60</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="B8" s="9" t="s">
         <v>60</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>60</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="C10" s="9" t="s">
+        <v>348</v>
+      </c>
+      <c r="D10" s="9" t="s">
         <v>339</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="9" t="s">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="9" t="s">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="s">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="s">
-        <v>373</v>
+        <v>382</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="s">
-        <v>375</v>
+        <v>384</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="s">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="9" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>380</v>
+        <v>389</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="9" t="s">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="9" t="s">
-        <v>382</v>
+        <v>391</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="9" t="s">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="9" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="s">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="9" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="s">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="9" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="9" t="s">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="C38" s="9"/>
       <c r="D38" s="9" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="9" t="s">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="9" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="8" t="s">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="C40" s="9"/>
       <c r="D40" s="9" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="9" t="s">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="9" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="9" t="s">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="8" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>325</v>
+        <v>334</v>
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="9" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
     </row>
   </sheetData>

--- a/exhibition/contacts.xlsx
+++ b/exhibition/contacts.xlsx
@@ -13,7 +13,7 @@
     <sheet name="Стенд INPD (Китай)" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Контакты!$A$1:$W$23</definedName>
+    <definedName function="false" hidden="true" localSheetId="0" name="_xlnm._FilterDatabase" vbProcedure="false">Контакты!$A$1:$W$24</definedName>
     <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Стенд INPD (Китай)'!$A$1:$D$43</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="404">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="412">
   <si>
     <t xml:space="preserve">№</t>
   </si>
@@ -886,6 +886,30 @@
   </si>
   <si>
     <t xml:space="preserve">photos/010_formulance.jpg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Франция (Париж — агентство Centdegrés); подразделения в Европе и Северной Америке</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IBG — Innovative Beauty Group (Orchard Custom Beauty, Fasten Packaging, Roberts Beauty) + агентство Centdegrés</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cosmetic 360, пространство «The Innovative Menu» (IBG × Centdegrés)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Разработка продукта и бренда под ключ (turnkey): парфюм, макияж («инновационные рецептуры с высокой пигментацией»), уход; упаковка; брендинг и дизайн (Centdegrés). Сегменты масс-маркет и масстиж, работают с брендами и торговыми сетями. На стенде — флаконы парфюма в цветном стекле, ароматическое сырьё, макияж</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IBG — подразделение Albéa (с 2024 г. принадлежит фонду Freeman Capital). Оборот ~380 млн $ (2024), ~400 сотрудников. В июле 2025 купили парижское агентство Centdegrés (основано в 1988 г.). Модель: под ключ + упаковка + агентство. По словам CEO, работают без своих фабрик — производство через партнёров (источники расходятся). Запущен Centdegrés North America.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.formesdeluxe.com/article/with-centdegres-acquisition-innovative-beauty-group-gets-a-shot-of-creativity.65037 ; https://www.beautymatter.com/articles/french-creative-agency-centdegres-joins-innovative-beauty-group ; https://www.premiumbeautynews.com/en/innovative-beauty-group-boosts,26053 ; https://www.formesdeluxe.com/article/innovative-beauty-group-ibg-unveils-new-positioning.65153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Взять контакт; уточнить MOQ (вероятно, крупные — масс-маркет), парфюм и макияж под ключ, цены, сроки</t>
+  </si>
+  <si>
+    <t xml:space="preserve">photos/023_ibg_centdegres.jpg</t>
   </si>
   <si>
     <t xml:space="preserve">Форкалькье (Альпы Верхнего Прованса), Прованс; второй сайт — Валансоль</t>
@@ -2368,7 +2392,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:W23"/>
+  <dimension ref="A1:W24"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="5"/>
@@ -3271,7 +3295,7 @@
         <v>210</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
@@ -3288,55 +3312,43 @@
         <v>212</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G15" s="4" t="s">
         <v>213</v>
       </c>
+      <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="J15" s="2" t="s">
+      <c r="J15" s="2"/>
+      <c r="K15" s="2"/>
+      <c r="L15" s="2"/>
+      <c r="M15" s="2"/>
+      <c r="N15" s="2"/>
+      <c r="O15" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q15" s="2"/>
+      <c r="R15" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="K15" s="2"/>
-      <c r="L15" s="2" t="s">
+      <c r="S15" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="M15" s="2" t="s">
+      <c r="T15" s="2" t="s">
         <v>217</v>
-      </c>
-      <c r="N15" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="O15" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="P15" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="Q15" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="R15" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="S15" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="T15" s="2" t="s">
-        <v>224</v>
       </c>
       <c r="U15" s="2"/>
       <c r="V15" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W15" s="2" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
@@ -3347,51 +3359,61 @@
         <v>45</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>226</v>
+        <v>219</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>227</v>
+        <v>220</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>229</v>
+        <v>27</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>221</v>
       </c>
       <c r="H16" s="2"/>
       <c r="I16" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="K16" s="2"/>
+      <c r="L16" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="P16" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="R16" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
-      <c r="M16" s="2"/>
-      <c r="N16" s="2"/>
-      <c r="O16" s="2" t="s">
+      <c r="S16" s="2" t="s">
         <v>231</v>
       </c>
-      <c r="P16" s="2" t="s">
+      <c r="T16" s="2" t="s">
         <v>232</v>
-      </c>
-      <c r="Q16" s="2"/>
-      <c r="R16" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="S16" s="2" t="s">
-        <v>234</v>
-      </c>
-      <c r="T16" s="2" t="s">
-        <v>235</v>
       </c>
       <c r="U16" s="2"/>
       <c r="V16" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W16" s="2" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
@@ -3402,63 +3424,51 @@
         <v>45</v>
       </c>
       <c r="D17" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="G17" s="2" t="s">
         <v>237</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="G17" s="4" t="s">
-        <v>240</v>
       </c>
       <c r="H17" s="2"/>
       <c r="I17" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2"/>
+      <c r="L17" s="2"/>
+      <c r="M17" s="2"/>
+      <c r="N17" s="2"/>
+      <c r="O17" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="P17" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="Q17" s="2"/>
+      <c r="R17" s="2" t="s">
         <v>241</v>
       </c>
-      <c r="J17" s="2" t="s">
+      <c r="S17" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="K17" s="2"/>
-      <c r="L17" s="2" t="s">
+      <c r="T17" s="2" t="s">
         <v>243</v>
       </c>
-      <c r="M17" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="N17" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="O17" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="P17" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="Q17" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="R17" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="S17" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="T17" s="2" t="s">
-        <v>251</v>
-      </c>
-      <c r="U17" s="2" t="s">
-        <v>58</v>
-      </c>
+      <c r="U17" s="2"/>
       <c r="V17" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W17" s="2" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="180.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
@@ -3469,41 +3479,51 @@
         <v>45</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="G18" s="2"/>
+        <v>247</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>248</v>
+      </c>
       <c r="H18" s="2"/>
       <c r="I18" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="M18" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="N18" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="O18" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="P18" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="Q18" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="J18" s="2"/>
-      <c r="K18" s="2"/>
-      <c r="L18" s="2"/>
-      <c r="M18" s="2"/>
-      <c r="N18" s="2"/>
-      <c r="O18" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="P18" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q18" s="2" t="s">
+      <c r="R18" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="R18" s="2" t="s">
+      <c r="S18" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="S18" s="2" t="s">
+      <c r="T18" s="2" t="s">
         <v>259</v>
-      </c>
-      <c r="T18" s="2" t="s">
-        <v>260</v>
       </c>
       <c r="U18" s="2" t="s">
         <v>58</v>
@@ -3512,10 +3532,10 @@
         <v>42</v>
       </c>
       <c r="W18" s="2" t="s">
-        <v>261</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="180.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
@@ -3526,20 +3546,18 @@
         <v>45</v>
       </c>
       <c r="D19" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="F19" s="2" t="s">
         <v>263</v>
       </c>
-      <c r="F19" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G19" s="4" t="s">
-        <v>264</v>
-      </c>
+      <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
@@ -3547,27 +3565,31 @@
       <c r="M19" s="2"/>
       <c r="N19" s="2"/>
       <c r="O19" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="R19" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="P19" s="2" t="s">
+      <c r="S19" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="Q19" s="2"/>
-      <c r="R19" s="2" t="s">
+      <c r="T19" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="S19" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="T19" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="U19" s="2"/>
+      <c r="U19" s="2" t="s">
+        <v>58</v>
+      </c>
       <c r="V19" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W19" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3581,20 +3603,20 @@
         <v>45</v>
       </c>
       <c r="D20" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G20" s="4" t="s">
         <v>272</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>275</v>
       </c>
       <c r="H20" s="2"/>
       <c r="I20" s="2" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
@@ -3602,118 +3624,122 @@
       <c r="M20" s="2"/>
       <c r="N20" s="2"/>
       <c r="O20" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="Q20" s="2"/>
+      <c r="R20" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="S20" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="P20" s="2" t="s">
+      <c r="T20" s="2" t="s">
         <v>278</v>
-      </c>
-      <c r="Q20" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="R20" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="S20" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="T20" s="2" t="s">
-        <v>282</v>
       </c>
       <c r="U20" s="2"/>
       <c r="V20" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W20" s="2" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="2" t="n">
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>284</v>
+        <v>143</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>45</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="G21" s="2"/>
-      <c r="H21" s="4" t="s">
-        <v>288</v>
-      </c>
+        <v>282</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="H21" s="2"/>
       <c r="I21" s="2" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
-      <c r="L21" s="2" t="s">
-        <v>290</v>
-      </c>
+      <c r="L21" s="2"/>
       <c r="M21" s="2"/>
       <c r="N21" s="2"/>
       <c r="O21" s="2" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>67</v>
+        <v>286</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="R21" s="2" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="S21" s="2" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="T21" s="2" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="U21" s="2"/>
       <c r="V21" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W21" s="2" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="2" t="n">
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D22" s="2"/>
+      <c r="D22" s="2" t="s">
+        <v>293</v>
+      </c>
       <c r="E22" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="G22" s="2"/>
+      <c r="H22" s="4" t="s">
+        <v>296</v>
+      </c>
+      <c r="I22" s="2" t="s">
         <v>297</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2" t="s">
-        <v>299</v>
       </c>
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
-      <c r="L22" s="2"/>
+      <c r="L22" s="2" t="s">
+        <v>298</v>
+      </c>
       <c r="M22" s="2"/>
       <c r="N22" s="2"/>
-      <c r="O22" s="2"/>
+      <c r="O22" s="2" t="s">
+        <v>299</v>
+      </c>
       <c r="P22" s="2" t="s">
         <v>67</v>
       </c>
@@ -3737,67 +3763,118 @@
         <v>304</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="2" t="n">
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
+        <v>292</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="C23" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="D23" s="2" t="s">
+      <c r="F23" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2" t="s">
         <v>307</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="G23" s="4" t="s">
-        <v>308</v>
-      </c>
-      <c r="H23" s="4" t="s">
-        <v>309</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>310</v>
       </c>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
       <c r="L23" s="2"/>
       <c r="M23" s="2"/>
       <c r="N23" s="2"/>
-      <c r="O23" s="2" t="s">
+      <c r="O23" s="2"/>
+      <c r="P23" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q23" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="R23" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="S23" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="T23" s="2" t="s">
         <v>311</v>
-      </c>
-      <c r="P23" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="Q23" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="R23" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="S23" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="T23" s="2" t="s">
-        <v>316</v>
       </c>
       <c r="U23" s="2"/>
       <c r="V23" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W23" s="2" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>313</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="G24" s="4" t="s">
+        <v>316</v>
+      </c>
+      <c r="H24" s="4" t="s">
         <v>317</v>
       </c>
+      <c r="I24" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
+      <c r="M24" s="2"/>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="P24" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="Q24" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="R24" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="S24" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="T24" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="U24" s="2"/>
+      <c r="V24" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="W24" s="2" t="s">
+        <v>325</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:W23"/>
+  <autoFilter ref="A1:W24"/>
   <hyperlinks>
     <hyperlink ref="G2" r:id="rId1" display="https://www.dachser.fr"/>
     <hyperlink ref="H2" r:id="rId2" display="https://www.dachser.com/en/cosmetic-logistics"/>
@@ -3813,12 +3890,12 @@
     <hyperlink ref="G12" r:id="rId12" display="https://www.desjardin.fr"/>
     <hyperlink ref="H12" r:id="rId13" display="https://www.desjardin.fr/en/categories/cosmetic-packaging"/>
     <hyperlink ref="G13" r:id="rId14" display="www.effervescence-lab.com"/>
-    <hyperlink ref="G15" r:id="rId15" display="https://www.laboratoiresbea.com"/>
-    <hyperlink ref="G17" r:id="rId16" display="https://www.msbeautilab.com"/>
-    <hyperlink ref="G19" r:id="rId17" display="https://simah-cosmetiques.fr"/>
-    <hyperlink ref="H21" r:id="rId18" display="https://welcon.kocca.kr/en/directory/company/cosplan-inc--5601"/>
-    <hyperlink ref="G23" r:id="rId19" display="https://iwasecosfa.eu"/>
-    <hyperlink ref="H23" r:id="rId20" display="https://iwasecosfa-eu.covalo.com/"/>
+    <hyperlink ref="G16" r:id="rId15" display="https://www.laboratoiresbea.com"/>
+    <hyperlink ref="G18" r:id="rId16" display="https://www.msbeautilab.com"/>
+    <hyperlink ref="G20" r:id="rId17" display="https://simah-cosmetiques.fr"/>
+    <hyperlink ref="H22" r:id="rId18" display="https://welcon.kocca.kr/en/directory/company/cosplan-inc--5601"/>
+    <hyperlink ref="G24" r:id="rId19" display="https://iwasecosfa.eu"/>
+    <hyperlink ref="H24" r:id="rId20" display="https://iwasecosfa-eu.covalo.com/"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3849,10 +3926,10 @@
         <v>1</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3860,11 +3937,11 @@
         <v>23</v>
       </c>
       <c r="B2" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$23,A2)</f>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$24,A2)</f>
         <v>1</v>
       </c>
       <c r="C2" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$23,A2,Контакты!$U$2:$U$23,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$24,A2,Контакты!$U$2:$U$24,"Высокий")</f>
         <v>0</v>
       </c>
     </row>
@@ -3873,11 +3950,11 @@
         <v>44</v>
       </c>
       <c r="B3" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$23,A3)</f>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$24,A3)</f>
         <v>6</v>
       </c>
       <c r="C3" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$23,A3,Контакты!$U$2:$U$23,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$24,A3,Контакты!$U$2:$U$24,"Высокий")</f>
         <v>4</v>
       </c>
     </row>
@@ -3886,11 +3963,11 @@
         <v>131</v>
       </c>
       <c r="B4" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$23,A4)</f>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$24,A4)</f>
         <v>1</v>
       </c>
       <c r="C4" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$23,A4,Контакты!$U$2:$U$23,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$24,A4,Контакты!$U$2:$U$24,"Высокий")</f>
         <v>0</v>
       </c>
     </row>
@@ -3899,47 +3976,47 @@
         <v>143</v>
       </c>
       <c r="B5" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$23,A5)</f>
-        <v>11</v>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$24,A5)</f>
+        <v>12</v>
       </c>
       <c r="C5" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$23,A5,Контакты!$U$2:$U$23,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$24,A5,Контакты!$U$2:$U$24,"Высокий")</f>
         <v>4</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="B6" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$23,A6)</f>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$24,A6)</f>
         <v>2</v>
       </c>
       <c r="C6" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$23,A6,Контакты!$U$2:$U$23,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$24,A6,Контакты!$U$2:$U$24,"Высокий")</f>
         <v>0</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="B7" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$B$2:$B$23,A7)</f>
+        <f aca="false">COUNTIF(Контакты!$B$2:$B$24,A7)</f>
         <v>1</v>
       </c>
       <c r="C7" s="6" t="n">
-        <f aca="false">COUNTIFS(Контакты!$B$2:$B$23,A7,Контакты!$U$2:$U$23,"Высокий")</f>
+        <f aca="false">COUNTIFS(Контакты!$B$2:$B$24,A7,Контакты!$U$2:$U$24,"Высокий")</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="B8" s="7" t="n">
         <f aca="false">SUM(B2:B7)</f>
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8" s="7" t="n">
         <f aca="false">SUM(C2:C7)</f>
@@ -3956,7 +4033,7 @@
         <v>2</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="C10" s="6"/>
     </row>
@@ -3965,7 +4042,7 @@
         <v>132</v>
       </c>
       <c r="B11" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$23,A11)</f>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$24,A11)</f>
         <v>1</v>
       </c>
       <c r="C11" s="6"/>
@@ -3975,8 +4052,8 @@
         <v>45</v>
       </c>
       <c r="B12" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$23,A12)</f>
-        <v>12</v>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$24,A12)</f>
+        <v>13</v>
       </c>
       <c r="C12" s="6"/>
     </row>
@@ -3985,7 +4062,7 @@
         <v>24</v>
       </c>
       <c r="B13" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$23,A13)</f>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$24,A13)</f>
         <v>1</v>
       </c>
       <c r="C13" s="6"/>
@@ -3995,7 +4072,7 @@
         <v>186</v>
       </c>
       <c r="B14" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$23,A14)</f>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$24,A14)</f>
         <v>1</v>
       </c>
       <c r="C14" s="6"/>
@@ -4005,7 +4082,7 @@
         <v>60</v>
       </c>
       <c r="B15" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$23,A15)</f>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$24,A15)</f>
         <v>3</v>
       </c>
       <c r="C15" s="6"/>
@@ -4015,7 +4092,7 @@
         <v>72</v>
       </c>
       <c r="B16" s="6" t="n">
-        <f aca="false">COUNTIF(Контакты!$C$2:$C$23,A16)</f>
+        <f aca="false">COUNTIF(Контакты!$C$2:$C$24,A16)</f>
         <v>4</v>
       </c>
       <c r="C16" s="6"/>
@@ -4050,585 +4127,585 @@
         <v>4</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>60</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>60</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>60</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="B8" s="9" t="s">
         <v>60</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>60</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="B10" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="C10" s="9" t="s">
+        <v>356</v>
+      </c>
+      <c r="D10" s="9" t="s">
         <v>347</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>348</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="B11" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="C11" s="9" t="s">
+        <v>358</v>
+      </c>
+      <c r="D11" s="9" t="s">
         <v>347</v>
-      </c>
-      <c r="C11" s="9" t="s">
-        <v>350</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="B12" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="C12" s="9" t="s">
+        <v>360</v>
+      </c>
+      <c r="D12" s="9" t="s">
         <v>347</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>352</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="B13" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="C13" s="9" t="s">
+        <v>362</v>
+      </c>
+      <c r="D13" s="9" t="s">
         <v>347</v>
-      </c>
-      <c r="C13" s="9" t="s">
-        <v>354</v>
-      </c>
-      <c r="D13" s="9" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
+        <v>363</v>
+      </c>
+      <c r="B14" s="9" t="s">
         <v>355</v>
       </c>
-      <c r="B14" s="9" t="s">
+      <c r="C14" s="9" t="s">
+        <v>364</v>
+      </c>
+      <c r="D14" s="9" t="s">
         <v>347</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>356</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="B15" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="C15" s="9" t="s">
+        <v>366</v>
+      </c>
+      <c r="D15" s="9" t="s">
         <v>347</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>358</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="B16" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="C16" s="9" t="s">
+        <v>368</v>
+      </c>
+      <c r="D16" s="9" t="s">
         <v>347</v>
-      </c>
-      <c r="C16" s="9" t="s">
-        <v>360</v>
-      </c>
-      <c r="D16" s="9" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="B18" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="C18" s="9" t="s">
+        <v>372</v>
+      </c>
+      <c r="D18" s="9" t="s">
         <v>347</v>
-      </c>
-      <c r="C18" s="9" t="s">
-        <v>364</v>
-      </c>
-      <c r="D18" s="9" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="B19" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="C19" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="D19" s="9" t="s">
         <v>347</v>
-      </c>
-      <c r="C19" s="9" t="s">
-        <v>366</v>
-      </c>
-      <c r="D19" s="9" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="B20" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="C20" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="D20" s="9" t="s">
         <v>347</v>
-      </c>
-      <c r="C20" s="9" t="s">
-        <v>366</v>
-      </c>
-      <c r="D20" s="9" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="B22" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="C22" s="9" t="s">
+        <v>379</v>
+      </c>
+      <c r="D22" s="9" t="s">
         <v>347</v>
-      </c>
-      <c r="C22" s="9" t="s">
-        <v>371</v>
-      </c>
-      <c r="D22" s="9" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="B24" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>372</v>
+      </c>
+      <c r="D24" s="9" t="s">
         <v>347</v>
-      </c>
-      <c r="C24" s="9" t="s">
-        <v>364</v>
-      </c>
-      <c r="D24" s="9" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="B25" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="C25" s="9" t="s">
+        <v>384</v>
+      </c>
+      <c r="D25" s="9" t="s">
         <v>347</v>
-      </c>
-      <c r="C25" s="9" t="s">
-        <v>376</v>
-      </c>
-      <c r="D25" s="9" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="9" t="s">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="B26" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="C26" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="D26" s="9" t="s">
         <v>347</v>
-      </c>
-      <c r="C26" s="9" t="s">
-        <v>366</v>
-      </c>
-      <c r="D26" s="9" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="9" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="B27" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="C27" s="9" t="s">
+        <v>387</v>
+      </c>
+      <c r="D27" s="9" t="s">
         <v>347</v>
-      </c>
-      <c r="C27" s="9" t="s">
-        <v>379</v>
-      </c>
-      <c r="D27" s="9" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="B28" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="C28" s="9" t="s">
+        <v>389</v>
+      </c>
+      <c r="D28" s="9" t="s">
         <v>347</v>
-      </c>
-      <c r="C28" s="9" t="s">
-        <v>381</v>
-      </c>
-      <c r="D28" s="9" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="B29" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="C29" s="9" t="s">
+        <v>391</v>
+      </c>
+      <c r="D29" s="9" t="s">
         <v>347</v>
-      </c>
-      <c r="C29" s="9" t="s">
-        <v>383</v>
-      </c>
-      <c r="D29" s="9" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="9" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="B32" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="C32" s="9" t="s">
+        <v>397</v>
+      </c>
+      <c r="D32" s="9" t="s">
         <v>347</v>
-      </c>
-      <c r="C32" s="9" t="s">
-        <v>389</v>
-      </c>
-      <c r="D32" s="9" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="9" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="B33" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="C33" s="9" t="s">
+        <v>374</v>
+      </c>
+      <c r="D33" s="9" t="s">
         <v>347</v>
-      </c>
-      <c r="C33" s="9" t="s">
-        <v>366</v>
-      </c>
-      <c r="D33" s="9" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="9" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="B34" s="9" t="s">
+        <v>355</v>
+      </c>
+      <c r="C34" s="9" t="s">
+        <v>400</v>
+      </c>
+      <c r="D34" s="9" t="s">
         <v>347</v>
-      </c>
-      <c r="C34" s="9" t="s">
-        <v>392</v>
-      </c>
-      <c r="D34" s="9" t="s">
-        <v>339</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="9" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="9" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="9" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="9" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="9" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="C38" s="9"/>
       <c r="D38" s="9" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="9" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="9" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="8" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="C40" s="9"/>
       <c r="D40" s="9" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="9" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="9" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="9" t="s">
-        <v>401</v>
+        <v>409</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="C42" s="9" t="s">
+        <v>410</v>
+      </c>
+      <c r="D42" s="9" t="s">
         <v>402</v>
-      </c>
-      <c r="D42" s="9" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="8" t="s">
-        <v>403</v>
+        <v>411</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="9" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
     </row>
   </sheetData>

--- a/exhibition/contacts.xlsx
+++ b/exhibition/contacts.xlsx
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="412">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="414">
   <si>
     <t xml:space="preserve">№</t>
   </si>
@@ -900,6 +900,9 @@
     <t xml:space="preserve">Разработка продукта и бренда под ключ (turnkey): парфюм, макияж («инновационные рецептуры с высокой пигментацией»), уход; упаковка; брендинг и дизайн (Centdegrés). Сегменты масс-маркет и масстиж, работают с брендами и торговыми сетями. На стенде — флаконы парфюма в цветном стекле, ароматическое сырьё, макияж</t>
   </si>
   <si>
+    <t xml:space="preserve">Оценка: для старта скорее не подходит — посредник-разработчик без своих фабрик (дороже, чем напрямую), работает на масс-маркет и крупные сети, MOQ вероятно десятки тысяч. Плюс — всё под ключ: продукт, брендинг, упаковка, парфюм и макияж. Вариант на будущее при больших объёмах</t>
+  </si>
+  <si>
     <t xml:space="preserve">IBG — подразделение Albéa (с 2024 г. принадлежит фонду Freeman Capital). Оборот ~380 млн $ (2024), ~400 сотрудников. В июле 2025 купили парижское агентство Centdegrés (основано в 1988 г.). Модель: под ключ + упаковка + агентство. По словам CEO, работают без своих фабрик — производство через партнёров (источники расходятся). Запущен Centdegrés North America.</t>
   </si>
   <si>
@@ -907,6 +910,9 @@
   </si>
   <si>
     <t xml:space="preserve">Взять контакт; уточнить MOQ (вероятно, крупные — масс-маркет), парфюм и макияж под ключ, цены, сроки</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Низкий (на будущее)</t>
   </si>
   <si>
     <t xml:space="preserve">photos/023_ibg_centdegres.jpg</t>
@@ -3330,22 +3336,26 @@
       <c r="P15" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="Q15" s="2"/>
+      <c r="Q15" s="2" t="s">
+        <v>215</v>
+      </c>
       <c r="R15" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="U15" s="2"/>
+        <v>218</v>
+      </c>
+      <c r="U15" s="2" t="s">
+        <v>219</v>
+      </c>
       <c r="V15" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W15" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="147" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3359,58 +3369,58 @@
         <v>45</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>27</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="H16" s="2"/>
       <c r="I16" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="K16" s="2"/>
       <c r="L16" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="T16" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="U16" s="2"/>
       <c r="V16" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W16" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3424,20 +3434,20 @@
         <v>45</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="H17" s="2"/>
       <c r="I17" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
@@ -3445,27 +3455,27 @@
       <c r="M17" s="2"/>
       <c r="N17" s="2"/>
       <c r="O17" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="Q17" s="2"/>
       <c r="R17" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="T17" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="U17" s="2"/>
       <c r="V17" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W17" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3479,51 +3489,51 @@
         <v>45</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="H18" s="2"/>
       <c r="I18" s="2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="K18" s="2"/>
       <c r="L18" s="2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="R18" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="S18" s="2" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="T18" s="2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="U18" s="2" t="s">
         <v>58</v>
@@ -3532,7 +3542,7 @@
         <v>42</v>
       </c>
       <c r="W18" s="2" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="180.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3546,18 +3556,18 @@
         <v>45</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="G19" s="2"/>
       <c r="H19" s="2"/>
       <c r="I19" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
@@ -3571,16 +3581,16 @@
         <v>67</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="R19" s="2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="S19" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="T19" s="2" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="U19" s="2" t="s">
         <v>58</v>
@@ -3589,7 +3599,7 @@
         <v>42</v>
       </c>
       <c r="W19" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3603,20 +3613,20 @@
         <v>45</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>27</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="H20" s="2"/>
       <c r="I20" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
@@ -3624,27 +3634,27 @@
       <c r="M20" s="2"/>
       <c r="N20" s="2"/>
       <c r="O20" s="2" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="Q20" s="2"/>
       <c r="R20" s="2" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="T20" s="2" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="U20" s="2"/>
       <c r="V20" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W20" s="2" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="158.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3658,20 +3668,20 @@
         <v>45</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="H21" s="2"/>
       <c r="I21" s="2" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
@@ -3679,29 +3689,29 @@
       <c r="M21" s="2"/>
       <c r="N21" s="2"/>
       <c r="O21" s="2" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="R21" s="2" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="S21" s="2" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="T21" s="2" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="U21" s="2"/>
       <c r="V21" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W21" s="2" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="124.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3709,58 +3719,58 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>45</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="G22" s="2"/>
       <c r="H22" s="4" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
       <c r="L22" s="2" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="M22" s="2"/>
       <c r="N22" s="2"/>
       <c r="O22" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="P22" s="2" t="s">
         <v>67</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="R22" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="S22" s="2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="T22" s="2" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="U22" s="2"/>
       <c r="V22" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W22" s="2" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="102.2" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3768,22 +3778,22 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>45</v>
       </c>
       <c r="D23" s="2"/>
       <c r="E23" s="2" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="G23" s="2"/>
       <c r="H23" s="2"/>
       <c r="I23" s="2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
@@ -3795,23 +3805,23 @@
         <v>67</v>
       </c>
       <c r="Q23" s="2" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="R23" s="2" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="S23" s="2" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="T23" s="2" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="U23" s="2"/>
       <c r="V23" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W23" s="2" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="79.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3819,28 +3829,28 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>60</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>27</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
@@ -3848,29 +3858,29 @@
       <c r="M24" s="2"/>
       <c r="N24" s="2"/>
       <c r="O24" s="2" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="Q24" s="2" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="R24" s="2" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="S24" s="2" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="T24" s="2" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="U24" s="2"/>
       <c r="V24" s="2" t="s">
         <v>42</v>
       </c>
       <c r="W24" s="2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
     </row>
   </sheetData>
@@ -3926,10 +3936,10 @@
         <v>1</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3986,7 +3996,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="6" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B6" s="6" t="n">
         <f aca="false">COUNTIF(Контакты!$B$2:$B$24,A6)</f>
@@ -3999,7 +4009,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="B7" s="6" t="n">
         <f aca="false">COUNTIF(Контакты!$B$2:$B$24,A7)</f>
@@ -4012,7 +4022,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="7" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="B8" s="7" t="n">
         <f aca="false">SUM(B2:B7)</f>
@@ -4033,7 +4043,7 @@
         <v>2</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C10" s="6"/>
     </row>
@@ -4127,585 +4137,585 @@
         <v>4</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C1" s="5" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B2" s="9" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C2" s="9" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="9" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B3" s="9" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C3" s="9" t="s">
+        <v>339</v>
+      </c>
+      <c r="D3" s="9" t="s">
         <v>337</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>335</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B4" s="9" t="s">
         <v>60</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="8" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="B6" s="9" t="s">
         <v>60</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="8" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="B7" s="9" t="s">
         <v>60</v>
       </c>
       <c r="C7" s="9" t="s">
+        <v>351</v>
+      </c>
+      <c r="D7" s="9" t="s">
         <v>349</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>347</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="25.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="8" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B8" s="9" t="s">
         <v>60</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="8" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="B9" s="9" t="s">
         <v>60</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
+        <v>359</v>
+      </c>
+      <c r="B11" s="9" t="s">
         <v>357</v>
       </c>
-      <c r="B11" s="9" t="s">
-        <v>355</v>
-      </c>
       <c r="C11" s="9" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="8" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="8" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="8" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="8" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="8" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="8" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="8" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="8" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="8" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="8" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="8" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="8" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="9" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="9" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="8" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="8" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="8" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="8" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="9" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="9" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="9" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="9" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C35" s="9"/>
       <c r="D35" s="9" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="8" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C36" s="9"/>
       <c r="D36" s="9" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="8" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C37" s="9"/>
       <c r="D37" s="9" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="9" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C38" s="9"/>
       <c r="D38" s="9" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="9" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C39" s="9"/>
       <c r="D39" s="9" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="8" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C40" s="9"/>
       <c r="D40" s="9" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="9" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C41" s="9"/>
       <c r="D41" s="9" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="9" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="8" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C43" s="9"/>
       <c r="D43" s="9" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
     </row>
   </sheetData>
